--- a/evaluation.xlsx
+++ b/evaluation.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,11 +74,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="007F6000"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +165,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
@@ -190,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -248,6 +260,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -618,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -627,17 +642,20 @@
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="35" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -665,10 +683,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Avg Action Correctness (1-5)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Avg Clarity (1-5)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Overall Composite Quality</t>
         </is>
@@ -680,22 +703,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>4.95 / 5.0</t>
+          <t>5.00 / 5.0</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>4.88 / 5.0</t>
+          <t>4.86 / 5.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4.93 / 5.0</t>
+          <t>3.83 / 5.0</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>4.92 / 5.0</t>
+          <t>4.83 / 5.0</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>4.63 / 5.0</t>
         </is>
       </c>
     </row>
@@ -714,25 +742,28 @@
       </c>
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>AGENT OUTPUT (EVALUATED ARTIFACTS)</t>
         </is>
       </c>
-      <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>LLM JUDGE EVALUATION &amp; JUSTIFICATIONS</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>COMPOSITE</t>
         </is>
@@ -769,60 +800,76 @@
           <t>GT Policy Coverage &amp; Gaps</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Golden Mandatory Actions</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>Agent Hazard &amp; Risk Assessment</t>
         </is>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>Agent Proposed Micro-Actions</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>Agent Dispatched SMS</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Agent Push Notification</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>Faithfulness
 (1-5)</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Faithfulness Justification</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>Action Relevance
 (1-5)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>Action Relevance Justification</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>Action Correctness
+(1-5)</t>
+        </is>
+      </c>
+      <c r="Q6" s="16" t="inlineStr">
+        <is>
+          <t>Action Correctness Justification</t>
+        </is>
+      </c>
+      <c r="R6" s="16" t="inlineStr">
         <is>
           <t>Clarity
 (1-5)</t>
         </is>
       </c>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="S6" s="16" t="inlineStr">
         <is>
           <t>Clarity Justification</t>
         </is>
       </c>
-      <c r="Q6" s="17" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t>Composite
 Quality (1-5)</t>
@@ -873,6 +920,12 @@
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>• Elevate or remove ground-level belongings and valuables in the crawlspace to protect against water pooling and seepage
+• Ensure ground-level downspout extensions and surface runoff paths direct water safely away from the cabin foundation</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
@@ -882,53 +935,61 @@
 Identified Gaps: Sewer Backup Endorsement: UNINSURED, Overland Water Endorsement: UNINSURED</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Clear eavestroughs and downspouts to ensure proper drainage away from the crawlspace.
-Rationale: Heavy rainfall can overwhelm blocked drainage systems, leading to water accumulation around the foundation and potential crawlspace flooding, which is uninsured.
-[P2] INDOOR_WATER_PROTECTION: Move any valuable items currently stored in the crawlspace to a higher, dry location.
-Rationale: With a crawlspace basement and no sump pump, there is a high risk of water ingress during heavy rain, and both sewer backup and overland water damage are uninsured.
-[P3] INDOOR_WATER_PROTECTION: Monitor for water pooling around the foundation and consider deploying temporary barriers like sandbags if water levels rise.
-Rationale: Proactive monitoring and temporary barriers can help mitigate water intrusion into the crawlspace, especially given the lack of overland water coverage.</t>
-        </is>
-      </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy rain expected at HOM-1051. Clear eavestroughs &amp; move crawlspace valuables to prevent uninsured water damage. Stay safe!"
-(Length: 133 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear eavestroughs and downspouts to ensure proper drainage away from the crawlspace foundation.
+Rationale: Heavy rainfall (80 mm) can lead to water pooling and ingress into the crawlspace, which is uninsured for sewer backup and overland water.
+[P2] INDOOR_WATER_PROTECTION: Move any valuable items currently stored in the crawlspace to higher ground or a secure, dry location.
+Rationale: With no sump pump or backwater valve and uninsured water damage, items in the crawlspace are at high risk from 80 mm of rain.
+[P3] LIFE_SAFETY: Monitor local water levels, especially near rivers, creeks, and culverts, and be prepared for rapid runoff and localized washouts.
+Rationale: Heavy rainfall can cause rapid river runoff and localized washouts, posing a risk to property and safety.</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain (80mm) expected. Clear eavestroughs &amp; move crawlspace valuables. Uninsured for water damage. Stay safe!"
+(Length: 122 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rain expected at your property. Clear eavestroughs and move valuables from crawlspace to prevent uninsured water damage. Monitor foundation for pooling.</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning is accurately described with the expected maximum rainfall amount of 80 mm, which matches the ground truth alert. The property vulnerabilities and coverage gaps are correctly identified: the property has a crawlspace, no sump pump, and no backwater valve, and lacks sewer backup and overland water endorsements, all of which are consistent with the ground truth. The micro-actions suggested are appropriate and based on the property's specific vulnerabilities and insurance coverage gaps. There are no fabricated or hallucinated details in the advisory.</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril of heavy rainfall and the dwelling's vulnerabilities. The actions directly address the primary loss drivers of water ingress due to heavy rain, particularly focusing on the uninsured gaps of sewer backup and overland water. Clearing eavestroughs and downspouts is crucial to prevent water accumulation around the foundation, which is a significant risk given the crawlspace and lack of sump pump. Moving valuables from the crawlspace is a prudent measure to protect against potential water damage. Monitoring for water pooling and using temporary barriers like sandbags are practical and effective strategies to mitigate water intrusion, especially since the property lacks overland water coverage. These actions are executable within the warning lead time and avoid any dangerous outdoor work, aligning perfectly with the dwelling's structural vulnerabilities and policy gaps.</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and actionable, immediately informing the homeowner of the threat (heavy rain) and what to do first (clear eavestroughs, move valuables). It avoids insurance jargon and stays within the character limit, maintaining urgency without causing panic. The push notification complements the SMS by providing additional context and instructions, such as monitoring the foundation for pooling, which is clear and free of jargon. The micro-actions are straightforward, providing step-by-step guidance without technical language, ensuring homeowners can quickly understand and act on the instructions.</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="n">
+Body: Heavy rain (80mm) expected. Clear eavestroughs &amp; move crawlspace valuables. Uninsured for water damage. Monitor local water levels.</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning is accurately described with the expected 80 mm of rain, which matches the upper limit of the ground truth alert. The property details, such as the crawlspace basement, lack of sump pump, and lack of backwater valve, are correctly identified. The coverage gaps for sewer backup and overland water endorsements are also accurately noted as uninsured. All micro-actions and safety advisories are consistent with the potential risks outlined in the weather alert and the property's vulnerabilities. There are no fabricated or hallucinated details in the advisory.</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril of heavy rainfall and the dwelling's vulnerabilities. The first action addresses the primary loss driver of water ingress by ensuring proper drainage, which is crucial given the uninsured gaps for sewer backup and overland water. The second action is tailored to the dwelling's lack of a sump pump and backwater valve, directly mitigating potential damage to valuable items stored in the crawlspace. The third action focuses on life safety by monitoring water levels, which is essential given the risk of rapid runoff and washouts. All actions are executable within the warning lead time and avoid hazardous outdoor work during the rain event.</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover the mandatory reference actions. The action to "Move any valuable items currently stored in the crawlspace to higher ground or a secure, dry location" semantically matches the requirement to "Elevate or remove ground-level belongings and valuables in the crawlspace to protect against water pooling and seepage." The action to "Clear eavestroughs and downspouts to ensure proper drainage away from the crawlspace foundation" aligns with ensuring that "ground-level downspout extensions and surface runoff paths direct water safely away from the cabin foundation." Additionally, the agent's suggestion to "Monitor local water levels" is a logical and practical action given the alert's mention of rapid runoff and localized washouts, thus addressing potential secondary hazards. No illogical actions were proposed, and all actions are grounded in the context of the dwelling and weather alert.</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and actionable. They immediately inform the homeowner of the threat (heavy rain) and provide specific actions to take (clear eavestroughs, move valuables). The message is urgent but not panic-inducing, and it avoids any insurance jargon, simply stating 'uninsured for water damage' which is straightforward. The SMS is well within the character limit, maximizing impact. The micro-actions are detailed yet clear, providing step-by-step guidance without overwhelming the reader.</t>
+        </is>
+      </c>
+      <c r="T7" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -976,62 +1037,77 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
+          <t>• Secure or bring indoors all loose exterior items and yard equipment to prevent windborne projectile damage in 95 km/h gusts
+• Maintain steady indoor heating and protect exposed plumbing pipes to prevent freeze-up during extreme -38 wind chills</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: blizzard warning in effect
 Wind Gust: 95 km/h | Hail: None (None cm)
 Rain: None mm | Snow: 45.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 24-year-old asphalt shingle roof vulnerable to high winds and heavy snow load, crawlspace basement
-Identified Gaps: Overland Water Endorsement (UNINSURED for surface runoff)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Stay indoors and avoid all non-essential travel due to blizzard conditions, near-zero visibility, and extreme wind chills.
-Rationale: Blizzard conditions with high winds and heavy snow create dangerous travel conditions and risk of frostbite.
-[P2] INDOOR_SHELTER: Prepare for potential power outages by charging devices, having flashlights and extra blankets ready, and ensuring alternative heating sources are safe to use.
-Rationale: Extreme weather with high winds and heavy snow can cause power lines to fail, leading to prolonged outages.
-[P3] INDOOR_WATER_PROTECTION: Monitor for snow accumulation on the roof and be aware of potential stress on the 24-year-old asphalt shingle roof. Do NOT attempt to clear snow from the roof yourself.
-Rationale: Heavy snowfall (up to 45 cm) combined with an aged roof can lead to structural stress and potential damage. Self-clearing is unsafe in blizzard conditions.</t>
+Identified Vulnerabilities: Aged asphalt shingle roof (24 years old) vulnerable to high winds and heavy snow loading, Crawlspace foundation susceptible to snow accumulation and potential utility line freeze-up
+Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Blizzard Warning for HOM-1052. Stay indoors, avoid travel. Prepare for power outages. Do NOT clear snow from roof. Info: +1-306-555-1052"
-(Length: 144 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from around the foundation and egress points to prevent accumulation and potential issues for the crawlspace.
+Rationale: Heavy snowfall (45 cm) can accumulate around the crawlspace foundation and egress points, potentially leading to issues if not cleared.
+[P2] INDOOR_WATER_PROTECTION: Monitor for signs of ice damming and roof loading from inside the home or from a safe ground-level distance.
+Rationale: The aged asphalt shingle roof (24 years old) is vulnerable to heavy snow accumulation (45 cm) and potential ice damming, which can cause structural stress and water ingress. Monitoring should be done safely without climbing or direct roof inspection due to high winds.
+[P3] LIFE_SAFETY: Prepare for potential power outages and ensure alternative heating sources are available.
+Rationale: Blizzard conditions with high winds and extreme cold increase the risk of power outages and frozen pipes.</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Blizzard Mitigation Required
-Body: Blizzard conditions with 95 km/h winds and 45 cm snow. Stay indoors, prepare for outages, and monitor roof. Do NOT clear snow from roof.</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The blizzard warning details match exactly with the alert: 95 km/h wind gusts and 45 cm snowfall are correctly stated. The property details such as the 24-year-old asphalt shingle roof and crawlspace basement are accurately reflected. The advisory correctly notes the lack of overland water endorsement, aligning with the ground truth. No unverified claims or hallucinations are present.</t>
-        </is>
-      </c>
-      <c r="M8" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific blizzard conditions and the dwelling's vulnerabilities. The life safety action to stay indoors addresses the primary hazard of dangerous travel conditions and extreme cold, which is crucial given the blizzard warning. The indoor shelter action is appropriate for potential power outages due to high winds and snow, ensuring preparedness with charged devices and alternative heating, which is critical given the expected freeze-up of utility lines. The indoor water protection action is particularly well-tailored, acknowledging the aged asphalt shingle roof's vulnerability to heavy snow load without encouraging dangerous self-clearing during the blizzard. The actions are executable within the warning lead time and directly address the primary loss drivers of the blizzard, including structural stress from snow accumulation and power outage risks.</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, providing immediate instructions on what to do (stay indoors, avoid travel, prepare for outages) and what not to do (do not clear snow from roof). It avoids any insurance jargon and is well within the character limit. The push notification complements the SMS by providing additional context (wind speed and snow accumulation) without overwhelming the user. The micro-actions are clear, actionable, and free of jargon, providing specific steps to take during the blizzard. Overall, the communication is effective, urgent without causing panic, and easy to understand.</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: Blizzard warning for HOM-1052. Clear snow from foundation. Monitor roof for ice/loading from inside. Prepare for power outages. Stay safe!"
+(Length: 146 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Storm Mitigation Required
+Body: Blizzard warning for HOM-1052. Clear snow from foundation. Monitor roof for ice/loading from inside. Prepare for power outages. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The blizzard warning details, including wind gusts up to 95 km/h and snowfall of 45 cm, match the alert text. The property details, such as the 24-year-old asphalt shingle roof and crawlspace foundation, are accurately reflected in the advisory. The advisory correctly identifies the lack of overland water endorsement as a coverage gap, consistent with the policy details. No unverified claims or hallucinations are present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific blizzard conditions and the dwelling's vulnerabilities. The first action addresses the risk of snow accumulation around the foundation and egress points, which is crucial given the crawlspace and the uninsured overland water gap. The second action focuses on monitoring for ice damming and roof loading, which is pertinent given the aged asphalt shingle roof and the heavy snow forecast. Importantly, it emphasizes safe monitoring practices due to high winds, avoiding dangerous roof work. The third action addresses life safety by preparing for power outages and ensuring alternative heating, which is critical given the extreme cold and potential for utility disruptions. Overall, these actions directly target the primary loss drivers of the blizzard and are tailored to the property's specific vulnerabilities and policy gaps.</t>
+        </is>
+      </c>
+      <c r="P8" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions do not semantically cover any of the mandatory reference actions. The first mandatory action, which involves securing or bringing indoors loose exterior items to prevent windborne projectile damage, is not addressed by any of the agent's actions. The second mandatory action, which involves maintaining steady indoor heating and protecting exposed plumbing pipes, is also not covered. The agent's action to prepare for potential power outages and ensure alternative heating sources is related to maintaining heating but does not explicitly address protecting plumbing pipes from freezing.
+Additionally, the action to clear snow from around the foundation and egress points is illogical given the context of a blizzard with high winds and heavy snowfall, as it is impractical and unsafe to perform such an action during the blizzard conditions described. The other actions proposed by the agent, such as monitoring for ice damming and preparing for power outages, are logical and relevant to the blizzard conditions but do not cover the mandatory actions.</t>
+        </is>
+      </c>
+      <c r="R8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise and clear, effectively communicating the urgency of the situation without causing panic. The SMS is within the character limit and provides specific actions: clearing snow from the foundation, monitoring the roof for ice, and preparing for power outages. The language is straightforward and free of insurance jargon, making it easy for a homeowner to understand and act upon quickly. The micro-actions further clarify the steps without introducing complexity or technical terms, ensuring the homeowner knows exactly what to do.</t>
+        </is>
+      </c>
+      <c r="T8" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="9" ht="135" customHeight="1">
@@ -1077,64 +1153,77 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
 Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Asphalt shingle roof vulnerable to 90 km/h wind gusts and nickel-sized hail, Finished basement at risk from torrential downpours exceeding 50 mm
-Identified Gaps: Sewer Backup Endorsement: UNINSURED, Overland Water Endorsement: UNINSURED</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>[P1] VEHICLE_PROTECTION: Move all vehicles into a garage or covered area to protect them from hail and high winds.
-Rationale: Nickel-sized hail and 90 km/h wind gusts can cause significant damage to vehicles.
-[P2] INDOOR_SHELTER: Secure or store all loose outdoor items such as patio furniture, garbage bins, and trampolines to prevent them from becoming dangerous projectiles in high winds.
-Rationale: High winds (90 km/h) can turn unsecured items into projectiles, causing property damage or injury.
-[P3] INDOOR_WATER_PROTECTION: Ensure all basement windows and ground-level entry points are securely closed and sealed to prevent water ingress from torrential downpours.
-Rationale: Heavy rainfall (exceeding 50 mm) poses a significant risk of water entry, and your policy has critical gaps for sewer backup and overland water.</t>
+Identified Vulnerabilities: Finished basement vulnerable to water damage from torrential downpours, Asphalt shingle roof (4 years old) vulnerable to 90 km/h wind gusts and nickel-sized hail
+Identified Gaps: Basement sewer backup damage is UNINSURED, Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe storm with 90km/h winds &amp; hail. Move vehicles to garage &amp; secure outdoor items. Check basement seals. Stay safe! #HOM-1001"
-(Length: 137 / 160 chars)</t>
+          <t>[P1] VEHICLE_PROTECTION: Move vehicles to a covered garage or a less exposed area away from trees and potential falling debris to protect against hail and wind damage.
+Rationale: 90 km/h wind gusts and nickel-sized hail pose a significant risk of damage to vehicles.
+[P2] INDOOR_WATER_PROTECTION: Ensure all downspouts are clear of debris and directed at least 6 feet away from the foundation to prevent water accumulation and potential basement flooding, especially given the uninsured overland water risk.
+Rationale: Torrential downpours with localized amounts exceeding 50 mm can overwhelm drainage systems and lead to water ingress, which is not covered by your policy.
+[P3] LIFE_SAFETY: Stay indoors and away from windows during the storm. Do not attempt to climb ladders, inspect shingles, or clean roof gutters due to high winds.
+Rationale: High winds (90 km/h) make outdoor activities extremely dangerous and can lead to serious injury.</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe storm with 90km/h winds &amp; hail. Move vehicles to shelter. Ensure downspouts are clear. Stay indoors. Safety first!"
+(Length: 129 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm warning for your area. Move vehicles, secure outdoor items, and seal basement entry points. Your property is at risk from 90 km/h winds, hail, and heavy rain.</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the asphalt shingle roof, finished basement, and lack of sewer backup and overland water endorsements, are accurately reflected in the advisory. No fabricated numbers or unverified property features are present. All claims are consistent with the ground truth.</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's vulnerabilities. The first action addresses the risk of hail and wind damage to vehicles, which is a primary concern given the forecasted nickel-sized hail and 90 km/h wind gusts. The second action mitigates the risk of windborne projectiles, a key loss driver in severe thunderstorms, by securing loose outdoor items. The third action is crucial for preventing water ingress into the finished basement, especially given the uninsured gaps for sewer backup and overland water, and the forecasted torrential downpours. All actions are executable within the warning lead time and avoid hazardous outdoor work during the storm.</t>
-        </is>
-      </c>
-      <c r="O9" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the severe storm threat and providing specific actions to take: moving vehicles, securing outdoor items, and checking basement seals. It avoids any insurance jargon and fits within the character limit, making it highly effective for quick comprehension during an emergency.
-The push notification complements the SMS by providing a slightly more detailed explanation of the threat and actions, maintaining clarity and urgency without causing panic. It also avoids jargon and clearly outlines the risks and necessary actions.
-The micro-actions are detailed yet straightforward, providing clear instructions on what to do to mitigate damage, without any confusing terminology. Overall, the communication is crystal clear and actionable, making it easy for homeowners to understand and act upon immediately.</t>
-        </is>
-      </c>
-      <c r="Q9" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm with 90 km/h winds and nickel-sized hail. Move vehicles to shelter and ensure downspouts are clear. Stay indoors and prioritize safety.</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm, directly match the ground truth weather alert. The property details, such as the detached dwelling type, asphalt shingle roof (4 years old), finished basement, and lack of sewer backup and overland water endorsements, are accurately reflected in the advisory. There is no fabrication or unverified speculation present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and the dwelling's vulnerabilities. The vehicle protection action directly addresses the risk of hail and wind damage, which are primary loss drivers in a severe thunderstorm. The indoor water protection action is well-tailored to the dwelling's uninsured overland water risk, emphasizing the importance of clear downspouts to prevent basement flooding. The life safety action appropriately advises against dangerous outdoor activities during high winds, aligning with mandatory safety requirements. Overall, these actions are highly relevant and specifically tailored to the dwelling's structural features and policy gaps.</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
+        <is>
+          <t>The agent successfully covered the mandatory action of moving vehicles to a protective shelter to avoid hail damage. However, it completely omitted the actions of securing outdoor items to prevent projectile damage and closing windows and doors to prevent water infiltration and wind pressurization. Additionally, the agent proposed an illogical action regarding clearing downspouts, which is not directly relevant to the immediate threat of a severe thunderstorm with high winds and hail, and is more applicable to general rainstorm preparation. The life safety advice, while sound, is not relevant to property loss mitigation and does not affect the score.</t>
+        </is>
+      </c>
+      <c r="R9" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the severe storm threat and what actions to take first. It avoids any insurance jargon and fits well within the character limit. The push notification maintains the same clarity and urgency, with a slightly expanded explanation that remains free of jargon. The micro-actions are detailed yet clear, providing specific instructions without using technical insurance terms. Overall, the communication is direct, actionable, and prioritizes safety effectively.</t>
+        </is>
+      </c>
+      <c r="T9" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" ht="135" customHeight="1">
@@ -1180,62 +1269,77 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: 0.0 cm
+Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
 Identified Vulnerabilities: Unfinished basement, No sump pump, No backwater valve
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items from the unfinished basement floor to higher ground.
-Rationale: Without a sump pump or backwater valve, the unfinished basement is vulnerable to water damage from heavy rainfall and potential sewer backup, despite coverage.
-[P2] VEHICLE_PROTECTION: Park vehicles in a garage or away from trees and structures that could be damaged by high winds and hail.
-Rationale: 90 km/h wind gusts and nickel-sized hail pose a significant risk of damage to vehicles if left exposed.
-[P3] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and garden tools.
-Rationale: High wind gusts of 90 km/h can turn unsecured outdoor items into dangerous projectiles, causing property damage or injury.</t>
-        </is>
-      </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe thunderstorm with 90km/h winds &amp; hail. Move basement valuables &amp; secure outdoor items. Stay safe indoors!"
-(Length: 120 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Secure or bring indoors any loose outdoor items (patio furniture, garbage bins, toys) that could become projectiles.
+Rationale: 90 km/h wind gusts can turn unsecured outdoor items into dangerous projectiles, posing a risk to life and property. This action should be completed immediately if safe to do so.
+[P2] INDOOR_WATER_PROTECTION: Move valuable items from the unfinished basement floor to higher ground.
+Rationale: With no sump pump or backwater valve, the unfinished basement is vulnerable to water ingress from heavy rain (50 mm), despite coverage. Elevating items reduces damage risk.
+[P3] VEHICLE_PROTECTION: Park vehicles in a garage or the safest available location away from trees and structures.
+Rationale: 90 km/h wind gusts and nickel-sized hail pose a significant risk of damage to vehicles if left exposed. Seek immediate shelter for vehicles.</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90 km/h winds, hail, and 50mm rain. Secure outdoor items, move basement valuables, park vehicles safely. Do NOT climb ladders."
+(Length: 159 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds and nickel-sized hail. Move basement valuables to higher ground and secure all loose outdoor items. Park vehicles safely.</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm, match the weather alert. The property details, such as the unfinished basement, absence of a sump pump and backwater valve, and the endorsements for sewer backup and overland water, are accurately reflected in the advisory. There are no fabricated numbers or unverified features mentioned. The advisory's micro-actions and safety recommendations are consistent with the vulnerabilities and risks identified in the ground truth data.</t>
-        </is>
-      </c>
-      <c r="M10" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling characteristics. The first action addresses the risk of water damage in the unfinished basement due to heavy rainfall, acknowledging the lack of a sump pump or backwater valve, which are critical vulnerabilities. The second action effectively mitigates the risk of vehicle damage from high winds and hail, which are primary loss drivers in this scenario. The third action focuses on life safety by preventing windborne projectiles, directly addressing the hazard of 90 km/h wind gusts. All actions are practical and executable within the warning lead time, demonstrating a comprehensive approach to loss prevention.</t>
-        </is>
-      </c>
-      <c r="O10" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe thunderstorm with high winds and hail) and provides actionable steps (move valuables, secure outdoor items, stay indoors). It is well within the character limit and free of jargon. The push notification and micro-actions are also clear and actionable, providing specific instructions without using technical insurance terms. The tone is appropriately urgent, and the instructions are easy to follow, making them suitable for emergency conditions.</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm warning for your area. Secure outdoor items, move basement valuables, and park vehicles in a garage or away from trees. Do NOT climb ladders or inspect roof during storm.</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall are directly matched with the ground truth weather alert. The property details, including the unfinished basement, absence of a sump pump, and no backwater valve, are accurately reflected in the exposure analysis. The micro-actions are appropriate and based on the factual weather conditions and property vulnerabilities. There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling characteristics. The first action directly addresses the risk of windborne projectiles, which is a primary loss driver in severe thunderstorms with high wind gusts. It is tailored to the dwelling's outdoor environment and is executable within the warning lead time. The second action considers the dwelling's lack of a sump pump and backwater valve, addressing the vulnerability of the unfinished basement to water ingress from torrential downpours. This action is crucial despite the coverage, as it minimizes potential damage to personal property. The third action is well-aligned with the risk of hail and wind damage to vehicles, advising relocation to a safer area, which is a practical and effective measure. Overall, the actions are well-targeted and appropriately tailored to the specific conditions and vulnerabilities of the property.</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory reference actions. The action to secure or bring indoors loose outdoor items addresses the need to prevent projectile damage from wind gusts. The action to park vehicles in a garage or safe location covers the need to protect vehicles from hail damage. However, the agent did not include an action to close and latch all windows, exterior doors, and storm shutters, which is a critical step to prevent water infiltration and wind pressurization. The additional action to move valuable items from the basement floor is logical and relevant given the potential for water ingress due to heavy rain, and it aligns with the dwelling's lack of a sump pump or backwater valve. No illogical actions were proposed.</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the threat (severe thunderstorm) and provide specific, actionable steps to mitigate risk (securing outdoor items, moving valuables, parking vehicles safely). The instructions are free of insurance jargon and are easy to understand at a glance. The SMS complies with the character limit, maximizing impact with direct language. The micro-actions are detailed yet straightforward, ensuring homeowners know exactly what to do without confusion.</t>
+        </is>
+      </c>
+      <c r="T10" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="11" ht="135" customHeight="1">
@@ -1281,61 +1385,76 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: None cm
+Rain: 50.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 12-year-old slate roof vulnerable to high winds and hail, Crawlspace vulnerable to water intrusion from heavy rainfall, No backwater valve increases sewer backup risk
+Identified Vulnerabilities: 12-year-old slate roof susceptible to high winds and hail, Crawlspace basement with no backwater valve
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure or store all loose outdoor items (patio furniture, garbage bins, decorations) to prevent them from becoming projectiles in 90 km/h winds.
-Rationale: High winds can cause unsecured items to become dangerous projectiles, leading to property damage or injury.
-[P2] VEHICLE_PROTECTION: Park vehicles in a garage or under a sturdy cover, or at least away from trees and power lines, to protect against nickel-sized hail (2.1 cm) and potential falling debris.
-Rationale: Nickel-sized hail can cause significant damage to vehicle exteriors, and high winds increase the risk of falling branches.
-[P3] INDOOR_WATER_PROTECTION: Regularly check your crawlspace for any signs of water intrusion or accumulation due to torrential downpours (localized amounts exceeding 50 mm), even with a sump pump in place.
-Rationale: Heavy rainfall can overwhelm drainage systems, and a crawlspace is susceptible to water damage, requiring proactive monitoring.</t>
-        </is>
-      </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe thunderstorm with 90 km/h winds &amp; nickel hail. Secure outdoor items &amp; park vehicles safely. Do NOT go on roof. Stay safe!"
-(Length: 136 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and trampolines to prevent them from becoming projectiles in high winds.
+Rationale: High wind gusts of 90 km/h can turn unsecured outdoor items into dangerous projectiles, causing property damage or injury.
+[P2] VEHICLE_PROTECTION: Park all vehicles in a garage or under a covered area to protect them from potential damage by nickel-sized hail.
+Rationale: Nickel-sized hail (2.1 cm) can cause significant dents and damage to vehicle exteriors.
+[P3] INDOOR_WATER_PROTECTION: Regularly check your crawlspace for any signs of water intrusion or dampness, especially during and after heavy rainfall, as your property lacks a backwater valve.
+Rationale: Torrential downpours with localized amounts exceeding 50 mm can overwhelm drainage systems, and without a backwater valve, there's an increased risk of water entering the crawlspace despite having a sump pump.</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90 km/h winds &amp; hail. Secure outdoor items &amp; park vehicles indoors. Stay safe! #StormSafety"
+(Length: 124 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds &amp; nickel-sized hail. Secure outdoor items &amp; park vehicles safely. Monitor crawlspace. Do NOT go on roof.</t>
-        </is>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm, directly match the ground truth weather alert. The property details, such as the 12-year-old slate roof, crawlspace, and absence of a backwater valve, are accurately reflected in the advisory. There is no mention of snowfall or tornado risk, which aligns with the ground truth. The micro-actions and safety recommendations are consistent with the vulnerabilities identified in the property profile and the weather alert. No hallucinations or unverified extrapolations are present.</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and dwelling characteristics. The first action addresses the primary loss driver of windborne projectiles by securing loose outdoor items, which is crucial given the forecasted 90 km/h wind gusts. The second action protects vehicles from hail damage and falling debris, which is pertinent given the nickel-sized hail and high winds. The third action focuses on monitoring the crawlspace for water intrusion, which is appropriate given the torrential downpours and the presence of a sump pump but no backwater valve. All actions are executable within the warning lead time and consider the dwelling's structural vulnerabilities and policy coverage.</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P11" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe thunderstorm with high winds and hail) and provides clear, actionable steps (secure outdoor items, park vehicles safely, avoid going on the roof). It is well within the character limit and free of insurance jargon. The push notification complements the SMS by adding a reminder to monitor the crawlspace, which is relevant and actionable. The micro-actions are detailed yet straightforward, providing specific instructions without using technical jargon, ensuring homeowners can quickly understand and act upon them.</t>
-        </is>
-      </c>
-      <c r="Q11" s="21" t="n">
+Body: Severe thunderstorm warning for your area. Secure outdoor items, park vehicles indoors, and monitor crawlspace for water. Winds up to 90 km/h, nickel-sized hail, and heavy rain expected.</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm, match the weather alert details. The property details, such as the 12-year-old slate roof, crawlspace basement, and absence of a backwater valve, are accurately reflected in the advisory. The micro-actions and rationale are consistent with the vulnerabilities and weather conditions described. There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's characteristics. The first action addresses the primary loss driver of windborne projectiles by securing loose outdoor items, which is crucial given the forecasted 90 km/h wind gusts. The second action protects vehicles from hail damage, which is a significant risk with nickel-sized hail. The third action focuses on monitoring the crawlspace for water intrusion, which is pertinent due to the torrential downpours and the absence of a backwater valve, despite having a sump pump. All actions are executable within the warning lead time and directly target the dwelling's vulnerabilities and policy coverage gaps.</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover all mandatory reference actions. The action to "Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and trampolines" semantically matches the requirement to secure or store patio furniture and loose items to prevent projectile damage. The action to "Park all vehicles in a garage or under a covered area" aligns with the need to move vehicles into a protective shelter to avoid hail damage. Additionally, the agent suggests checking the crawlspace for water intrusion, which is a logical and practical action given the torrential downpours and the lack of a backwater valve, addressing potential water damage risk. No illogical actions were proposed, and all actions are grounded in the property context and weather alert details.</t>
+        </is>
+      </c>
+      <c r="R11" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without causing panic. It immediately informs the homeowner of the threat (severe thunderstorm with high winds and hail) and provides actionable steps (secure outdoor items, park vehicles indoors). It is well within the character limit and free of jargon. The push notification expands on the SMS with additional details and instructions, maintaining clarity and urgency. The micro-actions are specific and actionable, avoiding any insurance jargon, and clearly instruct the homeowner on what to do to mitigate damage.</t>
+        </is>
+      </c>
+      <c r="T11" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1382,62 +1501,76 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
+          <t>• Clear balcony of all loose furniture, planters, and lightweight items to prevent windborne hazards in 90 km/h gusts
+• Close and tightly latch all balcony doors and windows to prevent water ingress and wind pressurization during the severe storm</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
 Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: 16-year-old tar_and_gravel roof vulnerable to wind and hail, Highrise condo susceptible to wind-driven rain and water ingress through windows/balcony doors
-Identified Gaps: Overland Water Endorsement missing (surface overland flood runoff is UNINSURED)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Ensure all windows and balcony doors are securely closed to prevent water ingress from torrential downpours and wind-driven rain.
-Rationale: High winds and 50 mm of rain can lead to significant water intrusion if openings are not sealed.
-[P2] VEHICLE_PROTECTION: If a vehicle is parked outdoors, move it to a covered or sheltered area to protect against hail and wind damage.
-Rationale: 90 km/h wind gusts and nickel-sized hail pose a high risk of damage to exposed vehicles.
-[P3] LIFE_SAFETY: Stay indoors and away from windows during the storm due to high winds and hail.
-Rationale: High winds and hail can cause flying debris and window breakage, posing a safety risk.</t>
+Identified Vulnerabilities: Older tar_and_gravel roof (16 years old) susceptible to wind and hail damage, High-rise condo balconies exposed to high winds
+Identified Gaps: Overland Water Endorsement: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe storm with 90km/h winds &amp; hail. Close all windows/balcony doors. Move vehicles to shelter. Stay indoors. #StormSafety"
-(Length: 132 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek indoor shelter immediately and stay away from windows and doors.
+Rationale: Severe thunderstorms with 90 km/h wind gusts and hail pose a direct threat to personal safety.
+[P2] VEHICLE_PROTECTION: Secure all loose items on balconies, patios, or near windows to prevent them from becoming dangerous projectiles in high winds.
+Rationale: High winds (90 km/h) can turn unsecured outdoor items into projectiles, causing property damage or injury.
+[P3] INDOOR_WATER_PROTECTION: Move any valuable items from ground-level areas that could be exposed to surface runoff due to torrential downpours, as overland water is not covered by your policy.
+Rationale: Torrential downpours (exceeding 50 mm) combined with a lack of overland water coverage create a significant risk of uninsured property damage from surface runoff.</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90 km/h winds &amp; hail. Seek indoor shelter. Secure balcony items. Overland water uninsured."
+(Length: 123 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds, nickel-sized hail, and heavy rain. Close all windows/balcony doors. Move vehicles to shelter. Stay indoors and away from windows.</t>
-        </is>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall, directly match the ground truth weather alert. The property details, such as the 16-year-old tar and gravel roof and the highrise condo dwelling type, are accurately reflected in the advisory. The mention of the missing Overland Water Endorsement is also correct according to the policy data. There are no fabricated numbers or unverified structural features mentioned in the advisory.</t>
-        </is>
-      </c>
-      <c r="M12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of a severe thunderstorm with high winds, hail, and heavy rain. The first action addresses the risk of water ingress through windows and balcony doors, which is crucial given the torrential downpours and the dwelling's slab-on-grade construction, which lacks a basement but still faces water intrusion risks. The second action to protect vehicles from hail and wind damage is pertinent, as vehicles are vulnerable to the forecasted nickel-sized hail and 90 km/h wind gusts. The third action focuses on life safety by advising occupants to stay indoors and away from windows, which is critical given the potential for flying debris and window breakage. These actions are executable within the warning lead time and directly target the primary loss drivers of the storm, while also considering the dwelling's structural features and policy gaps, such as the lack of overland water coverage.</t>
-        </is>
-      </c>
-      <c r="O12" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe storm with 90km/h winds and hail) and provides clear, actionable steps (close windows, move vehicles, stay indoors). It is well within the character limit and free of insurance jargon. The push notification complements the SMS by providing additional details (nickel-sized hail, heavy rain) while maintaining clarity and urgency. The micro-actions are straightforward, avoiding technical language, and clearly instruct the homeowner on what to do first, ensuring safety and property protection.</t>
-        </is>
-      </c>
-      <c r="Q12" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm with 90 km/h winds &amp; hail. Seek indoor shelter, secure balcony items, and protect valuables from potential overland water runoff.</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm, directly match the ground truth weather alert. The property details, such as the dwelling type being a highrise condo, the roof type being tar and gravel, and the roof age of 16 years, are accurately reflected in the advisory. The advisory correctly notes the lack of overland water endorsement, aligning with the ground truth policy details. No fabricated numbers or non-existent property features are present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's characteristics. The life safety action to seek indoor shelter and avoid windows directly addresses the threat posed by high winds and hail, which is crucial for personal safety in a highrise condo. The vehicle protection action to secure loose items on balconies is pertinent given the high wind speeds, which could turn these items into projectiles, a common risk in highrise settings. The indoor water protection action is particularly well-tailored, as it addresses the uninsured gap for overland water by advising the relocation of valuables from ground-level areas, mitigating potential damage from torrential downpours. Overall, these actions are executable within the warning lead time and effectively target the primary loss drivers of the severe thunderstorm.</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions include securing loose items on balconies, which semantically covers the mandatory action of clearing the balcony of loose items to prevent windborne hazards. However, the agent did not explicitly mention closing and latching balcony doors and windows, which is a critical action to prevent water ingress and wind pressurization during the storm. The additional action of moving valuable items from ground-level areas is logical given the torrential downpours mentioned in the alert, and it is relevant to the risk of surface runoff. No illogical actions were proposed, but the omission of the door and window securing action results in a score of 4.</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise and effectively communicates the urgency of the situation, specifying the threat (severe thunderstorm with high winds and hail) and immediate actions (seek shelter, secure items). However, the mention of 'Overland water uninsured' introduces a slight element of insurance jargon that could be confusing in an emergency context. The push notification and micro-actions are clear and actionable, though the push notification could be slightly more concise. Overall, the instructions are clear, but the reference to insurance coverage could be rephrased to maintain focus on immediate safety actions.</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="13" ht="135" customHeight="1">
@@ -1483,62 +1616,79 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
 Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: 20-year-old asphalt shingle roof vulnerable to high winds and hail, Finished basement vulnerable to heavy rainfall and potential sewer backup, No backwater valve increases sewer backup risk
-Identified Gaps: Sewer Backup Endorsement: Basement sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure or store all outdoor furniture, decorations, and garbage bins to prevent them from becoming projectiles in 90 km/h wind gusts.
-Rationale: High winds can turn unsecured outdoor items into dangerous projectiles, causing property damage or injury.
-[P2] INDOOR_WATER_PROTECTION: Move valuable items from the basement floor to higher ground to mitigate potential water damage from torrential downpours, especially since sewer backup is uninsured.
-Rationale: Heavy rainfall and the lack of sewer backup coverage increase the risk of water damage to basement contents.
-[P3] VEHICLE_PROTECTION: Park vehicles in a garage or covered area to protect them from potential damage from nickel-sized hail (2.1 cm) and flying debris.
-Rationale: Hail and wind-borne debris can cause significant damage to vehicles if left exposed.</t>
+Identified Vulnerabilities: 20-year-old asphalt shingle roof vulnerable to wind and hail, Finished basement vulnerable to water damage, No backwater valve increasing sewer backup risk
+Identified Gaps: Sewer Backup Endorsement is missing, basement sewer backup damage is uninsured</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe thunderstorm with 90 km/h winds &amp; hail. Secure outdoor items immediately. Stay indoors. Info: +1-613-555-1005"
-(Length: 124 / 160 chars)</t>
+          <t>[P1] OUTDOOR_PROTECTION: Secure or bring indoors all loose outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming projectiles in 90 km/h winds.
+Rationale: High wind gusts can turn unsecured items into dangerous projectiles, causing property damage or injury.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or covered area to protect them from potential damage by nickel-sized hail (2.1 cm).
+Rationale: Hail of this size can cause significant dents and damage to vehicle exteriors.
+[P3] INDOOR_WATER_PROTECTION: Elevate valuable items in the finished basement to protect them from potential water damage due to torrential downpours and the uninsured sewer backup risk.
+Rationale: Elevating valuables mitigates damage from any water intrusion, especially given the finished basement and the lack of sewer backup coverage.</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe storm with 90 km/h winds &amp; hail. Secure outdoor items, move vehicles to cover. Stay safe indoors!"
+(Length: 112 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds and nickel-sized hail. Secure outdoor items and protect basement valuables. Stay safe indoors.</t>
-        </is>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the 20-year-old asphalt shingle roof, finished basement, lack of backwater valve, and absence of sewer backup endorsement, are accurately reflected in the advisory. There is no evidence of hallucination or unverified speculation in the advisory.</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling vulnerabilities. The first action directly addresses the risk of windborne projectiles, which is a primary loss driver in severe thunderstorms with 90 km/h wind gusts. The second action is well-tailored to the dwelling's specific vulnerability, considering the finished basement and the uninsured sewer backup gap, by suggesting the relocation of valuables to mitigate potential water damage from torrential downpours. The third action effectively addresses the risk of hail damage to vehicles, which is pertinent given the forecasted nickel-sized hail. All actions are executable within the warning lead time and avoid any hazardous outdoor work during the storm.</t>
-        </is>
-      </c>
-      <c r="O13" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P13" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (severe thunderstorm with high winds and hail) and what to do first (secure outdoor items and stay indoors). It avoids any insurance jargon and complies with the character limit. The push notification is similarly clear, providing additional context without overwhelming the user. The micro-actions are direct and actionable, with clear instructions on securing outdoor items, protecting basement valuables, and parking vehicles safely. There is no use of insurance jargon, and the instructions are straightforward and easy to follow in an emergency.</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm with 90 km/h winds, nickel-sized hail, and heavy rain. Secure outdoor items, move vehicles to cover, and elevate basement valuables. Stay safe indoors.</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the 20-year-old asphalt shingle roof, finished basement, and absence of a backwater valve, are accurately reflected in the exposure analysis. The advisory correctly notes the lack of sewer backup endorsement, aligning with the policy details. No fabricated or unverified information is present, ensuring a score of 5 for full faithfulness.</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling vulnerabilities. The first action directly addresses the risk of windborne projectiles by securing outdoor items, which is crucial given the forecasted 90 km/h wind gusts. The second action protects vehicles from hail damage, which is a primary concern with nickel-sized hail. The third action is particularly well-tailored, as it considers the finished basement and the uninsured sewer backup risk, advising the elevation of valuables to mitigate potential water damage from torrential downpours. All actions are practical and executable within the warning lead time, effectively addressing the primary loss drivers of the severe thunderstorm.</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two out of the three mandatory reference actions. The action to secure or bring indoors loose outdoor items addresses the need to prevent projectile damage from high winds. The action to move vehicles into a garage or covered area addresses the need to protect vehicles from hail damage. However, the agent did not include an action to close and latch all windows, exterior doors, and storm shutters, which is a mandatory action to prevent water infiltration and wind pressurization. The additional action to elevate valuable items in the basement is logical and relevant given the torrential downpours and the finished basement context, and it does not detract from the overall assessment.</t>
+        </is>
+      </c>
+      <c r="R13" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe storm with 90 km/h winds and hail) and provides clear, actionable steps (secure outdoor items, move vehicles to cover, stay indoors). It is well within the character limit and free of jargon.
+The push notification is slightly more detailed but maintains clarity and urgency. It expands on the SMS by including additional details about the storm (nickel-sized hail, heavy rain) and adds an extra action (elevate basement valuables). The language is straightforward and free of insurance jargon.
+The micro-actions are clear and provide specific instructions without using technical insurance terms. They are detailed yet easy to understand, ensuring homeowners know exactly what to do to mitigate damage.</t>
+        </is>
+      </c>
+      <c r="T13" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="14" ht="135" customHeight="1">
@@ -1584,61 +1734,76 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
 Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: 24-year-old metal roof susceptible to wind and hail damage
+Identified Vulnerabilities: Metal roof (24 years old) susceptible to wind and hail damage, Unfinished basement with no sump pump or backwater valve, increasing risk of water damage from heavy rainfall
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Immediately seek shelter in the lowest level of your home (unfinished basement) or an interior room away from windows and doors to protect against 90 km/h winds and nickel-sized hail.
-Rationale: Strong winds and hail pose a significant risk of injury from flying debris or broken glass; seeking interior shelter is crucial for personal safety.
-[P2] VEHICLE_PROTECTION: If safe to do so immediately, park vehicles inside a garage to protect them from potential damage caused by 90 km/h winds and nickel-sized hail.
-Rationale: Vehicles are highly susceptible to damage from severe wind gusts and hail, leading to costly repairs.
-[P3] INDOOR_WATER_PROTECTION: Monitor for any signs of water ingress around windows, doors, and in the unfinished basement due to 50 mm of torrential rainfall, and be prepared to use towels or barriers if necessary.
-Rationale: Heavy rainfall can overwhelm drainage systems or find entry points, potentially causing interior water damage even with policy coverage.</t>
-        </is>
-      </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe T-storm warning for HOM-1006. Seek indoor shelter immediately. Winds 90km/h, nickel hail, 50mm rain. Stay safe!"
-(Length: 126 / 160 chars)</t>
+          <t>[P1] VEHICLE_PROTECTION: Move all vehicles into a garage or covered parking to protect them from potential hail and wind damage.
+Rationale: 90 km/h wind gusts and nickel-sized hail pose a significant risk of damage to vehicles.
+[P2] INDOOR_SHELTER: Secure all loose outdoor items such as patio furniture, garbage bins, and decorations, or bring them indoors to prevent them from becoming dangerous projectiles in high winds.
+Rationale: High wind gusts of 90 km/h can turn unsecured outdoor items into projectiles, causing property damage or injury.
+[P3] INDOOR_WATER_PROTECTION: Ensure all windows and doors are securely closed and locked to prevent water ingress from torrential downpours. Monitor the unfinished basement for any signs of water intrusion.
+Rationale: 50 mm of rainfall combined with an unfinished basement and no sump pump or backwater valve increases the risk of water damage.</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90km/h winds &amp; hail. Move vehicles to cover &amp; secure outdoor items. Stay safe!"
+(Length: 111 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm warning for your property. Seek immediate indoor shelter. Park vehicles in a garage. Monitor for water ingress. Expect 90 km/h winds, nickel-sized hail, and 50 mm of rain.</t>
-        </is>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall, directly match the details in the weather alert. The property details, such as the 24-year-old metal roof and the unfinished basement, are accurately reflected in the advisory. There are no fabricated numbers or unverified structural features mentioned. The advisory's actions and rationale are consistent with the provided data, ensuring a faithful representation of the situation.</t>
-        </is>
-      </c>
-      <c r="M14" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and dwelling characteristics. The life-safety action to seek shelter in the unfinished basement or an interior room directly addresses the risk of injury from high winds and hail, which is the primary threat in a severe thunderstorm. The vehicle protection action is appropriate, as it aims to prevent damage from hail and wind, which are significant loss drivers in this scenario. The indoor water protection action is also relevant, as it addresses the potential for water ingress due to heavy rainfall, which is a concern given the lack of a sump pump or backwater valve, despite policy coverage for overland water. Overall, these actions are executable within the warning lead time and effectively mitigate the specific risks posed by the severe thunderstorm.</t>
-        </is>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P14" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the severe thunderstorm threat and the primary action to take (seek indoor shelter). It avoids any insurance jargon and fits well within the character limit. The push notification effectively expands on the SMS, providing additional actions like parking vehicles in a garage and monitoring for water ingress, all in clear, direct language. The micro-actions are detailed yet straightforward, guiding the homeowner on specific protective measures without overwhelming them with technical terms or unnecessary complexity. Overall, the communications are well-structured for emergency clarity and action.</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="n">
+Body: Severe thunderstorm warning for your area. Move vehicles to covered parking and secure all loose outdoor items immediately. Monitor basement for water.</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall are directly taken from the weather alert. The property details, including the metal roof aged 24 years and the unfinished basement without a sump pump or backwater valve, match the property data. There are no fabricated or hallucinated claims in the advisory, and all recommendations are consistent with the risks outlined in the ground truth.</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling characteristics. The vehicle protection action directly addresses the risk of hail and wind damage, which is a primary concern given the forecasted conditions. The indoor shelter action effectively mitigates the risk of windborne projectiles, a significant threat during high wind events. The indoor water protection action is well-tailored to the dwelling's vulnerabilities, particularly the unfinished basement and lack of a sump pump or backwater valve, addressing the risk of water ingress from torrential downpours. All actions are executable within the warning lead time and avoid hazardous outdoor work during severe weather.</t>
+        </is>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover all mandatory reference actions. The action to move vehicles into a garage or covered parking addresses the need to protect vehicles from hail damage. Securing or storing patio furniture and other loose outdoor items is covered by the action to secure all loose outdoor items to prevent them from becoming projectiles. The action to ensure all windows and doors are securely closed and locked addresses the need to prevent water infiltration and wind pressurization. Additionally, the agent logically suggests monitoring the unfinished basement for water intrusion, which is a sound and practical action given the torrential downpours and the lack of a sump pump or backwater valve. No illogical actions were proposed.</t>
+        </is>
+      </c>
+      <c r="R14" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent, effectively communicating the immediate threat (severe thunderstorm with high winds and hail) and the first actions to take (move vehicles and secure items). It is well within the character limit and free of jargon. The push notification is similarly clear, with a direct title and body that expands slightly on the SMS by adding the action of monitoring the basement for water, which is relevant and actionable. The micro-actions are detailed yet straightforward, avoiding any insurance jargon and providing clear, step-by-step instructions on what to do, making them easy to follow even in a stressful situation.</t>
+        </is>
+      </c>
+      <c r="T14" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1685,62 +1850,77 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>Identified Event: Severe Thunderstorm Warning
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: None cm
+Rain: 50.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Roof susceptible to high winds and hail despite being relatively new, Potential for surface water accumulation due to torrential downpours
+Identified Vulnerabilities: Potential for wind and hail damage to roof (despite being new slate), Crawlspace basement susceptible to overland flooding
 Identified Gaps: Overland Water Endorsement: UNINSURED for surface overland flood runoff</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming dangerous projectiles in 90 km/h winds.
-Rationale: High wind gusts can turn unsecured outdoor items into projectiles, causing property damage or injury.
-[P2] VEHICLE_PROTECTION: Park vehicles in a garage or under a covered area to protect them from potential hail damage.
-Rationale: Nickel-sized hail can cause significant damage to vehicle exteriors.
-[P3] INDOOR_WATER_PROTECTION: Monitor for any signs of water ingress, especially in the crawlspace, given the heavy rainfall and the critical uninsured overland water risk.
-Rationale: Torrential downpours can lead to surface water runoff and potential water ingress, which is not covered by your policy.</t>
-        </is>
-      </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe T-storm warning for HOM-1007. Secure outdoor items &amp; park vehicles. Monitor for water ingress. Overland flood not covered. Stay safe!"
-(Length: 148 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Ensure downspouts are extended away from the foundation and clear any nearby storm drains to prevent overland flooding, as you are uninsured for this peril.
+Rationale: Heavy rainfall (50 mm) combined with a critical policy gap for overland water coverage increases the risk of uninsured water damage to your property.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or carport, or cover them with a protective tarp, to shield against 90 km/h wind gusts and nickel-sized hail.
+Rationale: High winds and hail can cause significant damage to vehicles, leading to costly repairs.
+[P3] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming projectiles in 90 km/h winds.
+Rationale: Strong wind gusts can turn unsecured objects into dangerous projectiles, causing property damage or injury.</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90km/h winds, hail, 50mm rain. Extend downspouts &amp; clear drains. Overland flood is uninsured. Secure outdoor items. Stay safe!"
+(Length: 159 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds, nickel-sized hail, and heavy rain. Secure outdoor items, park vehicles, and monitor for water ingress. Overland flood is not covered.</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the townhouse dwelling type, slate roof, and presence of a sump pump, are accurately reflected. The advisory correctly identifies the lack of overland water endorsement, aligning with the policy details. No fabricated numbers or unverified features are present, ensuring complete faithfulness to the ground truth.</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's characteristics. The first action addresses the primary loss driver of windborne projectiles by securing loose outdoor items, which is crucial given the forecasted 90 km/h wind gusts. The second action protects vehicles from hail damage, which is a significant risk with nickel-sized hail. The third action is particularly well-tailored to the dwelling's uninsured overland water risk, advising monitoring for water ingress in the crawlspace during torrential downpours. All actions are executable within the warning lead time and avoid hazardous outdoor work during the storm.</t>
-        </is>
-      </c>
-      <c r="O15" s="21" t="n">
+Body: Severe thunderstorm warning for your area. Extend downspouts &amp; clear drains to prevent uninsured overland flood damage. Secure outdoor items and protect vehicles.</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall, match the weather alert exactly. The property details, such as the townhouse dwelling type, slate roof, crawlspace basement, and lack of overland water endorsement, are accurately reflected in the advisory. There is no fabrication or unverified speculation present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and property vulnerabilities. The first action directly addresses the risk of overland water damage, which is a critical uninsured gap for this property, by ensuring downspouts are extended and storm drains are clear. This is crucial given the forecasted torrential downpours. The second action protects vehicles from hail and wind damage, which are primary loss drivers in this severe thunderstorm scenario. The third action focuses on life safety by securing loose items that could become windborne projectiles, directly addressing the 90 km/h wind gusts threat. All actions are practical and executable within the warning lead time, making them highly relevant and well-tailored to the dwelling's specific circumstances.</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and mostly clear, effectively communicating the threat of a severe thunderstorm and immediate actions to take. It avoids insurance jargon, though the mention of 'Overland flood not covered' could be slightly confusing without context. The push notification is clear and provides detailed information about the storm, but the mention of 'overland flood is not covered' could be misinterpreted as insurance jargon. The micro-actions are clear and actionable, though slightly wordy, which could be challenging in an emergency. Overall, the messages are effective but could be improved by simplifying the language around insurance coverage.</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="n">
-        <v>4.67</v>
+      <c r="Q15" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory reference actions. The action to move vehicles into a garage or carport to protect against hail and wind damage is covered. Additionally, the action to secure or bring indoors loose outdoor items to prevent them from becoming projectiles in high winds is also covered. However, the agent did not include an action to close and latch all windows, exterior doors, and storm shutters, which is a mandatory action to prevent water infiltration and wind pressurization. The additional action regarding ensuring downspouts are extended and clearing storm drains is logical and relevant given the torrential downpours mentioned in the alert, and it addresses a potential risk of overland flooding, which is a reasonable concern for the property type. Therefore, the score is 4 due to the omission of one mandatory action.</t>
+        </is>
+      </c>
+      <c r="R15" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, effectively communicating the threat and immediate actions without causing panic. It avoids insurance jargon, though the mention of 'uninsured' could be slightly alarming. The push notification is clear but slightly wordy, especially with the phrase 'uninsured overland flood damage,' which could be simplified. The micro-actions are detailed and clear, though the first instruction could be more concise by omitting the insurance status, which is less critical in an emergency. Overall, the communications are effective but could be slightly refined for brevity and focus on immediate actions.</t>
+        </is>
+      </c>
+      <c r="T15" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="16" ht="135" customHeight="1">
@@ -1786,63 +1966,75 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
+          <t>• Clear balcony of all loose furniture, planters, and lightweight items to prevent windborne hazards in 90 km/h gusts
+• Close and tightly latch all balcony doors and windows to prevent water ingress and wind pressurization during the severe storm</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: 0.0 cm
+Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Highrise condo with potential for wind and hail damage to exterior elements (balconies, windows), Tar and gravel roof (7 years old) susceptible to high winds and hail, Slab-on-grade basement, but heavy rain can still cause issues with windows/balcony doors if not properly sealed
-Identified Gaps: Wind/Hail deductible of $5,000.00 is higher than base deductible</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure all loose items on balconies, patios, and near windows to prevent them from becoming projectiles in high winds.
-Rationale: 90 km/h wind gusts can turn unsecured items into dangerous projectiles, causing property damage or injury.
-[P2] VEHICLE_PROTECTION: Park vehicles in a garage or covered area to protect them from potential damage by nickel-sized hail.
-Rationale: Nickel-sized hail (2.1 cm) can cause significant dents and damage to vehicle exteriors.
-[P3] INDOOR_WATER_PROTECTION: Ensure all windows and balcony doors are fully closed and locked to prevent water intrusion from torrential downpours and wind-driven rain.
-Rationale: 50 mm of rain combined with high winds can lead to water infiltration if openings are not properly sealed.</t>
+Identified Vulnerabilities: Highrise condo with 7-year-old tar_and_gravel roof (potential for wind/hail damage to common areas/balconies), Slab-on-grade basement (potential for drainage issues with heavy rain)
+Identified Gaps: None</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe thunderstorm with 90km/h winds &amp; hail. Secure balcony items, park vehicles under cover, close windows. Stay safe!"
-(Length: 128 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Secure any loose items on balconies or patios to prevent them from becoming projectiles in high winds.
+Rationale: High winds can cause unsecured items to become dangerous projectiles, damaging property or causing injury.
+[P2] INDOOR_WATER_PROTECTION: Ensure all windows and balcony doors are securely closed and locked to prevent water intrusion from torrential downpours and wind-driven rain.
+Rationale: Heavy rainfall and strong winds can force water into the dwelling through unsealed openings, leading to interior water damage.
+[P3] VEHICLE_PROTECTION: Move vehicles to an underground or covered parking area if available, to protect them from hail damage.
+Rationale: Nickel-sized hail can cause significant damage to vehicles, and covered parking offers protection.</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90 km/h winds and hail. Secure balcony items and close windows. Move vehicles to covered parking if possible. Stay safe!"
+(Length: 153 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90 km/h winds and nickel-sized hail. Secure loose items on balconies, park vehicles under cover, and close all windows and balcony doors. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall are directly matched with the ground truth weather alert. The property details, including the dwelling type (highrise condo), roof type (tar and gravel), roof age (7 years), and basement type (slab-on-grade), are accurately reflected in the advisory. There is no mention of a sump pump or backwater valve, which aligns with the ground truth indicating their absence. The advisory's micro-actions and exposure analysis are consistent with the potential impacts of the specified weather conditions on the described property features. No hallucinations or unverified claims are present.</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of a severe thunderstorm with high winds, hail, and heavy rain. The first action addresses the primary loss driver of windborne projectiles by securing loose items on balconies, which is crucial for a highrise condo where such items can become dangerous projectiles. The second action protects vehicles from hail damage, which is a significant risk given the forecasted nickel-sized hail. The third action focuses on preventing water intrusion through windows and doors, which is pertinent given the torrential downpours and the condo's slab-on-grade construction, minimizing the risk of water damage. All actions are executable within the warning lead time and align with the dwelling's structural features and policy coverage.</t>
-        </is>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe thunderstorm with high winds and hail) and provides specific, actionable steps (secure balcony items, park vehicles under cover, close windows). The message is well within the character limit and free of insurance jargon, making it easy to understand quickly during an emergency.
-The push notification maintains the same clarity and urgency, with a slightly more detailed body that remains free of jargon and provides clear instructions. The title effectively conveys urgency and the need for action.
-The micro-actions are detailed yet clear, providing specific instructions without using technical language. They effectively guide the homeowner on what to do to mitigate damage, maintaining clarity and urgency throughout.</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="n">
+Body: Severe thunderstorm with 90 km/h winds and hail. Secure balcony items, close windows, and move vehicles to covered parking. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the highrise condo dwelling type, 7-year-old tar and gravel roof, and slab-on-grade basement, are accurately reflected in the advisory. There are no fabricated or hallucinated claims about the property or the weather event. The advisory does not mention any features not present in the ground truth, such as a sump pump or backwater valve, and correctly identifies the absence of a tornado risk and snowfall. All actions and recommendations are consistent with the provided data, ensuring a score of 5 for full faithfulness.</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of a severe thunderstorm with high winds, hail, and heavy rain. The actions directly address the primary loss drivers: windborne projectiles, water intrusion, and hail damage. The first action targets the risk of windborne projectiles by securing loose items on balconies, which is crucial for a highrise condo. The second action focuses on preventing water intrusion by ensuring windows and doors are closed, which is appropriate given the torrential downpours. The third action protects vehicles from hail damage by suggesting relocation to covered parking, which is a practical and effective measure. All actions are executable within the warning lead time and consider the dwelling's structural features and policy coverage, such as the lack of a basement and existing overland water coverage.</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover the mandatory reference actions. The action to "Secure any loose items on balconies or patios" semantically matches the requirement to clear the balcony of loose items to prevent windborne hazards. Similarly, the action to "Ensure all windows and balcony doors are securely closed and locked" aligns with the requirement to close and latch all balcony doors and windows to prevent water ingress and wind pressurization. Additionally, the agent suggests moving vehicles to a covered parking area to protect against hail damage, which is a logical and practical action given the presence of nickel-sized hail in the weather alert. There are no illogical actions proposed, and all actions are grounded in the context of the dwelling and the weather alert.</t>
+        </is>
+      </c>
+      <c r="R16" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the threat (severe thunderstorm with high winds and hail) and provide specific, actionable steps to mitigate risk (secure balcony items, close windows, move vehicles). The language is straightforward and free of insurance jargon, making it easy to understand quickly in an emergency. The SMS complies with the character limit, ensuring it is suitable for quick reading. The micro-actions are detailed yet clear, providing additional guidance without overwhelming the reader.</t>
+        </is>
+      </c>
+      <c r="T16" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1889,62 +2081,77 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: None cm
+Rain: 50.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Asphalt shingle roof (11 years old) vulnerable to high winds and hail, Finished basement vulnerable to water damage, No backwater valve increases sewer backup risk
-Identified Gaps: Sewer Backup Endorsement: UNINSURED</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items from the basement floor to higher ground to protect against potential sewer backup.
-Rationale: Heavy rainfall (50 mm) combined with a finished basement and no sewer backup coverage creates a high risk of water damage to basement contents.
-[P2] VEHICLE_PROTECTION: Park vehicles in a garage or away from trees and structures that could be damaged by high winds and hail.
-Rationale: 90 km/h wind gusts and nickel-sized hail pose a significant risk of damage to vehicles if left exposed.
-[P3] INDOOR_SHELTER: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and trampolines.
-Rationale: High winds (90 km/h) can turn unsecured outdoor items into dangerous projectiles, causing property damage or injury.</t>
+Identified Vulnerabilities: 11-year-old asphalt shingle roof vulnerable to high winds and hail, Finished basement vulnerable to water damage, No backwater valve increases sewer backup risk
+Identified Gaps: Sewer Backup Endorsement: Basement sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe thunderstorm with 90 km/h winds, hail, and 50mm rain. Move basement valuables, park cars safely. Stay indoors. #HOM1009"
-(Length: 134 / 160 chars)</t>
+          <t>[P1] VEHICLE_PROTECTION: Move vehicles to covered parking or a garage to protect against hail and wind-borne debris.
+Rationale: High winds and nickel-sized hail pose a significant risk of damage to vehicles.
+[P2] INDOOR_WATER_PROTECTION: Ensure all basement windows and doors are securely closed and sealed to prevent water ingress from torrential downpours.
+Rationale: Torrential downpours with localized amounts exceeding 50 mm can lead to basement flooding if entry points are not secured.
+[P3] INDOOR_WATER_PROTECTION: Elevate valuable items in the basement to minimize potential water damage, especially given the lack of sewer backup coverage.
+Rationale: With a finished basement and no sewer backup endorsement, there is a critical financial gap for potential sewer backup damage from heavy rainfall.</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90 km/h winds &amp; hail. Move vehicles to shelter. Secure basement. Do NOT climb ladders. Stay safe!"
+(Length: 130 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm warning for your area. Protect your basement from potential flooding and secure outdoor items. Park vehicles safely.</t>
-        </is>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall are directly matched with the alert text. The property details, including the asphalt shingle roof age (11 years), finished basement, and lack of a backwater valve, are accurately reflected in the exposure analysis. The advisory correctly identifies the absence of sewer backup endorsement as a coverage gap. All micro-actions are logically derived from the factual data provided, with no hallucinated or fabricated information. Therefore, the advisory is fully faithful to the ground truth.</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling vulnerabilities. The first action directly addresses the risk of basement flooding due to heavy rainfall and the lack of sewer backup coverage, which is a critical gap given the finished basement. The second action is well-aligned with the threat of wind and hail damage to vehicles, suggesting practical measures to mitigate this risk. The third action effectively targets the risk of windborne projectiles, which is a primary loss driver in severe thunderstorms with high winds. All actions are executable within the warning lead time and avoid hazardous outdoor activities during the storm, adhering to mandatory life-safety requirements.</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P17" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without causing panic. It immediately informs the homeowner of the threat (severe thunderstorm with specific details) and provides actionable steps (move valuables, park cars safely, stay indoors). It is well within the character limit and free of jargon. The push notification complements the SMS by reiterating the urgency and providing additional context on securing outdoor items. The micro-actions are clear, specific, and free of technical language, making them easy to follow in an emergency.</t>
-        </is>
-      </c>
-      <c r="Q17" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm with 90 km/h winds &amp; hail. Move vehicles to shelter. Secure basement windows/doors. Elevate basement valuables. Do NOT climb ladders.</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the 11-year-old asphalt shingle roof, finished basement, and lack of a backwater valve, are accurately reflected in the exposure analysis. The advisory correctly identifies the absence of sewer backup endorsement as a coverage gap. All claims are consistent with the ground truth, with no fabricated or unverified information.</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling vulnerabilities. The first action addresses the risk of hail and wind-borne debris to vehicles, which is a primary concern during a severe thunderstorm with high winds and hail. The second action focuses on securing basement windows and doors, directly targeting the risk of water ingress from torrential downpours, which is crucial given the finished basement. The third action is particularly well-tailored, as it addresses the critical policy gap of uninsured sewer backup by recommending the elevation of valuables in the basement, thus mitigating potential financial loss. All actions are executable within the warning lead time and avoid any hazardous outdoor activities during the storm.</t>
+        </is>
+      </c>
+      <c r="P17" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="20" t="inlineStr">
+        <is>
+          <t>The agent successfully covered the mandatory action of moving vehicles to a covered area to protect against hail damage. However, it completely omitted the actions related to securing outdoor items to prevent projectile damage and closing windows and doors to prevent water infiltration and wind pressurization. The additional actions proposed by the agent, such as securing basement windows and elevating items in the basement, are logical and relevant given the torrential downpours mentioned in the alert. However, the omission of two mandatory actions results in a moderate coverage score.</t>
+        </is>
+      </c>
+      <c r="R17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (severe thunderstorm with high winds and hail) and provides clear, actionable steps (move vehicles, secure basement, avoid climbing ladders). It is well within the character limit and free of jargon. The push notification complements the SMS by providing additional details without overwhelming the user. The micro-actions are clear and actionable, avoiding insurance jargon and focusing on practical steps to mitigate damage.</t>
+        </is>
+      </c>
+      <c r="T17" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="18" ht="135" customHeight="1">
@@ -1990,62 +2197,78 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
+          <t>• Move vehicles into a garage, carport, or protective shelter to avoid hail damage from nickel-sized hail
+• Secure or store patio furniture, garbage bins, and loose outdoor items to prevent projectile damage in 90 km/h wind gusts
+• Close and latch all windows, exterior doors, and storm shutters tightly to prevent water infiltration and wind pressurization</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: severe thunderstorm warning in effect
 Wind Gust: 90 km/h | Hail: nickel-sized (2.1 cm)
-Rain: 50.0 mm | Snow: 0.0 cm
+Rain: 50.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Metal roof (15 years old) susceptible to wind and hail damage, Unfinished basement at risk of water ingress from torrential downpours
-Identified Gaps: Overland Water Endorsement: UNINSURED for surface overland flood runoff</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>[P1] VEHICLE_PROTECTION: Move all vehicles into a garage or covered area immediately to protect them from hail and strong winds.
-Rationale: Nickel-sized hail and 90 km/h wind gusts can cause significant damage to vehicles. This action should be completed from a safe, sheltered position.
-[P2] INDOOR_WATER_PROTECTION: In your unfinished basement, move any valuables, electronics, or items susceptible to water damage off the floor.
-Rationale: Torrential downpours (50mm+) combined with a critical lack of overland water coverage increases the risk of uninsured water damage to your property, especially in an unfinished basement.
-[P3] INDOOR_SHELTER: Ensure all windows and doors are securely closed and locked to prevent wind-driven rain and debris from entering your home.
-Rationale: 90 km/h wind gusts can force rain and debris through unsecured openings, leading to interior damage.</t>
+Identified Vulnerabilities: Metal roof (15 years old) susceptible to high winds and hail, Unfinished basement susceptible to water ingress from heavy rainfall
+Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Severe storm with 90km/h winds &amp; hail. Move vehicles to garage, secure windows/doors, and clear basement floor. Stay safe indoors!"
-(Length: 138 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Seek shelter in the lowest level of the home, away from windows and doors, especially during peak wind gusts and hail.
+Rationale: To ensure personal safety from 90 km/h wind gusts and nickel-sized hail.
+[P2] VEHICLE_PROTECTION: Move vehicles to an enclosed garage or to higher ground away from trees and potential flood areas.
+Rationale: To protect vehicles from hail and wind damage, and from potential overland flooding due to 50mm rain and uninsured overland water.
+[P3] INDOOR_WATER_PROTECTION: Monitor the basement for any signs of water ingress and be prepared to use towels or buckets to manage minor leaks.
+Rationale: To mitigate risk of water ingress to the unfinished basement due to 50mm rain, especially with the critical gap in overland water coverage.</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Severe thunderstorm with 90km/h winds, hail, 50mm rain. Seek indoor shelter. Move vehicles to garage. Stay safe! Info: sophia.brown10@example.ca"
+(Length: 152 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Severe thunderstorm with 90km/h winds, nickel-sized hail, and heavy rain expected. Move vehicles to garage, secure all windows/doors, and clear basement floor. Overland water is uninsured. Stay indoors!</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics such as 90 km/h wind gusts, nickel-sized hail (2.1 cm), and rainfall exceeding 50 mm are directly matched with the alert text. The property details, including the metal roof aged 15 years, unfinished basement, and lack of overland water endorsement, are accurately reflected in the advisory. There is no fabrication or hallucination of any structural features or peril metrics. All claims are consistent with the ground truth.</t>
-        </is>
-      </c>
-      <c r="M18" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's vulnerabilities. The first action addresses the risk of hail and wind damage to vehicles, which is a primary concern during a severe thunderstorm with hail and high winds. The second action is crucial given the dwelling's lack of overland water coverage and the unfinished basement, directly targeting the risk of water damage from torrential downpours. The third action ensures the home is secured against wind-driven rain and debris, which is a direct threat from the forecasted 90 km/h wind gusts. All actions are executable within the warning lead time and avoid any dangerous outdoor activities, aligning perfectly with life-safety requirements.</t>
-        </is>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and actionable, providing immediate instructions on what the threat is (severe storm with 90km/h winds and hail) and what to do first (move vehicles, secure windows/doors, clear basement floor). It is urgent without inciting panic and free of insurance jargon, complying with the character limit. The push notification is similarly clear, with a slightly more detailed description of the storm, and includes a note about overland water being uninsured, which is relevant but not overly technical. The micro-actions are straightforward, providing specific steps to mitigate damage, and are free of jargon, making them easy to follow in an emergency.</t>
-        </is>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <v>5</v>
+Body: Severe thunderstorm with 90 km/h winds, nickel-sized hail, and 50 mm rain. Seek indoor shelter. Move vehicles to garage. Monitor basement for leaks.</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event, including the 90 km/h wind gusts, nickel-sized hail (2.1 cm), and 50 mm of rainfall, directly match the ground truth weather alert. The property details, such as the metal roof being 15 years old and the unfinished basement, are accurately reflected in the advisory. The mention of the lack of overland water endorsement is also correct, as the ground truth confirms that overland water is not endorsed. There are no fabricated numbers or unverified structural features mentioned in the advisory.</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril and the dwelling's vulnerabilities. The indoor shelter action directly addresses personal safety from high wind gusts and hail, which are primary threats in a severe thunderstorm. The vehicle protection action is crucial for preventing hail and wind damage to vehicles, and it also considers the uninsured gap for overland water by suggesting relocation to higher ground. The indoor water protection action is tailored to the dwelling's lack of a sump pump and the critical policy gap in overland water coverage, addressing potential water ingress in the basement. All actions are executable within the warning lead time and avoid hazardous outdoor activities during the storm.</t>
+        </is>
+      </c>
+      <c r="P18" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions partially cover the mandatory actions. The action to move vehicles to an enclosed garage addresses the mandatory action to protect vehicles from hail damage. However, the agent fails to address securing or storing outdoor items to prevent projectile damage and closing and latching windows and doors to prevent water infiltration and wind pressurization. 
+The additional action to seek shelter indoors is illogical in the context of property loss mitigation, as it focuses on personal safety rather than property protection. The action to monitor the basement for water ingress is sound and relevant given the torrential downpours mentioned in the alert, but it does not cover any of the mandatory actions. Therefore, the score is 3 due to the omission of two mandatory actions and the inclusion of an illogical additional action.</t>
+        </is>
+      </c>
+      <c r="R18" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, providing immediate instructions on what the threat is (severe thunderstorm) and what actions to take (seek shelter, move vehicles). It avoids any insurance jargon and fits within the character limit. The push notification complements the SMS by providing additional details without overwhelming the user, maintaining clarity and urgency. The micro-actions are clear, actionable, and free of jargon, providing specific steps to ensure safety during the storm.</t>
+        </is>
+      </c>
+      <c r="T18" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="19" ht="135" customHeight="1">
@@ -2091,61 +2314,75 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: Detached dwelling, Asphalt shingle roof (4 years old) vulnerable to high winds and hail, Finished basement at risk from water ingress
-Identified Gaps: Basement sewer backup damage is UNINSURED, Surface overland flood runoff is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room or basement, away from windows, due0 to the active tornado warning and extreme wind/hail risk.
-Rationale: Active tornado warning and severe weather pose an immediate threat to life and property. Seeking shelter in a safe interior space is critical.
+Identified Vulnerabilities: Asphalt shingle roof vulnerable to high winds and large hail, Finished basement at risk from wind-driven rain and potential water ingress
+Identified Gaps: Sewer Backup Endorsement: UNINSURED, Overland Water Endorsement: UNINSURED</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room or basement, away from windows, due to the active tornado and extreme wind/hail risk.
+Rationale: Direct protection from life-threatening tornado, high winds, and large hail.
 [P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area to protect them from large hail and damaging winds.
-Rationale: Ping-pong ball sized hail and 120 km/h winds can cause significant damage to vehicles if left exposed.
-[P3] INDOOR_SHELTER: Ensure all windows and doors are securely closed and locked to prevent wind and hail intrusion, and prepare for potential power outages.
-Rationale: High winds and hail can breach unsecured openings, causing interior damage. Power outages are common during severe storms.</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>"URGENT: Tornado Warning! Seek immediate shelter in basement/interior room. Move vehicles to garage. Secure windows/doors. Stay safe!"
-(Length: 132 / 160 chars)</t>
+Rationale: Mitigate potential damage to vehicles from ping-pong ball sized hail and 120 km/h wind gusts.
+[P3] INDOOR_WATER_PROTECTION: Ensure all windows and doors are securely closed and locked to prevent wind and rain intrusion.
+Rationale: Minimize property damage from wind-driven rain and potential debris entry during the tornado.</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning &amp; Severe Storm
-Body: Tornado Warning active for your area. Seek immediate shelter. Move vehicles to garage. Secure all windows and doors.</t>
-        </is>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the detached dwelling, asphalt shingle roof age, and finished basement are accurately reflected from the property data. The advisory correctly identifies the lack of sewer backup and overland water endorsements, aligning with the policy details. No fabricated or unverified information is present in the advisory.</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling characteristics. The primary action of seeking shelter in the basement directly addresses the life-safety threat posed by the tornado, considering the finished basement as a suitable shelter area. The vehicle protection action is pertinent given the risk of hail and wind damage, and moving vehicles to a garage is a practical measure. Securing windows and doors is crucial to prevent wind and hail intrusion, and preparing for power outages is a sensible precaution. These actions are executable within the warning lead time and align with the dwelling's structural features and policy gaps, particularly the lack of sewer backup and overland water coverage, which are not directly relevant to the immediate tornado threat.</t>
-        </is>
-      </c>
-      <c r="O19" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and providing specific actions to take: seek shelter, move vehicles, and secure windows/doors. It is well within the character limit and avoids any insurance jargon. The push notification complements the SMS by reiterating the urgency and actions, maintaining clarity and directness. The micro-actions are detailed yet clear, providing specific instructions without overwhelming the reader with technical terms or unnecessary information. Overall, the communication is effective, actionable, and free of jargon, making it suitable for emergency conditions.</t>
-        </is>
-      </c>
-      <c r="Q19" s="21" t="n">
+          <t>"URGENT: Tornado Warning for your area. Seek immediate shelter in basement/interior room. Move vehicles to garage. Stay safe! #TornadoWarning"
+(Length: 140 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
+Body: A tornado is occurring. Seek immediate shelter in your basement or an interior room away from windows. Move vehicles to garage. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the asphalt shingle roof, finished basement, and lack of sewer backup and overland water endorsements are accurately reflected in the advisory. All actions and recommendations are consistent with the ground truth, with no fabricated or unverified claims.</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling characteristics. The first action prioritizes life safety by advising immediate shelter in the basement, which is appropriate given the finished basement and the tornado threat. The second action addresses vehicle protection from hail and wind, which is a secondary but relevant concern. The third action focuses on securing the home against wind-driven rain and debris, which is crucial given the uninsured gaps for sewer backup and overland water. All actions are executable within the warning lead time and avoid dangerous outdoor activities, aligning perfectly with the peril's primary loss drivers and the property's vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="P19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover both mandatory reference actions. The first action advises seeking shelter in the lowest interior room or basement, away from windows, which semantically matches both mandatory actions by emphasizing shelter in a safe location and avoiding windows. The additional actions proposed by the agent are logical and grounded in the context of the alert. Moving vehicles to a covered area is a practical measure to protect them from hail and wind damage, and ensuring windows and doors are securely closed is a sound action to prevent wind and rain intrusion. All actions are appropriate for the dwelling type and the specific weather threats described in the alert.</t>
+        </is>
+      </c>
+      <c r="R19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both clear, concise, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps to take: seek shelter and move vehicles. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions are detailed yet clear, providing additional guidance without overwhelming the reader.</t>
+        </is>
+      </c>
+      <c r="T19" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2192,60 +2429,76 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: semi_detached dwelling susceptible to extreme wind and hail damage, metal roof (8 years old) can be damaged by extreme winds and large hail
+Identified Vulnerabilities: semi_detached dwelling, metal roof (8 years old) vulnerable to extreme wind and large hail
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room or basement, away from windows, due to the active tornado warning.
-Rationale: A tornado is active with extreme danger. The safest place is an interior room on the lowest floor or a basement to protect against flying debris and structural collapse.
-[P2] INDOOR_SHELTER: Stay away from all windows and glass doors, and close interior doors to provide additional protection from flying debris.
-Rationale: During a tornado, windows can shatter due to extreme winds and hail, posing a severe risk from flying glass and debris. Closing interior doors can offer some additional structural integrity.</t>
-        </is>
-      </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Tornado Warning! Seek immediate shelter in basement/interior room, away from windows. Stay safe! #TornadoWarning"
-(Length: 120 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Seek immediate shelter in the lowest interior room of your home, away from windows.
+Rationale: An active tornado warning with extreme winds and hail poses an immediate life-safety threat. Prioritize personal safety above all else.
+[P2] LIFE_SAFETY: Ensure all occupants are aware of the tornado warning and know where to take shelter.
+Rationale: Clear communication and preparedness among household members are crucial for safety during a tornado.
+[P3] LIFE_SAFETY: Stay informed by monitoring local weather updates from reliable sources.
+Rationale: Continuous monitoring of official weather alerts provides critical updates on the storm's progression and duration.</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
-Body: A tornado is active near your property. Immediately seek shelter in your basement or an interior room away from windows. Stay safe indoors.</t>
-        </is>
-      </c>
-      <c r="K20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the semi-detached dwelling type and metal roof age are accurately reflected in the advisory. The advisory correctly advises seeking shelter in an interior room or basement, aligning with the alert's recommendation. There are no fabricated or hallucinated claims in the advisory.</t>
-        </is>
-      </c>
-      <c r="M20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril. The primary loss drivers in a tornado event are windborne debris and structural damage, which these actions directly address by advising immediate shelter in the safest part of the home (interior room or basement). The dwelling's unfinished basement is appropriately considered as a viable shelter option, and the actions avoid unnecessary outdoor or hazardous activities, aligning with life-safety requirements. Additionally, the advice to stay away from windows and close interior doors is well-suited to mitigate risks from flying debris and glass, which are significant threats during a tornado. The actions are executable within the warning lead time and do not require any structural modifications or unrealistic measures, making them highly relevant and tailored to the situation.</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P20" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable instructions on what to do first: seek shelter in a basement or interior room away from windows. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is well within the character limit, maximizing impact and clarity. The micro-actions further reinforce the instructions with clear, jargon-free guidance.</t>
-        </is>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: Tornado Warning! Seek immediate shelter in lowest interior room. Ensure all occupants are aware. Stay safe!"
+(Length: 115 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Now
+Body: A tornado warning is active. Seek immediate shelter in the lowest interior room, away from windows. Ensure all occupants are aware. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as 'semi_detached dwelling' and 'metal roof (8 years old)' are accurately reflected from the property data. There are no fabricated or hallucinated claims regarding the weather event or property attributes. All actions and recommendations are consistent with the alert's emphasis on immediate safety due to the tornado risk.</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril. The primary loss driver in this scenario is the immediate life-safety threat posed by the tornado, with damaging winds and hail. The actions prioritize seeking shelter in the lowest interior room, which is appropriate given the dwelling's unfinished basement and the need to avoid windows due to potential windborne debris. The emphasis on ensuring all occupants are aware of the tornado warning and know where to take shelter directly addresses the critical need for life safety. Additionally, staying informed through reliable weather updates is essential for ongoing situational awareness. These actions are well-aligned with the peril and tailored to the dwelling's structural features and policy coverage, focusing on life safety without unnecessary outdoor activities.</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions effectively cover both mandatory reference actions. The first action, 'Seek immediate shelter in the lowest interior room of your home, away from windows,' semantically matches both mandatory actions by emphasizing shelter in the lowest interior room and staying away from windows. The additional actions proposed by the agent, such as ensuring all occupants are aware of the tornado warning and staying informed by monitoring local weather updates, are logical and practical given the context of a tornado warning. These actions enhance preparedness and safety, aligning with the overall goal of mitigating risk during a tornado. No illogical actions were identified, and all mandatory actions were addressed, resulting in a score of 4 due to the additional actions being somewhat redundant but still relevant.</t>
+        </is>
+      </c>
+      <c r="R20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both clear, concise, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable instructions on what to do first: seek shelter in the lowest interior room. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is well within the character limit, maximizing impact and clarity. The micro-actions further reinforce the instructions with clear, step-by-step guidance.</t>
+        </is>
+      </c>
+      <c r="T20" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="21" ht="135" customHeight="1">
@@ -2291,61 +2544,75 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: townhouse structure, slate roof (12 years old), crawlspace basement, no backwater valve
+Identified Vulnerabilities: 12-year-old slate roof vulnerable to high winds and hail, Crawlspace (though sump pump is present)
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Immediately move to the lowest interior room or basement, away from all windows and exterior walls, and cover your head and neck with your arms or a sturdy object.
-Rationale: An active tornado warning with extreme danger requires immediate life-saving action to protect against severe winds, hail, and potential structural collapse. Staying away from windows and exterior walls minimizes risk from flying debris.
-[P2] INDOOR_SHELTER: If you are in a crawlspace, get as low as possible to the ground and cover your head and neck.
-Rationale: In a crawlspace, minimizing your profile and protecting your head and neck offers the best available protection during a tornado.
-[P3] LIFE_SAFETY: Stay informed by monitoring local weather alerts on a battery-powered radio or mobile device, but do not leave your shelter until the warning has passed.
-Rationale: Staying updated on the tornado's path and duration is crucial for safety, but remaining in shelter is paramount until the immediate threat has subsided.</t>
-        </is>
-      </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>"TORNADO WARNING: Seek immediate shelter in the lowest interior room, away from windows. Cover head/neck. Do NOT go outside. #TornadoSafety"
-(Length: 138 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Immediately move to the lowest interior room or basement, away from windows, and take cover.
+Rationale: An active tornado warning with extreme winds and hail poses an immediate threat to life and safety.
+[P2] INDOOR_SHELTER: Stay informed by monitoring local weather updates from Environment Canada or local news channels.
+Rationale: Continuous monitoring is crucial for real-time safety decisions during a tornado warning.
+[P3] INDOOR_WATER_PROTECTION: Close and secure all windows and doors to minimize potential wind and hail intrusion.
+Rationale: Securing openings helps prevent wind and hail damage to the interior of your home.</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now
-Body: A tornado is active near your property. Immediately seek shelter in the lowest interior room or basement, away from windows. Do NOT go outside.</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as townhouse structure, slate roof (12 years old), crawlspace basement, and absence of a backwater valve are accurately reflected from the property data. There are no fabricated or hallucinated claims in the advisory.</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril. The primary loss drivers in a tornado event are windborne debris and structural damage, which these actions directly address by focusing on life safety and sheltering. The recommendation to move to the lowest interior room or basement is appropriate, considering the townhouse's crawlspace, and the advice to cover one's head and neck is crucial for protection against debris. The actions are also executable within the warning lead time, ensuring immediate safety. Additionally, the advice to stay informed without leaving shelter aligns with best practices for tornado safety. Overall, the actions are well-tailored to the dwelling's structural features and the immediate peril.</t>
-        </is>
-      </c>
-      <c r="O21" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P21" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both clear, concise, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps to take, such as seeking shelter in the lowest interior room and avoiding windows. The language is free of insurance jargon and technical terms, making it accessible and easy to understand in an emergency. The SMS is within the character limit, ensuring it is quick to read and comprehend. The micro-actions provide detailed instructions that are straightforward and reinforce the urgency of the situation.</t>
-        </is>
-      </c>
-      <c r="Q21" s="21" t="n">
+          <t>"Urgent: Tornado Warning for HOM-1013. Seek immediate shelter in basement/interior room. Stay away from windows. Monitor local alerts. #TornadoSafety"
+(Length: 148 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Storm Mitigation Required
+Body: Tornado Warning for your property (HOM-1013). Seek immediate shelter in the lowest interior room or basement, away from windows. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the 12-year-old slate roof and presence of a sump pump in the crawlspace are accurately reflected from the property data. There are no fabricated or hallucinated claims in the advisory.</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling characteristics. The primary loss drivers in a tornado event are life safety due to extreme winds and hail, and potential structural damage. The first action prioritizes life safety by advising immediate movement to the safest part of the home, which is crucial given the townhouse's lack of a full basement. The second action ensures occupants remain informed, which is vital for adapting to rapidly changing conditions. The third action addresses potential wind and hail intrusion, which is a significant risk given the townhouse's slate roof and the severe weather conditions. All actions are executable within the warning lead time and do not involve dangerous outdoor activities, aligning perfectly with the peril and property specifics.</t>
+        </is>
+      </c>
+      <c r="P21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover the mandatory reference actions. The first action, 'Immediately move to the lowest interior room or basement, away from windows, and take cover,' semantically matches both mandatory actions by advising to seek shelter in the lowest interior room and stay away from windows. The additional actions proposed by the agent are logical and relevant to the context of a tornado warning. Monitoring weather updates is a practical safety measure, and securing windows and doors is a reasonable action to prevent damage from wind and hail. No illogical actions were identified.</t>
+        </is>
+      </c>
+      <c r="R21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, providing immediate instructions on what the threat is (tornado) and what to do first (seek shelter). It avoids any insurance jargon and fits within the character limit. The push notification complements the SMS by reiterating the urgency and providing clear instructions without causing panic. The micro-actions are straightforward, actionable, and free of technical language, ensuring homeowners know exactly what steps to take to stay safe.</t>
+        </is>
+      </c>
+      <c r="T21" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2392,61 +2659,75 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
+          <t>• Move immediately to an interior hallway, central stairwell, or the lowest accessible common floor away from external walls and glass
+• Stay far away from exterior windows, corner rooms, balcony doors, and do not use elevators during the active tornado threat</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: Tornado Warning
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
-Rain: None mm | Snow: None cm
+Rain: None mm | Snow: 0.0 cm
 Tornado Risk: YES
-Identified Vulnerabilities: 16-year-old tar and gravel roof (potential vulnerability to extreme wind and hail), Highrise condo (balconies and windows highly exposed to high winds and hail)
-Identified Gaps: Overland Water Endorsement (surface overland flood runoff is uninsured)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Immediately seek shelter in an interior room on the lowest floor of your unit, away from all windows and glass doors, due to the active tornado warning and extreme winds.
-Rationale: To protect against injury from tornado, extreme winds, and flying debris, prioritizing life safety above all else.
-[P2] INDOOR_SHELTER: Ensure all windows and exterior doors are closed and securely locked from inside your unit.
-Rationale: To minimize the risk of wind and hail intrusion and prevent damage to your property.
-[P3] INDOOR_SHELTER: Stay away from all windows, glass doors, and exterior walls, even if closed, as they could shatter from extreme wind or hail impact.
-Rationale: To prevent injury from broken glass or debris during the severe weather event.</t>
+Identified Vulnerabilities: Highrise condo (potential for exterior damage to building structure), Slab-on-grade (vulnerable to overland water entry at ground level)
+Identified Gaps: Overland Water Endorsement (CRITICAL GAP: Surface overland flood runoff is UNINSURED)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>"URGENT: Tornado Warning for your area. Seek immediate shelter indoors away from windows. Stay safe! #TornadoWarning"
-(Length: 115 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in an interior room on the lowest floor, away from windows, doors, and outside walls. If in a high-rise, use an interior hallway or a small interior room.
+Rationale: An active tornado poses an extreme and immediate threat to life and safety.
+[P2] INDOOR_WATER_PROTECTION: Move valuable items and electronics off the floor, especially near exterior doors or windows, to protect against potential overland water entry.
+Rationale: The property has a critical gap in overland water coverage, and a tornado can bring heavy rainfall leading to surface runoff.
+[P3] VEHICLE_PROTECTION: If you have a vehicle parked outdoors, move it to an underground parking garage or a covered area if it is safe to do so, to protect against hail and wind damage.
+Rationale: Damaging winds and ping-pong ball sized hail are occurring, posing a significant risk to vehicles.</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
-Body: A tornado is active. Seek immediate shelter in an interior room, away from windows. Close and lock all windows/doors. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the 16-year-old tar and gravel roof, highrise condo type, and lack of overland water endorsement are accurately reflected from the property data. There are no fabricated or hallucinated claims about the property or the weather event.</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the specific dwelling type. The primary loss drivers for a tornado event include extreme winds and flying debris, which are directly addressed by the life safety action of seeking shelter in an interior room away from windows and glass doors. This is crucial for a highrise condo where the structural vulnerabilities include large glass surfaces. The actions also consider the lack of a basement, directing occupants to the lowest floor of their unit, which is appropriate given the slab-on-grade foundation. Additionally, securing windows and doors helps mitigate wind and hail intrusion, aligning with the dwelling's structural features and the peril's damage mechanisms. The actions are executable within the warning lead time and prioritize life safety, making them highly relevant and well-tailored.</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P22" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and the first action to take: seeking shelter indoors away from windows. It is well within the character limit and avoids any insurance jargon. The push notification is similarly clear and urgent, with a direct call to action and additional safety instructions. The micro-actions are detailed yet straightforward, providing clear steps without overwhelming the reader with technical terms or unnecessary information. Overall, the communications are effective, actionable, and free of jargon, making them suitable for emergency conditions.</t>
-        </is>
-      </c>
-      <c r="Q22" s="21" t="n">
+          <t>"URGENT: Tornado Warning! Seek immediate interior shelter. Move valuables off floor. Stay safe! Info: +1-613-555-1014"
+(Length: 116 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Now
+Body: A tornado is occurring. Seek immediate interior shelter away from windows. Move valuables off the floor due to overland water risk.</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as 'highrise condo' and 'slab-on-grade' are consistent with the property data. The advisory correctly identifies the lack of overland water endorsement as a coverage gap, which is factual. All actions and recommendations are based on the provided data without any hallucination or unverified claims.</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling characteristics. The first action prioritizes life safety by advising occupants to seek shelter in an interior room or hallway, which is crucial given the high-rise condo setting and the immediate threat posed by a tornado. The second action addresses the critical policy gap of uninsured overland water by suggesting the movement of valuables away from potential water entry points, which is a prudent measure given the potential for heavy rainfall associated with tornadoes. The third action is relevant for protecting vehicles from hail and wind damage, which are significant threats during this event. All actions are executable within the warning lead time and avoid dangerous outdoor activities, aligning with mandatory life-safety requirements.</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover the mandatory reference actions. The first action advises seeking shelter in an interior room or hallway away from windows and external walls, which aligns with both mandatory actions. The additional actions proposed by the agent are logical and grounded in the context of the alert. The second action addresses potential water damage due to heavy rainfall associated with tornadoes, which is a reasonable precaution. The third action about vehicle protection is also logical given the hail and wind threats mentioned in the alert. No illogical actions were identified, and all proposed actions are appropriate for the dwelling type and weather conditions.</t>
+        </is>
+      </c>
+      <c r="R22" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and what actions to take first. It avoids any insurance jargon and stays well within the character limit. The push notification is similarly clear, with a direct title and body that reiterates the immediate actions needed. The micro-actions provide detailed, step-by-step instructions that are easy to follow, free of jargon, and prioritize safety without causing panic. Overall, the communications are well-structured for emergency conditions, ensuring clarity and actionability.</t>
+        </is>
+      </c>
+      <c r="T22" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2493,62 +2774,76 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: Asphalt shingle roof (20 years old) vulnerable to high winds and large hail, Finished basement vulnerable to water damage, No backwater valve increases sewer backup risk
-Identified Gaps: Sewer Backup Endorsement: NO - CRITICAL GAP: Basement sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Immediately seek shelter in the lowest interior room of your home, such as a basement or an interior closet/bathroom on the ground floor, away from windows.
-Rationale: This is critical due to the active tornado warning and extreme danger to life.
-[P2] VEHICLE_PROTECTION: If your vehicles are currently parked in a garage, ensure the garage door is securely closed to protect them from hail and wind damage. Do not go outside to move vehicles if the tornado is imminent or active.
-Rationale: High winds (120 km/h) and ping-pong ball sized hail (3.5 cm) pose a significant risk of damage to vehicles.
-[P3] INDOOR_WATER_PROTECTION: Be aware that your finished basement is vulnerable to sewer backup due to the lack of a backwater valve and an uninsured policy gap. After the immediate danger passes, inspect your basement for any water ingress.
-Rationale: Finished basements without backwater valves are at high risk of water damage from sewer backup, especially during severe weather with potential heavy rainfall, and this risk is uninsured.</t>
+Identified Vulnerabilities: asphalt_shingle roof (20 years old) vulnerable to high winds and large hail, finished basement vulnerable to sewer backup, no backwater valve increases risk of sewer backup
+Identified Gaps: Sewer Backup Endorsement: NO - Basement sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Tornado Warning for HOM-1015. Seek immediate shelter in lowest interior room. Stay away from windows. Monitor local alerts. #TornadoSafety"
-(Length: 146 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room of your home, away from windows.
+Rationale: An active tornado warning and extreme wind risk (120 km/h) pose an immediate threat to life and property.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area.
+Rationale: Large hail (ping-pong ball size) and damaging winds (120 km/h) can cause significant damage to vehicles.
+[P3] INDOOR_WATER_PROTECTION: Ensure all basement floor drains are covered and avoid using water (showers, toilets, washing machines).
+Rationale: Without sewer backup coverage and no backwater valve, minimizing water usage and covering drains can reduce the risk of uninsured basement sewer backup damage during heavy rainfall associated with severe storms.</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Storm Mitigation Required
-Body: Tornado Warning active for your property. Immediately seek shelter in the lowest interior room, away from windows. Ensure garage doors are closed.</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the asphalt shingle roof being 20 years old, the presence of a finished basement, and the lack of a backwater valve are accurately reflected in the advisory. The advisory correctly identifies the lack of sewer backup endorsement as a critical gap, which is consistent with the policy details. No fabricated numbers or non-existent features are present in the advisory.</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the specific dwelling vulnerabilities. The life-safety action to seek shelter in the basement or an interior room directly addresses the primary threat of a tornado, which is critical given the severe weather conditions. The vehicle protection action is well-aligned with the risk of hail and high winds, advising against outdoor activity, which is crucial for safety. The indoor water protection action is highly tailored to the dwelling's specific vulnerability of an uninsured sewer backup risk due to the lack of a backwater valve, highlighting the need for post-event inspection of the finished basement. All actions are executable within the warning lead time and prioritize life safety and property protection effectively.</t>
-        </is>
-      </c>
-      <c r="O23" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P23" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and what actions to take first. It avoids any insurance jargon and fits within the character limit. The push notification is similarly clear and actionable, with a direct call to action and no unnecessary jargon. The micro-actions are detailed yet clear, providing specific instructions without overwhelming the reader with technical terms or insurance details. Overall, the communications are well-structured for emergency conditions, ensuring the homeowner knows exactly what to do.</t>
-        </is>
-      </c>
-      <c r="Q23" s="21" t="n">
-        <v>5</v>
+          <t>"URGENT: Tornado Warning! Seek immediate shelter in lowest interior room. Move vehicles to cover. Avoid water use due to sewer backup risk. Stay safe!"
+(Length: 149 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning &amp; Storm Mitigation Required
+Body: Tornado Warning active! Seek immediate shelter. Move vehicles to garage. Avoid water use to prevent uninsured sewer backup. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the asphalt shingle roof being 20 years old, the presence of a finished basement, and the absence of a backwater valve are accurately reflected in the advisory. The mention of no sewer backup endorsement is also correct. There are no fabricated numbers or unverified claims in the advisory.</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of a tornado and the dwelling's vulnerabilities. The first action prioritizes life safety by advising immediate shelter in the lowest interior room, which is crucial given the tornado warning and the finished basement. The second action addresses vehicle protection from hail and wind damage, which is pertinent given the forecasted hail size and wind speeds. The third action is particularly well-tailored to the dwelling's lack of sewer backup insurance and absence of a backwater valve, advising measures to mitigate potential basement flooding from sewer backup during the storm. All actions are executable within the warning lead time and directly target the primary loss drivers of the active weather peril.</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions semantically cover both mandatory reference actions. The first action advises seeking shelter in the lowest interior room away from windows, which aligns with both seeking shelter on the lowest level and staying away from windows. The additional actions proposed by the agent are logical and relevant to the context of the alert. Moving vehicles to a covered area is a practical measure against hail damage, and covering basement drains is a reasonable precaution given the lack of a backwater valve and potential for heavy rain. No illogical actions were identified, but the additional action regarding basement water protection is somewhat marginally relevant to the tornado warning, which slightly affects the score.</t>
+        </is>
+      </c>
+      <c r="R23" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, providing immediate instructions on what to do during a tornado warning. It avoids insurance jargon and focuses on actionable steps: seeking shelter, moving vehicles, and avoiding water use. The character count is within limits, ensuring quick readability. The push notification maintains the same clarity and urgency, with a slight mention of 'uninsured sewer backup,' which could be considered borderline jargon but is still understandable in context. The micro-actions are clear and provide detailed steps without overwhelming the reader, maintaining focus on immediate safety actions.</t>
+        </is>
+      </c>
+      <c r="T23" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="24" ht="135" customHeight="1">
@@ -2594,62 +2889,74 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>Identified Event: tornado warning in effect
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>Identified Event: Tornado Warning
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: Metal roof (24 years old) may be vulnerable to extreme winds and large hail, Unfinished basement is the safest place during a tornado, No sump pump or backwater valve (not directly relevant to current peril)
-Identified Gaps: Wind/Hail Deductible: $1,500.00 (financial exposure)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Immediately seek shelter in the lowest interior room or basement, away from windows, due to the active tornado warning and extreme winds.
-Rationale: An active tornado warning with 120 km/h winds and large hail poses an immediate threat to life. The basement or an interior room offers the best protection.
-[P2] INDOOR_SHELTER: Close all interior doors and stay away from windows and exterior walls to enhance protection from flying debris and strong winds.
-Rationale: Closing interior doors can provide an additional barrier against debris, and staying away from windows minimizes risk from shattering glass during a tornado.
-[P3] VEHICLE_PROTECTION: If vehicles are already in an attached garage, ensure the garage door is closed. Do not venture outside to move vehicles; prioritize personal safety.
-Rationale: While protecting vehicles from large hail (3.5 cm) and 120 km/h winds is important, personal safety during an active tornado warning takes precedence. Only secure vehicles if it does not require outdoor exposure.</t>
+Identified Vulnerabilities: 24-year-old metal roof susceptible to extreme wind and hail damage
+Identified Gaps: None</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>"URGENT: Tornado Warning for HOM-1016. Seek immediate shelter in basement/interior room. Close doors, stay from windows. Prioritize safety!"
-(Length: 138 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Seek immediate shelter in the lowest level of your home, away from windows, due to the active tornado and extreme weather.
+Rationale: To protect life and minimize injury risk from tornado, high winds, and flying debris.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or covered area to protect against hail and flying debris.
+Rationale: To prevent damage to vehicles from large hail and wind-borne objects.</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
-Body: A tornado warning is active for your property. Seek immediate shelter in your basement or an interior room away from windows. Close all interior doors. Your safety is paramount; do not go outside.</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the metal roof, its age, and the unfinished basement are accurately reflected from the property data. The advisory correctly notes the absence of a sump pump and backwater valve, aligning with the ground truth. All actions and recommendations are consistent with the factual data provided, with no hallucinations or fabrications present.</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the specific dwelling characteristics. The primary loss drivers in this scenario are life safety due to the tornado and potential damage from high winds and hail. The actions prioritize immediate life safety by advising shelter in the basement or lowest interior room, which is appropriate given the unfinished basement and the lack of a sump pump or backwater valve concerns. The recommendation to close interior doors and stay away from windows directly addresses the risk of flying debris and shattering glass, which are critical during a tornado. The vehicle protection advice is well-tailored, emphasizing personal safety over vehicle protection, which is crucial given the extreme weather conditions. Overall, the actions are well-aligned with the peril and the dwelling's structural vulnerabilities, ensuring both safety and property protection within the available lead time.</t>
-        </is>
-      </c>
-      <c r="O24" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P24" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both clear, concise, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps to take: seek shelter in a basement or interior room, close doors, and stay away from windows. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions further clarify the steps without unnecessary complexity, reinforcing the urgency and safety measures.</t>
-        </is>
-      </c>
-      <c r="Q24" s="21" t="n">
-        <v>5</v>
+          <t>"URGENT: Tornado Warning for HOM-1016. Seek immediate shelter in lowest level, away from windows. Move vehicles to garage. Stay safe!"
+(Length: 132 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Immediately
+Body: A tornado is active near your property (HOM-1016). Seek immediate shelter in the lowest level of your home, away from windows. Move vehicles to garage. Do not go outside.</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather hazard metrics are accurately reflected: the wind gusts are stated as 120 km/h and hail size as 3.5 cm, both of which match the alert text. The advisory correctly identifies the tornado risk and advises seeking shelter in the lowest level, consistent with the alert's recommendation to take cover in an interior room or basement. The property details, such as the 24-year-old metal roof, are accurately described, and there is no mention of a sump pump or backwater valve, which aligns with the ground truth. No unverified claims or hallucinations are present.</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the active tornado hazard and the specific dwelling characteristics. The first action prioritizes life safety by advising immediate shelter in the lowest level of the home, which is crucial during a tornado. This action is appropriately tailored to the dwelling's unfinished basement, which is the safest location given the lack of windows and the structural integrity of basements during tornadoes. The second action addresses the risk of hail and wind-borne debris damage to vehicles, which is a significant concern given the forecasted hail size and wind speeds. Both actions are executable within the warning lead time and directly target the primary loss drivers of the tornado and hail peril.</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions semantically cover both mandatory actions. The first action advises seeking shelter on the lowest level and away from windows, which aligns with both mandatory actions of seeking shelter in an interior room and staying away from windows. The additional action of moving vehicles to a covered area is logical and relevant given the hail and wind threats mentioned in the alert. However, the agent's action does not explicitly mention the need for as many walls between the individual and the exterior as possible, which is a minor secondary aspect of the first mandatory action. Therefore, the score is slightly reduced to 4, as the coverage is substantially complete but not perfect.</t>
+        </is>
+      </c>
+      <c r="R24" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S24" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps: seek shelter and move vehicles. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS complies with the character limit, ensuring quick readability. The micro-actions are also clear and provide detailed instructions without unnecessary complexity.</t>
+        </is>
+      </c>
+      <c r="T24" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="25" ht="135" customHeight="1">
@@ -2695,61 +3002,75 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: Townhouse dwelling, Crawlspace foundation
-Identified Gaps: Overland Water Endorsement missing</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room of your home, away from windows.
-Rationale: An active tornado warning with extreme winds and large hail poses an immediate threat to life and safety.
-[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area.
-Rationale: Large hail (3.5 cm) and damaging winds (120 km/h) can cause significant damage to vehicles.
-[P3] INDOOR_WATER_PROTECTION: Ensure all windows and doors are securely closed and locked.
-Rationale: To prevent wind and potential water intrusion from severe weather, especially with a crawlspace foundation.</t>
+Identified Vulnerabilities: Crawlspace vulnerable to water ingress, Roof and exterior vulnerable to extreme wind and hail from tornado
+Identified Gaps: Overland Water Endorsement missing (UNINSURED for surface overland flood runoff)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>"URGENT: Tornado Warning for HOM-1017. Seek immediate shelter in an interior room, away from windows. Move vehicles to cover. Stay safe!"
-(Length: 135 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room or basement, away from windows, due to the active tornado warning and extreme wind/hail risk.
+Rationale: Direct threat to life and safety from active tornado, high winds, and large hail.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area to protect them from large hail and flying debris.
+Rationale: Vehicles are at high risk of damage from ping-pong ball sized hail and wind-driven debris.
+[P3] INDOOR_WATER_PROTECTION: Ensure all ground-level windows and doors are securely closed and locked to prevent wind-driven rain and debris entry, especially given the crawlspace and lack of overland water coverage.
+Rationale: Mitigate potential water damage to the crawlspace and interior from wind-driven rain, exacerbated by the lack of overland water coverage.</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter!
-Body: A tornado warning is active for your property. Seek immediate shelter in the lowest interior room, away from windows. Move vehicles to cover.</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the townhouse dwelling type and crawlspace foundation are accurately reflected from the property data. The mention of the missing Overland Water Endorsement is also correct as per the policy details. All actions and recommendations are consistent with the provided data, with no fabricated or unverified claims.</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling characteristics. The first action prioritizes life safety by advising immediate shelter in the lowest interior room, which is crucial given the tornado warning and the townhouse's crawlspace, which is not suitable for shelter. The second action addresses vehicle protection from hail and wind damage, which is pertinent given the forecasted hail size and wind speeds. The third action focuses on securing the home against wind and water intrusion, which is particularly important due to the crawlspace foundation and the uninsured overland water gap. All actions are executable within the warning lead time and avoid dangerous outdoor activities, aligning perfectly with the peril and property specifics.</t>
-        </is>
-      </c>
-      <c r="O25" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P25" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps to take first, such as seeking shelter and moving vehicles. The language is free of insurance jargon and technical terms, making it accessible and easy to understand in an emergency. The SMS complies with the character limit, maximizing impact with a direct and punchy message. The micro-actions are also clear and actionable, providing step-by-step instructions that are easy to follow.</t>
-        </is>
-      </c>
-      <c r="Q25" s="21" t="n">
+          <t>"URGENT: Tornado Warning for HOM-1017. Seek immediate shelter indoors. Move vehicles to safety. Stay away from windows. #TornadoSafety"
+(Length: 133 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
+Body: A tornado is occurring near your property (HOM-1017). Seek immediate shelter in the lowest interior room. Move vehicles to safety. Stay away from windows.</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the presence of a crawlspace, sump pump, and lack of overland water endorsement are accurately reflected in the advisory. The micro actions and exposure analysis are consistent with the property's vulnerabilities and policy coverage details. No fabricated or hallucinated information is present.</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the specific dwelling characteristics. The life-safety action to seek shelter in the lowest interior room is critical given the tornado warning and aligns with the dwelling's crawlspace basement, which is not suitable for shelter. The vehicle protection action is highly relevant due to the risk of hail and debris, and moving vehicles to a covered area is a practical measure. The indoor water protection action is well-tailored to the dwelling's vulnerabilities, addressing the risk of wind-driven rain entry through ground-level openings, which is crucial given the uninsured gap for overland water. All actions are executable within the warning lead time and directly target the primary loss drivers of the tornado and associated severe weather.</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover both mandatory reference actions. The first action advises seeking shelter in the lowest interior room or basement, away from windows, which semantically matches both mandatory actions by emphasizing shelter in a safe interior space and avoiding windows. The additional actions proposed by the agent are logical and relevant to the context of the tornado warning. Moving vehicles to a covered area is a practical measure to protect them from hail and debris, and ensuring windows and doors are secured is a sound action to prevent water and debris entry, which aligns with the potential for wind-driven rain and the presence of a crawlspace. No illogical actions were identified.</t>
+        </is>
+      </c>
+      <c r="R25" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both clear, concise, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific actions to take: seek shelter, move vehicles, and stay away from windows. The SMS is within the character limit and uses a hashtag effectively for emphasis. The push notification expands slightly but remains focused and jargon-free. The micro-actions are detailed yet clear, avoiding insurance jargon and providing actionable steps in a logical sequence. Overall, the communication is highly effective for emergency conditions.</t>
+        </is>
+      </c>
+      <c r="T25" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2796,66 +3117,76 @@
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
+          <t>• Move immediately to an interior hallway, central stairwell, or the lowest accessible common floor away from external walls and glass
+• Stay far away from exterior windows, corner rooms, balcony doors, and do not use elevators during the active tornado threat</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
-Rain: None mm | Snow: 0.0 cm
+Rain: None mm | Snow: None cm
 Tornado Risk: YES
-Identified Vulnerabilities: Highrise condo structure susceptible to extreme winds and large hail, Tar and gravel roof (7 years old) vulnerable to high winds and hail
+Identified Vulnerabilities: Highrise condo exterior elements vulnerable to extreme wind and hail, Tar and gravel roof vulnerable to extreme hail
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Seek immediate shelter in an interior room on the lowest floor, away from windows, doors, and outside walls.
-Rationale: An active tornado warning with extreme winds and hail poses an immediate threat to life and safety. Interior rooms provide the best protection.
-[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to an underground parking area if available.
-Rationale: Damaging winds up to 120 km/h and ping-pong ball sized hail can cause significant damage to vehicles if left exposed.
-[P3] INDOOR_SHELTER: Close and secure all windows and doors.
-Rationale: Securing windows and doors will help prevent wind and hail intrusion, reducing potential damage to the interior of your home.</t>
-        </is>
-      </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Tornado Warning! Seek immediate shelter indoors away from windows. Move vehicles to safety. Stay safe, Harper."
-(Length: 118 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Immediately seek shelter in the lowest interior room or an underground parking garage, away from windows and doors. Follow local emergency instructions.
+Rationale: An active tornado warning with extreme winds and hail poses an immediate and severe threat to life and property. Seeking safe shelter is paramount.
+[P2] VEHICLE_PROTECTION: If safe to do so and time permits, move vehicles to an underground parking garage or a protected area away from windows, trees, and potential falling debris.
+Rationale: Extreme winds and hail can cause significant damage to vehicles. Protecting them can reduce potential losses.
+[P3] INDOOR_SHELTER: Close all windows and doors, and draw blinds or curtains to protect against flying debris and shattered glass.
+Rationale: Closing windows and drawing blinds can help protect against shattered glass and flying debris, enhancing indoor safety during extreme weather.</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
-Body: A tornado warning is active for your area. Seek immediate shelter in an interior room on the lowest floor. Move vehicles to a garage or underground parking. Close all windows and doors. Stay safe.</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the highrise condo structure and tar and gravel roof are accurately described. The advisory does not fabricate any features or metrics, and all actions and recommendations are consistent with the ground truth information. There is no mention of a basement or sump pump, which aligns with the property data indicating a slab on grade and no sump pump. Therefore, the advisory is fully faithful to the ground truth.</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N26" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling type. The primary loss drivers in a tornado event are life safety due to extreme winds and hail, and the actions prioritize these appropriately. 
-1. The first action focuses on life safety by advising occupants to seek shelter in an interior room on the lowest floor, which is crucial given the highrise condo setting where a basement is not available. This directly addresses the immediate threat to life from the tornado.
-2. The second action addresses vehicle protection, which is relevant given the potential for hail damage. Moving vehicles to a garage or underground parking is practical and effective in a highrise setting where such facilities are typically available.
-3. The third action to close and secure windows and doors is appropriate for preventing wind and hail intrusion, which is a significant risk in highrise buildings with large window areas.
-Overall, the actions are executable within the warning lead time and are specifically tailored to the structural characteristics and vulnerabilities of the highrise condo, ensuring comprehensive risk mitigation.</t>
-        </is>
-      </c>
-      <c r="O26" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P26" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and what actions to take first. It avoids any insurance jargon and fits well within the character limit. The push notification and micro-actions are also clear and actionable, providing detailed instructions without overwhelming the reader. The tone is urgent but not panicky, and the instructions are straightforward and easy to follow, ensuring the homeowner knows exactly what to do to stay safe.</t>
-        </is>
-      </c>
-      <c r="Q26" s="21" t="n">
-        <v>5</v>
+          <t>"URGENT: Tornado Warning for HOM-1018. Seek immediate shelter in an interior room or underground. Stay away from windows. Life safety is paramount."
+(Length: 146 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning - Seek Shelter Now
+Body: A tornado is active near HOM-1018. Immediately seek shelter in an interior room or underground. Stay away from windows. Close all windows and draw blinds.</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm (ping-pong ball size) are directly matched with the weather alert. The property is correctly identified as a highrise condo with a tar and gravel roof, and there is no mention of a sump pump or basement, which aligns with the 'slab on grade' basement type and absence of a sump pump in the ground truth. The advisory's micro-actions and safety instructions are appropriate for the described weather conditions and property type. No hallucinations or unverified claims are present.</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the active tornado peril and the specific dwelling type. The primary loss drivers in a tornado event are life safety due to extreme winds and flying debris, as well as potential damage from hail. The first action prioritizes life safety by advising occupants to seek shelter in the safest available location, which is crucial given the highrise condo setting with a slab-on-grade foundation. The second action addresses vehicle protection, which is pertinent given the potential for hail and debris damage, and suggests using the underground parking garage, a practical and effective measure. The third action enhances indoor safety by minimizing the risk of injury from shattered glass and debris, which is a significant concern in highrise buildings with many windows. All actions are executable within the warning lead time and appropriately consider the structural characteristics and policy coverages of the dwelling.</t>
+        </is>
+      </c>
+      <c r="P26" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions partially cover the mandatory actions. The action to 'Immediately seek shelter in the lowest interior room or an underground parking garage, away from windows and doors' semantically matches the requirement to move to an interior hallway or central stairwell, but it incorrectly suggests using an underground parking garage, which is not applicable for a highrise condo without such a feature. The action to 'Close all windows and doors, and draw blinds or curtains' is logical but does not fully cover the requirement to stay away from exterior windows and not use elevators. The suggestion to move vehicles is logical and relevant for vehicle protection but does not contribute to the mandatory actions. The illogical aspect is the suggestion of using an underground parking garage for shelter, which is not applicable to the dwelling type.</t>
+        </is>
+      </c>
+      <c r="R26" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S26" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, providing immediate instructions on what to do (seek shelter) and why (tornado warning). It avoids any insurance jargon and fits within the character limit. The push notification complements the SMS by reiterating the urgency and providing additional safety measures (closing windows and drawing blinds). The micro-actions are clear, actionable, and free of jargon, providing step-by-step guidance on how to protect oneself and property during a tornado. Overall, the communication is direct, easy to understand, and prioritizes life safety without causing panic.</t>
+        </is>
+      </c>
+      <c r="T26" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="27" ht="135" customHeight="1">
@@ -2901,61 +3232,80 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
 Rain: None mm | Snow: None cm
 Tornado Risk: YES
 Identified Vulnerabilities: asphalt_shingle roof (11 years old) vulnerable to high winds and hail, finished basement vulnerable to water damage, no backwater valve increases sewer backup risk
-Identified Gaps: Sewer Backup Endorsement: NO - Basement sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest level of your home, away from windows, due to the active tornado warning and extreme wind risk.
-Rationale: Tornadoes pose an immediate threat to life and property. Seeking shelter in an interior room on the lowest floor provides the best protection from high winds and flying debris.
-[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area to protect against ping-pong ball sized hail and flying debris.
-Rationale: Large hail and strong winds can cause significant damage to vehicles, leading to costly repairs. Covered parking offers protection.
-[P3] INDOOR_WATER_PROTECTION: Elevate valuable items off the basement floor to mitigate potential uninsured water damage from sewer backup.
-Rationale: With a finished basement and no sewer backup endorsement, there is a critical gap in coverage. Elevating items can reduce potential losses from water intrusion.</t>
+Identified Gaps: Sewer Backup Endorsement: Basement sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Tornado Warning! Seek immediate shelter in your basement. Move vehicles to cover. Stay safe! #TornadoWarning"
-(Length: 116 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest level, interior room, or basement away from windows, walls, and doors. This is critical due to the active tornado.
+Rationale: An active tornado with damaging winds and hail poses an extreme danger to life and property. Immediate shelter is paramount.
+[P2] VEHICLE_PROTECTION: Move vehicles into a garage or to a covered area to protect them from hail and wind damage.
+Rationale: Ping-pong ball sized hail and 120 km/h winds can cause significant damage to vehicles if left exposed.
+[P3] INDOOR_WATER_PROTECTION: Minimize water usage (e.g., avoid flushing toilets, running dishwashers/washing machines) to reduce the risk of sewer backup into your finished basement.
+Rationale: With a finished basement and no sewer backup endorsement, minimizing water usage can help prevent uninsured damage from potential sewer system overload during severe weather.</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning &amp; Hail Threat
-Body: A tornado warning is active. Seek immediate shelter in your basement. Move vehicles to covered areas to protect against ping-pong ball sized hail. Elevate basement valuables.</t>
-        </is>
-      </c>
-      <c r="K27" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the asphalt shingle roof being 11 years old, the presence of a finished basement, and the absence of a backwater valve are accurately reflected in the exposure analysis. The advisory correctly notes the lack of sewer backup endorsement, aligning with the policy details. All actions and recommendations are consistent with the factual data provided, with no hallucinations or fabrications present.</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N27" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of a tornado and the dwelling's vulnerabilities. The first action prioritizes life safety by advising immediate shelter in the basement, which is crucial given the tornado warning and the finished basement. The second action addresses the risk of hail damage to vehicles, which is pertinent given the forecasted hail size. The third action is tailored to the uninsured gap of sewer backup, advising the elevation of valuables in the finished basement to mitigate potential water damage. All actions are executable within the warning lead time and directly target the primary loss drivers of the tornado and hail event.</t>
-        </is>
-      </c>
-      <c r="O27" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P27" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and the first action to take (seek shelter). It avoids any insurance jargon and fits well within the character limit. The push notification effectively expands on the SMS, providing additional details about the hail threat and further actions to protect property, such as moving vehicles and elevating valuables. The micro-actions are clear, actionable, and free of jargon, providing specific instructions without overwhelming the reader. Overall, the messages are well-structured for quick comprehension during an emergency.</t>
-        </is>
-      </c>
-      <c r="Q27" s="21" t="n">
+          <t>"URGENT: Tornado Warning! Seek immediate shelter. Move vehicles to safety. Minimize water use. Stay safe, Michael. #TornadoSafety"
+(Length: 128 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning &amp; Mitigation Required
+Body: Tornado Warning active for your area. Seek immediate shelter. Move vehicles to safety. Minimize water usage to prevent sewer backup. Stay safe.</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. All claims about the weather event and property attributes are directly supported by the ground truth. Specifically:
+- The tornado warning, wind gusts of 120 km/h, and hail size of 3.5 cm (ping-pong ball size) are accurately reflected from the weather alert.
+- The property details such as the asphalt shingle roof being 11 years old, the presence of a finished basement, and the absence of a backwater valve are correctly stated as per the property data.
+- The advisory correctly notes the lack of sewer backup endorsement, aligning with the policy details.
+- The micro actions and safety recommendations are appropriate and based on the accurate interpretation of the risks and property vulnerabilities outlined in the ground truth.
+There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the specific dwelling vulnerabilities. The life-safety action to seek shelter in the basement directly addresses the primary threat of tornado-induced structural damage and is appropriately prioritized. The vehicle protection action is relevant to the hail threat and is practical given the lead time. The indoor water protection action is particularly well-tailored to the dwelling's lack of a sewer backup endorsement and the presence of a finished basement, addressing a critical policy gap by mitigating potential uninsured losses. All actions are executable within the warning lead time and avoid hazardous outdoor activities, aligning perfectly with safety protocols.</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover both mandatory reference actions. The first action advises seeking shelter in the lowest level or interior room, away from windows and exterior walls, which semantically matches both mandatory actions. The additional actions proposed by the agent are logical and grounded in the context of the alert and property details. Moving vehicles to a covered area is a practical measure to protect them from hail and wind damage, and minimizing water usage is a sound precaution to prevent potential sewer backup in a finished basement during severe weather. No illogical actions were identified.</t>
+        </is>
+      </c>
+      <c r="R27" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S27" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and what actions to take first. It avoids any insurance jargon and fits well within the character limit. The push notification is similarly clear, with a slightly expanded explanation that remains free of jargon and maintains urgency without causing panic. The micro-actions are detailed yet straightforward, providing clear instructions on what to do and why, without using technical language. Overall, the communications are well-structured for emergency conditions, ensuring the homeowner knows exactly what to do.</t>
+        </is>
+      </c>
+      <c r="T27" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3002,62 +3352,76 @@
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
+          <t>• Seek immediate shelter on the lowest interior level of the home (basement, interior closet, or bathroom) with as many walls between you and the exterior as possible
+• Stay far away from all windows, skylights, exterior glass, and outside walls during the active tornado warning</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: tornado warning in effect
 Wind Gust: 120 km/h | Hail: ping-pong ball size (3.5 cm)
-Rain: None mm | Snow: None cm
+Rain: None mm | Snow: 0.0 cm
 Tornado Risk: YES
-Identified Vulnerabilities: Roof: metal (15 years old) vulnerable to 120 km/h winds and 3.5 cm hail, Unfinished basement provides potential shelter
-Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Seek immediate shelter in the lowest level of your home, such as the unfinished basement, away from windows and exterior walls. This is critical due to the active tornado and extreme wind/hail risk.
-Rationale: An active tornado with 120 km/h winds and ping-pong ball sized hail poses an immediate life-safety threat and significant property damage risk. The basement offers the most protection.
-[P2] VEHICLE_PROTECTION: If safe to do so immediately, move any vehicles into a garage or to a covered area to protect them from large hail and flying debris.
-Rationale: Ping-pong ball sized hail (3.5 cm) and 120 km/h winds can cause severe damage to vehicles if left exposed.
-[P3] INDOOR_WATER_PROTECTION: Be aware that heavy rainfall often accompanies tornadoes. While immediate action for overland water is limited during a tornado, understand that your policy has a critical gap for surface overland flood runoff.
-Rationale: Although the primary threat is tornado, heavy rain is possible. Your policy lacks overland water coverage, which is a significant financial vulnerability for potential flood damage.</t>
+Identified Vulnerabilities: semi_detached dwelling, metal roof (15 years old), unfinished basement, NO sump pump
+Identified Gaps: Overland Water Endorsement: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>"URGENT: Tornado Warning for HOM-1020. Seek immediate shelter in basement, away from windows. Move vehicles to cover. Stay safe!"
-(Length: 127 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Seek immediate shelter in the lowest interior room of your home, away from windows, due_to_the_active_tornado_warning.
+Rationale: An active tornado warning indicates extreme danger from damaging winds and potential debris, requiring immediate life-safety action.
+[P2] VEHICLE_PROTECTION: Move all vehicles into a garage or covered area to protect them from large hail (ping-pong ball size) and damaging winds.
+Rationale: Large hail and 120 km/h winds can cause significant damage to vehicles if left exposed.
+[P3] INDOOR_WATER_PROTECTION: Monitor your unfinished basement for any signs of water ingress and be prepared for potential flooding, especially given the lack of a sump pump and uninsured overland water coverage.
+Rationale: Severe thunderstorms often bring heavy rainfall, and without a sump pump and overland water coverage, your unfinished basement is highly vulnerable to water damage.</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Tornado Warning - Seek Shelter Now!
-Body: A tornado is occurring near HOM-1020. Seek immediate shelter in your basement, away from windows. Move vehicles to covered areas. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K28" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as the metal roof, its age of 15 years, and the unfinished basement are accurately reflected in the advisory. The mention of the lack of overland water endorsement is also correct as per the policy details. There are no fabricated or hallucinated claims in the advisory.</t>
-        </is>
-      </c>
-      <c r="M28" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active tornado peril and the dwelling's specific vulnerabilities. The first action prioritizes life safety by advising immediate shelter in the unfinished basement, which is the safest location during a tornado, directly addressing the primary loss driver of windborne debris and structural collapse. The second action is well-tailored to protect vehicles from hail and debris, acknowledging the risk posed by the forecasted hail size and wind speeds. The third action highlights a critical policy gap regarding overland water, which, while not the primary threat, is a relevant consideration given the potential for heavy rain accompanying the storm. Overall, the actions are well-aligned with the peril and the property's structural and policy characteristics, and they are executable within the warning lead time.</t>
-        </is>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P28" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the tornado threat and provide specific, actionable steps: seek shelter in the basement and move vehicles to cover. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions are detailed yet clear, emphasizing the importance of immediate shelter and vehicle protection, with a brief mention of potential flood risks without delving into complex insurance terms.</t>
-        </is>
-      </c>
-      <c r="Q28" s="21" t="n">
-        <v>5</v>
+          <t>"URGENT: Tornado Warning for HOM-1020. Seek immediate shelter. Move vehicles to garage. Monitor basement. Stay safe!"
+(Length: 115 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Tornado Warning &amp; Storm Mitigation Required
+Body: Tornado warning active for your property. Seek immediate shelter. Move vehicles to garage. Monitor basement for flooding. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The tornado warning, wind speed of 120 km/h, and hail size of 3.5 cm are directly matched with the weather alert. The property details such as 'semi_detached dwelling', 'metal roof (15 years old)', 'unfinished basement', and 'NO sump pump' are accurately reflected from the property data. The mention of 'Overland Water Endorsement: Surface overland flood runoff is UNINSURED' is consistent with the ground truth indicating no overland water endorsement. All actions and recommendations are based on the factual data provided, with no hallucinations or fabrications present.</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific tornado hazard and the dwelling's characteristics. The life-safety action to seek shelter in the lowest interior room directly addresses the primary threat of tornadoes, which is critical given the active warning and the potential for damaging winds and debris. The vehicle protection action is pertinent due to the forecasted large hail and high winds, which can cause significant damage to vehicles. Lastly, the indoor water protection action is appropriately tailored to the dwelling's vulnerabilities, specifically the lack of a sump pump and the uninsured overland water gap, highlighting the need to monitor for water ingress in the unfinished basement. These actions are executable within the warning lead time and effectively mitigate the primary loss drivers of the active peril.</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions semantically cover both mandatory actions. The first action advises seeking shelter in the lowest interior room away from windows, which aligns with both seeking shelter on the lowest level and staying away from windows. The additional actions proposed by the agent are logical and relevant to the context of the alert. Moving vehicles to a covered area is a practical measure to protect them from hail and wind damage, and monitoring the basement for water ingress is sensible given the potential for heavy rain accompanying the storm. No illogical actions were identified, and all mandatory actions were addressed, though the first action could have been more explicit about having as many walls between the individual and the exterior as possible. This minor omission results in a score of 4.</t>
+        </is>
+      </c>
+      <c r="R28" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the tornado threat and what actions to take first. It avoids any insurance jargon and fits well within the character limit. The push notification maintains the same clarity and urgency, providing additional context without overwhelming the user. The micro-actions are clear and actionable, with the first two instructions being particularly straightforward. The third instruction is slightly more detailed but remains free of jargon and provides necessary context for potential flooding. Overall, the communication is effective and appropriate for emergency conditions.</t>
+        </is>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="29" ht="135" customHeight="1">
@@ -3103,61 +3467,80 @@
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Asphalt shingle roof (4 years old) susceptible to significant roof load stress from heavy wet snow, Finished basement
-Identified Gaps: Sewer Backup Endorsement: UNINSURED, Overland Water Endorsement: UNINSURED</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from around basement windows and entryways to prevent water ingress from melting snow.
-Rationale: Heavy snowfall can lead to significant snowmelt, and clearing snow away from vulnerable points will reduce the risk of water entering your finished basement, especially given the lack of sewer backup and overland water coverage.
-[P2] INDOOR_WATER_PROTECTION: Monitor for potential ice damming on the roof and eavestroughs.
-Rationale: Heavy wet snow can contribute to ice dam formation, which can cause water to back up under shingles and into your home, leading to interior water damage.
-[P3] INDOOR_WATER_PROTECTION: Ensure downspouts are clear and extended away from the foundation to manage snowmelt runoff effectively.
-Rationale: Properly functioning downspouts will direct melting snow away from your home's foundation, reducing the risk of water pooling and potential basement leaks, which are not covered by your current policy.</t>
+Identified Vulnerabilities: Finished basement, Asphalt shingle roof (potential for heavy snow load and ice damming)
+Identified Gaps: Sewer Backup Endorsement (UNINSURED), Overland Water Endorsement (UNINSURED)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow expected. Clear snow from basement windows/entryways. Monitor for ice dams. Ensure downspouts are clear. Stay safe!"
-(Length: 134 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from around the foundation and basement window wells to prevent water ingress when snow melts.
+Rationale: Heavy snowfall can lead to significant meltwater accumulation around the foundation, increasing the risk of basement flooding, especially with uninsured sewer backup and overland water.
+[P2] INDOOR_WATER_PROTECTION: Monitor for potential ice damming on the roof and consider professional snow removal if accumulation becomes excessive to prevent structural stress and water intrusion.
+Rationale: Heavy, wet snow can cause ice dams on asphalt shingle roofs, leading to water backup under shingles and into the home, and excessive snow load can stress the roof structure.
+[P3] INDOOR_WATER_PROTECTION: Ensure downspouts are clear and extended away from the foundation to direct meltwater away from the house.
+Rationale: Properly functioning downspouts are crucial to divert large volumes of meltwater away from the home's foundation, reducing the risk of basement water damage.</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Snowfall Warning for HOM-1031. Clear snow from foundation &amp; window wells. Monitor roof for ice dams. Stay safe! Info: +1-403-555-1031"
+(Length: 141 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall expected. Clear snow from basement windows/entryways. Monitor for ice dams. Ensure downspouts are clear to prevent water damage.</t>
-        </is>
-      </c>
-      <c r="K29" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the ground truth alert (25-35 cm). The advisory accurately identifies the roof type as 'asphalt shingle' and its age as 4 years, which is consistent with the property data. The mention of a finished basement is also accurate. The coverage gaps for sewer backup and overland water endorsements are correctly identified as uninsured, aligning with the policy details. No unverified features or fabricated metrics are present in the advisory.</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N29" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's vulnerabilities. The first action addresses the risk of water ingress into the finished basement due to snowmelt, which is critical given the uninsured gaps for sewer backup and overland water. The second action on monitoring for ice damming is pertinent as heavy wet snow can lead to ice dams, which are a known risk for water intrusion under shingles. The third action ensures that downspouts are clear and extended, which is crucial for managing snowmelt runoff and preventing water from pooling near the foundation, again addressing the uninsured water damage risks. All actions are executable within the warning lead time and avoid hazardous outdoor work during the snowfall.</t>
-        </is>
-      </c>
-      <c r="O29" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P29" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both concise, clear, and actionable. They immediately inform the homeowner of the threat (heavy snow) and provide specific actions to mitigate potential damage (clear snow, monitor ice dams, ensure downspouts are clear). The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions are detailed yet clear, providing step-by-step guidance without overwhelming the reader.</t>
-        </is>
-      </c>
-      <c r="Q29" s="21" t="n">
+Body: Heavy snowfall expected for your property. Clear snow from foundation and window wells. Monitor roof for ice damming. Ensure downspouts are clear.</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the ground truth alert (25-35 cm). The advisory does not mention wind gusts or hail, aligning with the absence of such data in the alert. The vulnerabilities and coverage gaps are accurately identified: the finished basement and asphalt shingle roof are noted, and the lack of sewer backup and overland water endorsements is correctly highlighted. The micro-actions are reasonable and based on the potential risks associated with heavy snowfall, such as water ingress and ice damming, which are consistent with the alert's mention of hazardous conditions. No fabricated or unverified information is present.</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's vulnerabilities. The first action addresses the risk of basement flooding due to meltwater accumulation, which is critical given the uninsured gaps for sewer backup and overland water. The second action targets the risk of ice damming and excessive snow load on the relatively new asphalt shingle roof, which could lead to structural damage and water intrusion. The third action ensures that meltwater is directed away from the foundation, further mitigating the risk of basement flooding. All actions are executable within the warning lead time and avoid dangerous outdoor work during the snowfall event.</t>
+        </is>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover all the mandatory reference actions. 
+1. The action to "Clear snow from around the foundation and basement window wells" directly addresses the need to prevent meltwater seepage into the home, covering the first mandatory action.
+2. The action to "Monitor for potential ice damming on the roof" and consider professional snow removal addresses the need to monitor for signs of ice damming and heavy snow load strain, covering the second mandatory action.
+3. The action to "Ensure downspouts are clear and extended away from the foundation" directly addresses the need to ensure downspouts and drainage routes are clear, covering the third mandatory action.
+All actions are logical, practical, and appropriate for the dwelling type and the specific weather alert, with no illogical or ungrounded actions proposed.</t>
+        </is>
+      </c>
+      <c r="R29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the snowfall threat and specific actions to take: clearing snow from the foundation and window wells, and monitoring the roof for ice dams. It avoids any insurance jargon and stays within the character limit, making it highly effective for quick comprehension during an emergency. The push notification complements the SMS by providing additional context and instructions without overwhelming the user. The micro-actions are clear and actionable, providing detailed steps without using technical language, ensuring homeowners understand what to do to mitigate risks.</t>
+        </is>
+      </c>
+      <c r="T29" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3204,62 +3587,81 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Significant roof load stress from heavy wet snow, Potential for meltwater pooling around foundation due to lack of sump pump and backwater valve
+Identified Vulnerabilities: Potential for significant roof load stress from heavy wet snow, Unfinished basement with no sump pump or backwater valve (though covered by policy)
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Safely clear heavy snow from your roof to prevent structural stress and potential collapse. If you cannot do this safely yourself, consider hiring a professional.
-Rationale: Heavy snowfall (35 cm) can accumulate rapidly, placing significant stress on your roof structure, especially with wet snow.
-[P2] INDOOR_WATER_PROTECTION: Clear snow away from your home's foundation, window wells, and any drainage points to prevent meltwater from pooling and potentially seeping into your basement.
-Rationale: With no sump pump or backwater valve, proper exterior drainage is crucial to prevent water ingress from significant snowmelt.
-[P3] LIFE_SAFETY: Be prepared for potential power outages due to tree limb breakage from heavy snow accumulation. Have an emergency kit ready with flashlights, blankets, and a charged phone.
-Rationale: Heavy, wet snow can cause tree limbs to break and fall on power lines, leading to outages.</t>
-        </is>
-      </c>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: 35cm snow expected. Safely clear roof snow to prevent damage. Clear snow from foundation. Prepare for power outages. Stay safe!"
-(Length: 135 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from around basement windows and entryways to prevent water ingress during melt.
+Rationale: Heavy snowfall can lead to water seepage into the basement if snow accumulates against the foundation and melts.
+[P2] INDOOR_WATER_PROTECTION: Monitor for ice damming on the roof and safely remove snow from lower roof edges if accessible from the ground to prevent water backup under shingles.
+Rationale: Ice dams can cause water to back up under roof coverings, leading to leaks and interior water damage.
+[P3] INDOOR_WATER_PROTECTION: Ensure downspouts are clear and extended away from the foundation to direct meltwater effectively.
+Rationale: Proper drainage prevents meltwater from pooling around the foundation, reducing the risk of basement water intrusion.</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy snow expected. Clear snow from basement windows &amp; ensure downspouts are clear. Monitor for ice dams. Stay safe!"
+(Length: 125 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Snowfall Mitigation Required
-Body: 35cm of heavy snow expected. Safely clear roof snow to prevent damage. Clear snow from foundation. Prepare for power outages.</t>
-        </is>
-      </c>
-      <c r="K30" s="21" t="n">
+Body: Heavy snowfall expected. Clear snow from basement windows and entryways. Monitor for ice damming and ensure downspouts are clear.</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M30" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the ground truth alert (25 to 35 cm). The advisory accurately reflects the property's unfinished basement and lack of a sump pump or backwater valve, consistent with the ground truth. The vulnerabilities and micro-actions are appropriate and do not introduce any unverified features or metrics. There is no mention of wind gusts or hail, which aligns with the absence of such data in the ground truth. Overall, the advisory is faithful to the provided information without any hallucination or fabrication.</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is mostly faithful to the ground truth with minor imprecision. The snowfall amount of 35 cm is within the range provided (25-35 cm) in the alert, which is acceptable. The advisory correctly identifies the lack of a sump pump and backwater valve, aligning with the property data. However, it mentions 'potential for meltwater pooling around foundation due to lack of sump pump and backwater valve,' which is slightly misleading since the property does have a sewer backup endorsement, though this does not directly contradict the lack of a sump pump or backwater valve. The advisory's actions and rationale are consistent with the alert's description of risks from heavy snow. Overall, the advisory is factually grounded with minor descriptive liberties.</t>
-        </is>
-      </c>
-      <c r="M30" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's characteristics. The first action addresses the primary loss driver of roof stress due to heavy snow accumulation, which is particularly relevant given the metal roof's age and the potential for significant snow load. The recommendation to hire a professional if necessary ensures safety, avoiding dangerous roof work. The second action targets the risk of water ingress due to snowmelt, which is critical given the lack of a sump pump or backwater valve, despite the policy covering overland water. The third action addresses life safety by preparing for power outages, a common consequence of heavy snow causing tree limb breakage. Overall, these actions are executable within the warning lead time and directly mitigate the specific risks posed by the snowfall event.</t>
-        </is>
-      </c>
-      <c r="O30" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P30" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the snow threat and what actions to take first. It avoids any insurance jargon and is well within the character limit. The push notification maintains the same clarity and urgency, with a slightly expanded format that remains free of jargon. The micro-actions provide detailed, actionable steps without overwhelming the reader, maintaining clarity and avoiding technical language. Overall, the communication is direct, actionable, and easy to understand in an emergency.</t>
-        </is>
-      </c>
-      <c r="Q30" s="21" t="n">
-        <v>4.67</v>
+      <c r="O30" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are generally well-aligned with the primary loss drivers of the heavy snowfall peril, such as roof load stress and potential water ingress during melt. The actions are tailored to the dwelling's structural features, such as the unfinished basement, and the policy's coverage gaps, although the dwelling is covered for sewer backup and overland water. 
+1. Clearing snow from around basement windows and entryways is relevant to prevent water ingress during melt, although the basement is unfinished, reducing potential damage severity.
+2. Monitoring for ice damming and removing snow from lower roof edges is relevant, but the metal roof is less susceptible to ice damming compared to asphalt shingles, which slightly reduces the action's necessity.
+3. Ensuring downspouts are clear and extended is a good preventive measure for water management, although the dwelling is covered for overland water, reducing the criticality of this action.
+Overall, the actions are relevant and mostly tailored, but some minor adjustments could enhance their specificity to the dwelling's features and policy coverage.</t>
+        </is>
+      </c>
+      <c r="P30" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions fully cover all the mandatory reference actions. The first action addresses clearing snow from basement windows and entryways, aligning with the need to prevent meltwater seepage into the home. The second action involves monitoring for ice damming and removing snow from roof edges, which corresponds to monitoring for signs of ice damming and heavy snow load strain. The third action ensures downspouts are clear and extended, matching the requirement to keep drainage routes clear to direct meltwater away from the foundation. All actions are logical, practical, and appropriate for the dwelling type and weather conditions described in the alert.</t>
+        </is>
+      </c>
+      <c r="R30" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S30" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and free of jargon. They immediately inform the homeowner of the threat (heavy snow) and provide specific actions to take (clear snow from basement windows, ensure downspouts are clear, monitor for ice dams). The tone is urgent but not panicky, and the instructions are actionable and easy to understand. The SMS is within the character limit, maximizing impact. The micro-actions provide detailed, step-by-step guidance without using technical language, ensuring homeowners can easily follow them during an emergency.</t>
+        </is>
+      </c>
+      <c r="T30" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="31" ht="135" customHeight="1">
@@ -3305,62 +3707,77 @@
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Roof load stress due to heavy wet snow on 12-year-old slate roof, Potential for tree limb breakage onto power lines causing outages
+Identified Vulnerabilities: Heavy wet snow load on 12-year-old slate roof, Crawlspace basement susceptible to water ingress from melting snow
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Monitor your roof for excessive snow accumulation. If snow load appears significant, consider hiring a professional for safe snow removal to prevent structural stress.
-Rationale: Heavy wet snow can cause significant stress on your roof, potentially leading to damage. Professional removal is recommended for safety.
-[P2] INDOOR_WATER_PROTECTION: Ensure eaves and downspouts are clear of snow and ice to prevent ice damming and allow for proper drainage when snow melts.
-Rationale: Blocked eaves and downspouts can lead to ice dams, causing water to back up and potentially leak into your home.
-[P3] LIFE_SAFETY: Prepare an emergency kit with flashlights, blankets, and non-perishable food in case of power outages caused by tree limbs breaking under snow load.
-Rationale: Heavy snow can cause tree branches to fall on power lines, leading to electricity disruptions. Being prepared ensures your safety and comfort.</t>
-        </is>
-      </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Snowfall warning for HOM-1033. Monitor roof snow load and clear eaves. Prepare for potential power outages. Stay safe!"
-(Length: 126 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Safely clear heavy snow from your roof if accumulation exceeds 15 cm, or arrange for professional snow removal to prevent structural stress.
+Rationale: Heavy wet snow can cause significant roof load stress, especially on older roofs, leading to potential damage.
+[P2] INDOOR_WATER_PROTECTION: Clear snow accumulation from around your home's foundation, especially near the crawlspace, and ensure proper drainage to prevent water ingress when snow melts.
+Rationale: Melting snow can lead to water pooling around the foundation, potentially entering the crawlspace and causing damage.
+[P3] LIFE_SAFETY: Monitor local utility reports for power outages and prepare an emergency kit, as heavy snow can cause tree limbs to break and damage power lines.
+Rationale: Heavy snowfall increases the risk of tree limb breakage and power outages, impacting home safety and comfort.</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall expected for your property. Monitor roof snow load, clear eaves, and prepare for potential power outages. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K31" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning accurately reflects the alert's expected accumulation of 35 cm. The vulnerabilities mentioned, such as roof load stress and potential tree limb breakage, are directly supported by the alert text. The property details, including the 12-year-old slate roof and the presence of a sump pump, are consistent with the ground truth. No unverified claims or hallucinations are present in the advisory.</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's characteristics. The first action addresses the primary loss driver of roof stress due to heavy snow accumulation, which is particularly important given the townhouse's slate roof. It wisely recommends professional removal to avoid life-safety risks. The second action targets the risk of ice damming, a common issue with heavy snow, and is crucial for preventing water intrusion, especially since the dwelling has a crawlspace and no backwater valve. The third action is a prudent life-safety measure, preparing for power outages due to tree limb breakage, which is a realistic threat in this scenario. All actions are executable within the warning lead time and directly mitigate the specific damage mechanisms of the snowfall peril.</t>
-        </is>
-      </c>
-      <c r="O31" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P31" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the threat (snowfall) and provide actionable steps (monitor roof snow load, clear eaves, prepare for power outages). The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions provide detailed, jargon-free instructions that are easy to follow, enhancing the overall clarity and effectiveness of the communication.</t>
-        </is>
-      </c>
-      <c r="Q31" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: Heavy snow (35cm) expected. Safely clear roof snow or get professional help to prevent damage. Monitor for power outages. Stay safe!"
+(Length: 140 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Heavy Snowfall Warning
+Body: Heavy snowfall (35cm) expected. Safely clear roof snow to prevent structural stress. Clear snow from foundation. Monitor for power outages.</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the ground truth alert. The advisory does not mention wind gusts or hail, aligning with the absence of such data in the alert. The vulnerabilities and micro-actions are consistent with the property details: the roof is 12 years old and made of slate, and the property has a crawlspace basement, both of which are accurately reflected in the advisory. The advisory's actions and rationale are directly supported by the alert's mention of heavy snow causing roof stress and potential water ingress. No fabricated numbers or phantom features are present.</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril of heavy snowfall and the dwelling's characteristics. The first action directly addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is particularly relevant given the slate roof's age. It also wisely suggests professional removal to avoid life-safety risks. The second action targets potential water ingress into the crawlspace, a critical vulnerability given the lack of a backwater valve, and is proactive in preventing water damage from snowmelt. The third action addresses life safety by preparing for power outages due to tree limb breakage, which is a realistic threat in this scenario. All actions are executable within the warning lead time and are well-aligned with the dwelling's structural vulnerabilities and policy coverage.</t>
+        </is>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory actions. The action to clear snow accumulation from around the home's foundation addresses the need to prevent meltwater seepage into the home, aligning with the first mandatory action. The suggestion to ensure proper drainage indirectly covers the need to keep downspouts and drainage routes clear, satisfying the third mandatory action. However, the agent did not include an action to monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming or moisture leaks, which is a key aspect of the second mandatory action. The additional action regarding monitoring utility reports and preparing for power outages is logical and relevant given the alert's mention of potential tree limb breakage onto power lines. No illogical actions were proposed.</t>
+        </is>
+      </c>
+      <c r="R31" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S31" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy snow) and provides actionable steps (clear roof snow or get help, monitor power outages). It is free of insurance jargon and complies with the character limit. The push notification is similarly clear, with a slightly expanded explanation that remains free of jargon and maintains urgency. The micro-actions are detailed yet straightforward, providing clear instructions without unnecessary complexity or technical language.</t>
+        </is>
+      </c>
+      <c r="T31" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="32" ht="135" customHeight="1">
@@ -3406,62 +3823,79 @@
       </c>
       <c r="G32" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy wet snow accumulation from private balconies and sliding door thresholds to reduce structural load and prevent meltwater seepage into the living unit
+• Monitor interior window frames, doors, and exterior walls for signs of moisture seepage or water leaks as snow melts
+• Ensure balcony drains and scuppers remain clear of snow and ice to allow proper drainage of meltwater</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: tar_and_gravel roof (16 years old) susceptible to heavy snow load, highrise_condo with balconies/common areas requiring snow management
-Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from balconies, patios, and common areas to prevent excessive accumulation and potential water ingress from melting snow.
-Rationale: Heavy snowfall can lead to significant snow load on balconies and common areas. Clearing snow reduces the risk of structural stress and prevents water from pooling and potentially entering the dwelling when it melts, especially given the lack of overland water coverage.
-[P2] INDOOR_WATER_PROTECTION: Monitor for any signs of water ingress around windows, doors, and exterior walls as snow melts, and report any leaks immediately.
-Rationale: With heavy snowfall and an uninsured overland water gap, it's crucial to proactively check for water intrusion points that could lead to damage from melting snow.
-[P3] INDOOR_WATER_PROTECTION: Ensure all balcony drains and downspouts are clear of snow and ice to allow for proper drainage of melting snow.
-Rationale: Blocked drains can cause water to back up and potentially enter the dwelling or cause damage to the building structure as heavy snow melts.</t>
+Identified Vulnerabilities: highrise_condo, tar_and_gravel roof (16 years old) susceptible to heavy snow load
+Identified Gaps: Overland Water Endorsement: NO - Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow expected. Clear snow from balconies &amp; ensure drains are clear to prevent water damage. Monitor for leaks. Stay safe!"
-(Length: 135 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear heavy snow from balconies and accessible common areas to reduce structural load and prevent water ingress when snow melts.
+Rationale: Heavy wet snow can cause significant roof/balcony load stress and lead to water intrusion as it melts, especially for older roofs.
+[P2] INDOOR_WATER_PROTECTION: Monitor for any signs of water leakage or dampness around windows, balcony doors, and interior walls as snow accumulates and melts.
+Rationale: Melting snow can find pathways into the dwelling, causing interior water damage.
+[P3] INDOOR_WATER_PROTECTION: Be vigilant for surface runoff and potential overland flooding once the snow begins to melt, as your policy lacks overland water coverage.
+Rationale: Rapid snowmelt can lead to significant surface water accumulation and potential flooding, which is not covered by your current policy.</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall (up to 35 cm) expected. Clear snow from balconies/common areas &amp; ensure drains are clear to prevent water damage. Monitor for leaks. Your overland water coverage is limited.</t>
-        </is>
-      </c>
-      <c r="K32" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L32" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the ground truth alert text. The property details such as the dwelling type ('highrise_condo'), roof type ('tar_and_gravel'), and roof age (16 years) are accurately reflected in the advisory. The advisory correctly identifies the lack of overland water endorsement as a coverage gap, which is consistent with the ground truth policy details. No unverified features or fabricated numbers are present in the advisory.</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's characteristics. The actions focus on preventing water ingress and structural stress due to snow accumulation, which are primary concerns for a highrise condo during heavy snowfall. The emphasis on clearing snow from balconies and ensuring proper drainage directly addresses the risk of water damage, especially given the uninsured gap for overland water. Monitoring for water ingress is also crucial due to the potential for melting snow to cause leaks. These actions are executable within the warning lead time and avoid any dangerous outdoor work, aligning perfectly with the dwelling's vulnerabilities and policy gaps.</t>
-        </is>
-      </c>
-      <c r="O32" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P32" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and actionable, providing immediate instructions on what the threat is (heavy snow) and what to do first (clear snow and ensure drains are clear). It is urgent without causing panic and free of insurance jargon, complying with the character limit. The push notification is similarly clear, with a slightly more detailed context about the snowfall amount, and the mention of limited coverage is brief and not overly technical. The micro-actions are straightforward, providing clear steps without jargon, ensuring homeowners know exactly what to do.</t>
-        </is>
-      </c>
-      <c r="Q32" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: Heavy snow expected. Clear balconies to prevent water issues. Monitor for leaks. Overland water not covered. Stay safe!"
+(Length: 127 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Snowfall Warning - Mitigation Required
+Body: Heavy snow expected. Clear balconies to prevent water issues. Monitor for leaks. Be aware of overland water risk (uninsured).</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the ground truth alert text. The property details, such as the dwelling type ('highrise_condo') and roof type ('tar_and_gravel' with 16 years age), are accurately reflected in the advisory. The advisory correctly notes the lack of overland water endorsement, aligning with the ground truth policy details. No unverified features or fabricated metrics are present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N32" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant to the active snowfall hazard and the specific dwelling type. The actions focus on mitigating the primary loss drivers associated with heavy snowfall, such as structural load stress and potential water ingress. The first action addresses the risk of structural load on balconies, which is pertinent given the highrise condo setting and the older tar and gravel roof. The second action is relevant for detecting early signs of water intrusion, which is crucial for preventing interior damage. The third action highlights the policy gap regarding overland water, which is important given the risk of rapid snowmelt. However, the actions could be slightly more tailored by considering the specific vulnerabilities of the tar and gravel roof in more detail, such as potential drainage issues. Overall, the actions are well-aligned with the peril and property characteristics, warranting a score of 4.</t>
+        </is>
+      </c>
+      <c r="P32" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory reference actions. The action to clear heavy snow from balconies addresses the need to reduce structural load and prevent water ingress, matching the first mandatory action. The action to monitor for signs of water leakage around windows and doors aligns with the second mandatory action regarding monitoring for moisture seepage.
+However, the agent did not address the need to ensure balcony drains and scuppers remain clear, which is a specific requirement in the third mandatory action. This omission results in a deduction.
+The additional action regarding vigilance for surface runoff and potential overland flooding is logical and relevant given the context of rapid snowmelt, even though it is not explicitly required by the mandatory actions. It does not contradict any property facts or the alert context, so it is not penalized as illogical.</t>
+        </is>
+      </c>
+      <c r="R32" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is clear and concise, effectively communicating the urgency of the situation and the immediate actions required (clearing balconies and monitoring for leaks). It avoids insurance jargon, though the mention of 'overland water not covered' could be slightly confusing without context. The push notification maintains clarity and urgency, but the phrase 'overland water risk (uninsured)' might not be immediately clear to all users. The micro-actions are detailed and clear, though slightly wordy for an emergency context. Overall, the communications are effective but could be slightly refined for maximum clarity and impact.</t>
+        </is>
+      </c>
+      <c r="T32" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="33" ht="135" customHeight="1">
@@ -3507,62 +3941,77 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 20-year-old asphalt shingle roof susceptible to heavy snow load, No backwater valve (general vulnerability, not directly snow-related)
-Identified Gaps: Sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Safely clear heavy snow accumulation from your roof to prevent structural stress and potential collapse.
-Rationale: Heavy snowfall (up to 35 cm) can exceed your 20-year-old asphalt shingle roof's load capacity, leading to damage.
-[P2] INDOOR_WATER_PROTECTION: Ensure eavestroughs and downspouts are clear of snow and ice to prevent ice damming and water intrusion.
-Rationale: Blocked drainage systems can lead to ice dams, forcing meltwater into your home's interior.
-[P3] LIFE_SAFETY: Prepare for potential power outages due to tree limb breakage from heavy snow; have emergency supplies ready.
-Rationale: Heavy, wet snow can cause tree limbs to break and fall on power lines, disrupting electricity.</t>
+Identified Vulnerabilities: Asphalt shingle roof (20 years old) susceptible to heavy snow load, Finished basement
+Identified Gaps: Sewer Backup Endorsement: NO - Basement sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow (35cm) expected. Safely clear roof snow to prevent damage. Prepare for power outages. Info: +1-403-555-1035"
-(Length: 126 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Monitor snow accumulation on your roof. If safe to do so, clear heavy snow to prevent structural stress, or consider hiring a professional.
+Rationale: Heavy snowfall (25-35 cm) can lead to significant roof load stress, especially on an older asphalt shingle roof (20 years old).
+[P2] VEHICLE_PROTECTION: Park vehicles in a garage or covered area to protect them from heavy snow and potential falling tree limbs.
+Rationale: Rapidly accumulating wet heavy snow creates hazardous driving conditions and increases the risk of tree limb breakage onto power lines.
+[P3] INDOOR_WATER_PROTECTION: Be aware of the critical gap in your policy regarding sewer backup and consider contacting your insurer to discuss adding this endorsement.
+Rationale: Your finished basement is vulnerable to sewer backup, and your policy currently does not cover this, representing a significant financial risk.</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall (35cm) expected. Safely clear roof snow to prevent structural damage. Ensure eavestroughs are clear. Prepare for power outages.</t>
-        </is>
-      </c>
-      <c r="K33" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning specifies accumulations between 25 and 35 cm, and the advisory accurately reflects the upper limit of 35 cm. The property details, such as the 20-year-old asphalt shingle roof and lack of a backwater valve, are correctly stated. The advisory does not introduce any unverified claims or fabricated numbers. All actions and vulnerabilities mentioned are consistent with the ground truth data and the nature of the snowfall warning.</t>
-        </is>
-      </c>
-      <c r="M33" s="21" t="n">
+          <t>"Urgent: Heavy snow (up to 35cm) expected. Clear roof if safe, park vehicles in garage. Your basement sewer backup is uninsured. Stay safe!"
+(Length: 138 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Snowfall Warning - Mitigation Required
+Body: Heavy snow (up to 35cm) expected. Clear roof if safe, park vehicles in garage. Review your policy for uninsured sewer backup.</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning accurately reflects the alert's specified accumulation of 25-35 cm. The advisory correctly identifies the roof as asphalt shingle and 20 years old, matching the property data. It also accurately notes the lack of sewer backup endorsement, consistent with the policy details. No unverified claims or hallucinations are present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N33" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's vulnerabilities. The first action directly addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is particularly pertinent given the 20-year-old asphalt shingle roof. It also wisely suggests professional help to avoid life-safety risks. The second action mitigates the risk of vehicle damage from falling tree limbs and heavy snow, aligning with the peril's potential impacts. The third action highlights a critical policy gap regarding sewer backup, which is crucial given the finished basement, and suggests a proactive measure to address this vulnerability. Overall, the actions are executable within the warning lead time and effectively target the dwelling's specific risks and policy gaps.</t>
+        </is>
+      </c>
+      <c r="P33" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions do not semantically cover any of the mandatory reference actions. The first action about monitoring and clearing snow from the roof does not address the specific mandatory actions related to basement window wells, interior monitoring for leaks, or ensuring drainage routes are clear. The second action about vehicle protection is logical but unrelated to the mandatory actions focused on property protection from snow-related water damage. The third action about insurance policy gaps is illogical in the context of immediate snow hazard mitigation, as it does not address any physical action to prevent damage from the snowfall. Therefore, the score is 2 due to the complete omission of mandatory actions and the inclusion of an illogical additional action.</t>
+        </is>
+      </c>
+      <c r="R33" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant to the active snowfall hazard and the dwelling's specific vulnerabilities. The first action addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is critical given the 20-year-old asphalt shingle roof. However, it involves potentially dangerous outdoor work during heavy snowfall, which could be risky. The second action is well-aligned with preventing ice damming, a common issue with snow and ice, but it assumes the homeowner can safely clear eavestroughs during the storm, which may not be practical. The third action is appropriate for life safety, preparing for power outages due to snow-laden tree limbs. Overall, the actions are well-targeted but could be improved by emphasizing safety and practicality in execution.</t>
-        </is>
-      </c>
-      <c r="O33" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P33" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (heavy snow) and the first action to take (clear roof snow). It avoids jargon and is well within the character limit. The push notification is similarly clear, with a direct title and body that expands slightly on the SMS by adding the importance of clearing eavestroughs. The micro-actions are straightforward, providing clear, actionable steps without using technical language. Overall, the communications are effective, urgent without causing panic, and free of insurance jargon.</t>
-        </is>
-      </c>
-      <c r="Q33" s="21" t="n">
-        <v>4.67</v>
+      <c r="S33" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and mostly clear, effectively communicating the threat of heavy snow and immediate actions to take. It avoids insurance jargon, though the mention of 'uninsured' could cause slight concern without immediate context. The push notification is clear but slightly wordy, especially with the phrase 'Review your policy for uninsured sewer backup,' which could be simplified. The micro-actions are clear and actionable, though the last point introduces some insurance terminology ('endorsement') that could be simplified for clarity. Overall, the messages are effective but could be slightly refined for maximum clarity and impact.</t>
+        </is>
+      </c>
+      <c r="T33" s="21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34" ht="135" customHeight="1">
@@ -3608,62 +4057,77 @@
       </c>
       <c r="G34" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Metal roof (24 years old) susceptible to heavy snow load stress
+Identified Vulnerabilities: 24-year-old metal roof susceptible to heavy snow load, Unfinished basement (though covered for water perils)
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: If safe to do so, clear heavy snow from your roof to prevent structural damage and potential leaks from excessive load.
-Rationale: Heavy snowfall (35 cm) can cause significant stress on your 24-year-old metal roof, leading to structural issues or leaks.
-[P2] INDOOR_WATER_PROTECTION: Ensure eavestroughs and downspouts are clear of snow and ice to allow for proper drainage when snow melts, preventing water backup.
-Rationale: Blocked eavestroughs and downspouts can lead to water pooling and potential ice damming, increasing the risk of water ingress into your home.
-[P3] INDOOR_WATER_PROTECTION: Regularly check for ice damming and large icicles around your eaves, as these can indicate water buildup and potential roof damage.
-Rationale: Ice dams can force melting snow under your roof shingles, causing leaks and water damage inside your home.</t>
-        </is>
-      </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow (35cm) expected. Safely clear snow from your roof to prevent damage. Check eaves for ice dams. Stay safe!"
-(Length: 124 / 160 chars)</t>
+          <t>[P1] INDOOR_SHELTER: Regularly monitor snow accumulation on your roof to prevent excessive load and potential structural stress.
+Rationale: Heavy wet snow can cause significant roof load stress, especially on older roofs. Monitoring helps prevent structural damage.
+[P2] INDOOR_WATER_PROTECTION: Clear snow away from your home's foundation and all egress points to prevent water ingress during melt and ensure clear exits.
+Rationale: As snow melts, water can accumulate around the foundation, potentially leading to water ingress. Clearing snow helps direct water away.
+[P3] LIFE_SAFETY: Prepare an emergency kit with essentials like flashlights, blankets, and non-perishable food in case of power outages.
+Rationale: Heavy snowfall can lead to tree limb breakage onto power lines, causing power disruptions.</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: 35cm snow expected. Monitor roof snow load &amp; clear snow from foundation. Prepare for power outages. Stay safe! #SnowSafety"
+(Length: 130 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall (35cm) expected. Safely clear snow from your roof to prevent damage. Ensure eavestroughs are clear and monitor for ice dams.</t>
-        </is>
-      </c>
-      <c r="K34" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning specifies accumulations between 25 and 35 cm, and the advisory accurately uses the upper limit of 35 cm for its hazard summary and micro-actions. The property details, such as the 24-year-old metal roof and lack of a sump pump, are correctly reflected in the advisory. There are no fabricated or hallucinated claims about wind, hail, or other perils not mentioned in the ground truth. The advisory's actions and rationale are consistent with the potential impacts of heavy snowfall as described in the alert text, such as roof load stress and the need to clear snow to prevent structural damage. Overall, the advisory maintains complete fidelity to the ground truth data.</t>
-        </is>
-      </c>
-      <c r="M34" s="21" t="n">
+Body: Heavy snowfall (35cm) expected. Monitor roof snow load, clear snow from foundation, and prepare for potential power outages. Stay safe.</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states an expected accumulation of 35 cm, which matches the upper limit of the 25-35 cm range in the alert. The advisory does not mention wind gusts, hail, or rainfall, which aligns with the absence of such data in the alert. The property details, such as the 24-year-old metal roof and unfinished basement, are accurately reflected from the property data. The micro-actions are reasonable and based on the alert's mention of heavy snow causing roof stress and potential power outages due to tree limb breakage. No fabricated or hallucinated information is present.</t>
+        </is>
+      </c>
+      <c r="N34" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant to the active snowfall hazard and the dwelling's specific vulnerabilities. The first action addresses the potential for structural damage due to heavy snow load on the 24-year-old metal roof, which is a primary concern given the expected snow accumulation. However, it should emphasize safety and recommend professional assistance if necessary, as clearing snow from roofs can be dangerous. The second action is relevant as it targets the risk of water backup due to blocked eavestroughs and downspouts, which is pertinent given the potential for rapid snowmelt. The third action on monitoring for ice damming is also relevant, as ice dams can lead to water ingress and roof damage. While these actions are well-aligned with the peril, they could be slightly more tailored by explicitly advising against dangerous roof work during the storm and suggesting professional services for snow removal.</t>
-        </is>
-      </c>
-      <c r="O34" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P34" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without causing panic. It immediately informs the homeowner of the threat (heavy snow) and the first action to take (clear snow from the roof). It avoids any insurance jargon and is well within the character limit. The push notification maintains the same clarity and urgency, providing additional context without overwhelming the reader. The micro-actions are clear, actionable, and free of jargon, providing step-by-step guidance on what to do, ensuring the homeowner understands the importance of each action.</t>
-        </is>
-      </c>
-      <c r="Q34" s="21" t="n">
-        <v>4.67</v>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant to the active snowfall hazard and the dwelling's characteristics. The first action addresses the primary loss driver of roof load stress due to heavy snow, which is pertinent given the age of the metal roof. However, it lacks specific guidance on safe monitoring practices, especially considering the potential danger of accessing the roof in snowy conditions. The second action is relevant for preventing water ingress during snowmelt, although the dwelling's unfinished basement and coverage for overland water reduce the urgency. The third action is well-aligned with life safety concerns due to potential power outages from tree limb breakage. Overall, the actions are well-aligned with the peril and property, but minor tailoring improvements could enhance their effectiveness.</t>
+        </is>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to "Clear snow away from your home's foundation and all egress points" semantically matches the requirement to clear snow from basement window wells, exterior entryways, and foundation perimeters. The action to "Regularly monitor snow accumulation on your roof" partially addresses the need to monitor for heavy snow load strain, but it does not explicitly cover monitoring interior ceilings, rooflines, and upper-floor walls for signs of ice damming or moisture leaks. The additional action of preparing an emergency kit is logical and relevant given the potential for power outages due to tree limb breakage onto power lines, as mentioned in the alert text. No illogical actions were identified.</t>
+        </is>
+      </c>
+      <c r="R34" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, effectively communicating the threat (heavy snowfall) and immediate actions (monitor roof, clear foundation, prepare for outages) without any jargon. It stays well within the character limit, ensuring quick readability. The push notification mirrors this clarity, providing a slightly expanded version that maintains urgency and clarity. The micro-actions are straightforward, actionable, and free of technical language, making them easy to understand and follow in an emergency.</t>
+        </is>
+      </c>
+      <c r="T34" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="35" ht="135" customHeight="1">
@@ -3709,62 +4173,77 @@
       </c>
       <c r="G35" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Roof load stress from heavy wet snow, Potential tree limb breakage onto power lines
-Identified Gaps: Overland Water Endorsement: UNINSURED for surface overland flood runoff</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: If safe to do so, clear heavy snow from your roof to prevent structural damage from excessive weight.
-Rationale: Heavy wet snow can cause significant roof load stress, potentially leading to structural damage.
-[P2] INDOOR_WATER_PROTECTION: Clear snow away from your home's foundation, drains, and downspouts to prevent potential overland flooding when the snow melts, as you lack overland water coverage.
-Rationale: Rapid snowmelt can lead to surface overland flood runoff, which is not covered by your policy.
-[P3] LIFE_SAFETY: Monitor local news and utility updates for power outages due to tree limb breakage from heavy snow accumulation.
-Rationale: Heavy snow can cause tree limbs to break and fall on power lines, leading to outages.</t>
+Identified Vulnerabilities: Significant roof load stress from heavy snow, Potential tree limb breakage onto power lines
+Identified Gaps: Overland Water Endorsement is UNINSURED</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow expected. Clear snow from roof if safe &amp; away from foundation. Monitor for power outages. Stay safe!"
-(Length: 119 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow accumulation from around your home's foundation and egress windows to prevent water intrusion when snow melts, especially given the lack of overland water coverage.
+Rationale: Heavy snowfall and subsequent melting can lead to overland flooding, which is not covered by your policy. Clearing snow away from the foundation mitigates this risk.
+[P2] INDOOR_SHELTER: Monitor for power outages due to heavy snow causing tree limb breakage on power lines. Have an emergency kit ready with flashlights, blankets, and a charged phone.
+Rationale: Heavy, wet snow can cause tree branches to break and fall on power lines, leading to outages. Being prepared ensures your safety and comfort.
+[P3] LIFE_SAFETY: If snow accumulation on your roof becomes excessive, consider contacting a professional to safely remove it to prevent structural stress. Do NOT attempt to clear the roof yourself due to safety risks.
+Rationale: Significant snow load can stress your roof structure. Professional removal is recommended to ensure safety and prevent damage.</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Warning - Mitigation Required
-Body: Heavy snow expected. Clear snow from roof if safe &amp; away from foundation. Monitor for power outages. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K35" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the 25-35 cm range in the alert. The vulnerabilities mentioned, such as roof load stress and potential tree limb breakage, are directly cited from the alert text. The coverage gap regarding the lack of overland water endorsement is accurately reflected from the property data. All micro-actions are logically derived from the alert's implications and the property's insurance coverage details. No unverified claims or hallucinations are present.</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="n">
+          <t>"Urgent: Heavy snow (35cm) expected. Clear snow from foundation to prevent water damage. Monitor for power outages. Stay safe! #SnowSafety"
+(Length: 137 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Heavy Snowfall Warning
+Body: Heavy snowfall (35cm) expected. Clear snow from your foundation to prevent water damage. Monitor for power outages and stay safe.</t>
+        </is>
+      </c>
+      <c r="L35" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the range provided in the weather alert (25 to 35 cm). The advisory does not mention wind gusts or hail, which aligns with the absence of such data in the alert. The vulnerabilities and micro-actions are consistent with the alert's mention of roof load stress and potential tree limb breakage. The advisory accurately notes the lack of overland water endorsement, which is confirmed by the property data. All contact information and property details are correctly reflected from the ground truth. There are no fabricated or hallucinated claims.</t>
+        </is>
+      </c>
+      <c r="N35" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's characteristics. The first action directly addresses the risk of water intrusion due to snowmelt, which is critical given the uninsured gap for overland water. The second action prepares for power outages, a common consequence of heavy snow causing tree limb breakage onto power lines, ensuring life safety and comfort. The third action addresses the structural stress risk from snow accumulation on the roof, recommending professional removal to avoid safety hazards. All actions are executable within the warning lead time and avoid dangerous activities, such as personal roof clearing, aligning with mandatory life-safety requirements.</t>
+        </is>
+      </c>
+      <c r="P35" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant to the active snowfall hazard and the dwelling's specific vulnerabilities. The first action addresses the primary loss driver of roof load stress due to heavy snow, which is pertinent given the townhouse's slate roof, although it should caution against unsafe roof access. The second action is well-tailored to the uninsured overland water gap, focusing on preventing snowmelt infiltration. The third action is relevant for life safety, addressing power outage risks from tree limb breakage. However, the first action could be improved by emphasizing safety precautions or alternative methods for snow removal without direct roof access.</t>
-        </is>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without causing panic. It immediately informs the homeowner of the threat (heavy snow) and provides actionable steps (clear snow from roof and foundation, monitor power outages). The message is free of insurance jargon and complies with the character limit. The push notification maintains the same clarity and urgency, with a clear title and body. The micro-actions are detailed yet straightforward, avoiding technical insurance terms and focusing on practical steps.</t>
-        </is>
-      </c>
-      <c r="Q35" s="21" t="n">
-        <v>4.67</v>
+      <c r="Q35" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory actions. The action to clear snow accumulation from around the foundation and egress windows semantically matches the first mandatory action regarding preventing meltwater seepage. The suggestion to monitor for excessive snow on the roof and contact a professional aligns with monitoring for signs of heavy snow load strain, covering the second mandatory action. However, the agent did not address ensuring that ground-level downspouts and perimeter drainage routes are clear, which is a missed mandatory action. The additional action regarding power outages is logical given the alert's mention of tree limb breakage onto power lines, and no illogical actions were proposed.</t>
+        </is>
+      </c>
+      <c r="R35" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S35" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (heavy snow) and the first action to take (clear snow from foundation). It avoids jargon and fits within the character limit. The push notification maintains clarity and urgency, reiterating the key actions without unnecessary complexity. The micro-actions are detailed yet clear, providing actionable steps without insurance jargon, ensuring homeowners understand the risks and necessary precautions.</t>
+        </is>
+      </c>
+      <c r="T35" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="36" ht="135" customHeight="1">
@@ -3810,62 +4289,77 @@
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy wet snow accumulation from private balconies and sliding door thresholds to reduce structural load and prevent meltwater seepage into the living unit
+• Monitor interior window frames, doors, and exterior walls for signs of moisture seepage or water leaks as snow melts
+• Ensure balcony drains and scuppers remain clear of snow and ice to allow proper drainage of meltwater</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: highrise_condo, tar_and_gravel roof (7 years old) - potential for roof load stress from heavy wet snow
+Identified Vulnerabilities: highrise_condo roof load stress from heavy snow, potential tree limb breakage onto power lines
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow from balconies and common areas to prevent excessive load and potential water ingress when melting.
-Rationale: Heavy wet snow can accumulate on balconies and common areas of a highrise condo, leading to excessive structural load and potential water damage if not cleared, especially during melting.
-[P2] INDOOR_WATER_PROTECTION: Monitor for ice damming around roof drains and ensure proper drainage to prevent water accumulation.
-Rationale: Heavy snowfall on a tar and gravel roof, especially for a highrise, can lead to ice damming around drains, causing water to back up and potentially infiltrate the building envelope.
-[P3] LIFE_SAFETY: Prepare for potential power outages by having an emergency kit with flashlights, blankets, and charged devices.
-Rationale: Heavy wet snow can cause tree limb breakage, leading to power line damage and potential outages, impacting essential services in a highrise building.</t>
-        </is>
-      </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow expected. Clear snow from balconies to prevent load stress &amp; water issues. Prepare for power outages. Stay safe!"
-(Length: 131 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear balconies and ensure drains are free of snow and ice to prevent water accumulation when snow melts.
+Rationale: Heavy snowfall can lead to significant water accumulation on balconies and roofs, potentially causing leaks or structural stress if drains are blocked.
+[P2] LIFE_SAFETY: Monitor for power outages and have an emergency kit ready due to potential tree limb breakage onto power lines.
+Rationale: Wet, heavy snow can cause tree limbs to break and fall on power lines, leading to outages. An emergency kit ensures preparedness.
+[P3] LIFE_SAFETY: If safe to do so, clear snow from any accessible common areas or shared pathways to prevent slip hazards.
+Rationale: Accumulated snow creates slippery surfaces, increasing the risk of falls and injuries in common areas.</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Warning - Highrise Condo
-Body: Heavy snow expected. Clear balconies to prevent load stress &amp; water issues. Monitor roof drains. Prepare for power outages. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K36" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the ground truth alert (25-35 cm). The property is accurately identified as a 'highrise_condo' with a 'tar_and_gravel' roof that is 7 years old, consistent with the ground truth. The advisory does not fabricate any wind, hail, or rainfall data, as these are not mentioned in the ground truth. The micro actions and vulnerabilities are logically derived from the ground truth, focusing on snow load stress and potential power outages due to tree limb breakage, which are mentioned in the alert text. No unverified features or numbers are introduced, ensuring complete faithfulness to the ground truth.</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril of heavy snowfall and the structural characteristics of a highrise condo. The action to clear snow from balconies and common areas directly addresses the risk of excessive load and potential water ingress, which is pertinent given the condo's slab-on-grade foundation and lack of a sump pump. Monitoring for ice damming around roof drains is crucial for a tar and gravel roof, as it prevents water accumulation and potential infiltration, directly targeting the building's vulnerabilities. Preparing for power outages is a critical life-safety measure, considering the risk of tree limb breakage onto power lines. All actions are executable within the warning lead time and address the primary loss drivers effectively.</t>
-        </is>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy snow) and provides actionable steps (clear snow from balconies, prepare for power outages). It is well within the character limit and free of insurance jargon. The push notification maintains the same clarity and urgency, with additional details appropriate for the format. The micro-actions are clear and actionable, providing specific steps without using technical jargon.</t>
-        </is>
-      </c>
-      <c r="Q36" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: Snowfall Warning for HOM-1038. Clear balconies &amp; drains to prevent water accumulation. Stay safe!"
+(Length: 105 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Snowfall Warning - Action Required
+Body: Heavy snowfall expected. Clear balconies and drains to prevent water accumulation. Monitor for power outages.</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning is accurately described with a maximum accumulation of 35 cm, which matches the ground truth alert text. The vulnerabilities mentioned, such as roof load stress and potential tree limb breakage, are directly taken from the alert text. The property details, including the dwelling type as a 'highrise_condo' and the absence of a sump pump, are consistent with the ground truth property data. No wind gusts, hail, or rainfall are mentioned, aligning with the alert's focus on snowfall. All micro-actions are reasonable and based on the provided alert information, with no fabricated or unverified claims. Therefore, the advisory is fully faithful to the ground truth.</t>
+        </is>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant to the active snowfall hazard and the specific dwelling type. The action to clear balconies and ensure drains are free of snow and ice directly addresses the risk of water accumulation and potential leaks, which is pertinent given the heavy snowfall and the condo's structural features. Monitoring for power outages and having an emergency kit ready is a prudent life-safety measure, considering the risk of tree limb breakage onto power lines. Clearing snow from common areas to prevent slip hazards is also relevant, though it assumes safe conditions for doing so. The actions are well-aligned with the peril and dwelling, but could be slightly more tailored by considering the specific layout or features of the highrise condo's common areas.</t>
+        </is>
+      </c>
+      <c r="P36" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the mandatory actions: clearing snow from balconies and ensuring drains are clear, which addresses both the structural load and drainage concerns. However, the agent fails to address the monitoring of interior window frames, doors, and exterior walls for signs of moisture seepage or water leaks as snow melts, which is a critical aspect of the mandatory actions. Additionally, the action to clear snow from common areas or shared pathways is illogical in the context of a highrise condo, where individual residents typically do not have access or responsibility for these areas. The action related to power outages is logical given the alert text but does not contribute to the score as it is not related to property loss mitigation.</t>
+        </is>
+      </c>
+      <c r="R36" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the snowfall threat and the first action to take (clearing balconies and drains). It avoids any insurance jargon and fits within the character limit. The push notification effectively expands on the SMS, providing additional context about potential power outages without causing panic. The micro-actions are clear, actionable, and free of jargon, providing specific steps to mitigate risks associated with the snowfall. Overall, the communication is crystal clear, actionable, and appropriately urgent.</t>
+        </is>
+      </c>
+      <c r="T36" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="37" ht="135" customHeight="1">
@@ -3911,62 +4405,77 @@
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 11-year-old asphalt shingle roof susceptible to heavy snow load stress, Finished basement at risk of water ingress from melting snow
-Identified Gaps: Sewer Backup Endorsement: NO - Basement sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H37" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Safely clear accumulated snow from your roof to prevent excessive load and potential structural damage.
-Rationale: Heavy snowfall (25-35 cm) can cause significant roof load stress on your 11-year-old asphalt shingle roof.
-[P2] INDOOR_WATER_PROTECTION: Clear snow away from your home's foundation, window wells, and basement entry points.
-Rationale: Melting snow can pool around the foundation, leading to water ingress into your finished basement.
-[P3] INDOOR_WATER_PROTECTION: Verify your sump pump is operational and ensure all downspouts extend at least 6 feet away from the foundation.
-Rationale: Proactive water management is crucial to prevent uninsured water damage from melting snow, especially with a finished basement and no sewer backup coverage.</t>
+Identified Vulnerabilities: Asphalt shingle roof (11 years old) susceptible to heavy snow load, Finished basement at risk due to lack of backwater valve
+Identified Gaps: Sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy snow (35cm) expected. Safely clear roof snow &amp; ensure drainage away from foundation. Your basement is uninsured for sewer backup."
-(Length: 143 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: If safe to do so, clear heavy snow from your roof to prevent structural damage from excessive snow load. Consider hiring a professional if you cannot safely perform this task.
+Rationale: Heavy snowfall (35 cm) can lead to significant roof load stress on your 11-year-old asphalt shingle roof, potentially causing structural damage.
+[P2] INDOOR_WATER_PROTECTION: Regularly monitor your finished basement for any signs of water ingress, especially around floor drains and fixtures, as you lack sewer backup coverage and a backwater valve.
+Rationale: The critical gap in your policy for sewer backup and the absence of a backwater valve leave your finished basement vulnerable to water damage from potential sewer issues exacerbated by heavy precipitation.
+[P3] INDOOR_WATER_PROTECTION: Clear snow from around all downspouts and drains to ensure proper water runoff and prevent the formation of ice dams, which can cause water to back up under your roof shingles.
+Rationale: Blocked downspouts and drains can lead to water accumulation and ice damming, increasing the risk of water penetration into your home, especially with significant snowfall.</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
         <is>
-          <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snow (35cm) expected. Safely clear roof snow &amp; ensure drainage away from foundation. Your basement is uninsured for sewer backup.</t>
-        </is>
-      </c>
-      <c r="K37" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which is within the 25-35 cm range specified in the alert. The advisory accurately identifies the 11-year-old asphalt shingle roof and the finished basement, both of which are mentioned in the property data. The advisory also correctly notes the lack of sewer backup endorsement, aligning with the policy details. All actions and rationales are consistent with the potential risks outlined in the snowfall warning and the property characteristics. There are no fabricated or hallucinated details in the advisory.</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's vulnerabilities. The first action addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is pertinent given the 11-year-old asphalt shingle roof. The second action targets the risk of water ingress into the finished basement by clearing snow from critical areas around the foundation, which is crucial given the lack of sewer backup coverage. The third action ensures the sump pump is operational and downspouts are properly extended, directly addressing the risk of water damage from melting snow, which is particularly important due to the finished basement and uninsured sewer backup gap. All actions are executable within the warning lead time and avoid hazardous outdoor work during the snowfall event.</t>
-        </is>
-      </c>
-      <c r="O37" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P37" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the threat (heavy snow) and provide actionable steps (clear roof snow, ensure drainage). The message avoids insurance jargon, simply stating the basement is uninsured for sewer backup, which is relevant and understandable. The micro-actions are clear, specific, and free of technical language, providing straightforward instructions on what to do first. The SMS complies with the character limit, maximizing impact.</t>
-        </is>
-      </c>
-      <c r="Q37" s="21" t="n">
-        <v>5</v>
+          <t>"Urgent: 35cm snow expected. Clear roof snow if safe. Monitor basement for water. Clear drains. Stay safe! #SnowWarning"
+(Length: 118 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>Title: Urgent: Snowfall Warning - Mitigation Required
+Body: Heavy snowfall (35cm) expected. Clear snow from roof if safe. Monitor basement for water ingress. Clear drains.</t>
+        </is>
+      </c>
+      <c r="L37" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the ground truth alert text. The advisory accurately identifies the vulnerabilities related to the asphalt shingle roof and the finished basement, consistent with the property details. It correctly notes the lack of a backwater valve and the absence of sewer backup coverage, aligning with the policy information. No unverified claims or hallucinations are present in the advisory.</t>
+        </is>
+      </c>
+      <c r="N37" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's vulnerabilities. The first action addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is pertinent given the 11-year-old asphalt shingle roof. It also wisely suggests hiring a professional to avoid life-safety risks. The second action is crucial as it targets the critical policy gap of uninsured sewer backup, emphasizing the need to monitor the finished basement for water ingress, which is a significant risk during heavy snowfall. The third action focuses on preventing ice dams by ensuring proper water runoff, directly addressing the risk of water penetration under roof shingles. All actions are executable within the warning lead time and consider the dwelling's structural and policy vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="P37" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to clear snow from around downspouts and drains aligns with ensuring drainage routes are clear, and monitoring the basement for water ingress partially covers monitoring for signs of moisture leaks. However, the agent did not address clearing snow from basement window wells, exterior entryways, and foundation perimeters, which is a distinct mandatory action. The additional action of clearing snow from the roof is logical and relevant given the heavy snowfall warning and potential roof load stress. No illogical actions were proposed.</t>
+        </is>
+      </c>
+      <c r="R37" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S37" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the snow threat and what actions to take first. It avoids any insurance jargon and fits well within the character limit. The push notification maintains clarity and urgency, providing specific actions without overwhelming the reader. The micro-actions are detailed yet clear, avoiding technical jargon and focusing on actionable steps, ensuring homeowners understand the importance of each task without unnecessary complexity.</t>
+        </is>
+      </c>
+      <c r="T37" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="38" ht="135" customHeight="1">
@@ -4012,62 +4521,77 @@
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
+          <t>• Clear heavy snow accumulation away from basement window wells, exterior entryways, and foundation perimeters to prevent meltwater seepage into the home
+• Regularly monitor interior ceilings, rooflines, and upper-floor walls for signs of ice damming, heavy snow load strain, or moisture leaks
+• Ensure ground-level downspouts and perimeter drainage routes are clear of snow and ice blockage to direct meltwater away from the foundation</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: snowfall warning in effect
 Wind Gust: None km/h | Hail: None (None cm)
 Rain: None mm | Snow: 35.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Heavy snow load on roof, Potential for overland water from snowmelt
-Identified Gaps: Overland Water Endorsement (UNINSURED)</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: If safe to do so, clear heavy snow from your roof or arrange for professional snow removal to prevent structural stress.
-Rationale: Heavy snowfall can accumulate and exert significant pressure on your roof, potentially leading to structural damage.
-[P2] INDOOR_WATER_PROTECTION: Monitor for snowmelt and potential overland water accumulation around your property, especially near the foundation.
-Rationale: Your policy has a critical gap for overland water, making proactive monitoring essential to prevent uninsured water damage.
-[P3] INDOOR_WATER_PROTECTION: Ensure all downspouts are clear of snow and ice, and extended at least 6 feet away from your home's foundation.
-Rationale: Properly functioning downspouts will direct snowmelt away from your foundation, reducing the risk of water intrusion.</t>
+Identified Vulnerabilities: Heavy snow can cause significant roof load stress on 15-year-old metal roof, Unfinished basement with NO sump pump increases risk of water ingress from snowmelt, Potential for tree limb breakage onto power lines due to wet heavy snow
+Identified Gaps: Overland Water Endorsement is missing, leaving surface overland flood runoff uninsured</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: 35cm snow expected. Safely clear roof snow &amp; monitor for snowmelt. Your home is uninsured for overland water. Stay safe!"
-(Length: 128 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear snow away from your home's foundation and egress windows to prevent snowmelt from seeping into the basement.
+Rationale: Heavy snowfall and subsequent melt can lead to basement flooding, especially with no sump pump and uninsured overland water coverage.
+[P2] INDOOR_WATER_PROTECTION: Regularly check your roof and eaves for ice dam formation and safely remove snow to prevent water intrusion.
+Rationale: Heavy, wet snow increases the risk of ice dams, which can force water under shingles and into your home.
+[P3] VEHICLE_PROTECTION: Park all vehicles in a garage or covered area to protect them from heavy snow accumulation and potential falling tree limbs.
+Rationale: Heavy wet snow can cause tree branches to break, potentially damaging vehicles parked outdoors.</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: 35cm snow expected. Clear snow from foundation &amp; monitor roof for ice dams. Park vehicles under cover. Overland water is uninsured."
+(Length: 139 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K38" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Snowfall Mitigation Required
-Body: Heavy snowfall (35cm) expected. Safely clear roof snow and monitor for snowmelt. Your home is uninsured for overland water.</t>
-        </is>
-      </c>
-      <c r="K38" s="21" t="n">
+Body: Heavy snowfall (35cm) expected. Clear snow from foundation, monitor for ice dams, and park vehicles under cover. Overland water is uninsured.</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The snowfall warning correctly states the expected accumulation of 35 cm, which matches the upper limit of the ground truth alert (25-35 cm). The advisory accurately reflects the property's attributes: a 15-year-old metal roof, an unfinished basement without a sump pump, and the lack of overland water endorsement. All vulnerabilities and coverage gaps mentioned are consistent with the ground truth. No unverified features or fabricated metrics are present.</t>
+        </is>
+      </c>
+      <c r="N38" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is largely faithful to the ground truth with minor imprecision. The snowfall amount of 35 cm is consistent with the ground truth alert, which states accumulations between 25 and 35 cm. The advisory correctly identifies the lack of overland water endorsement, matching the ground truth policy details. However, the mention of 'potential for overland water from snowmelt' is speculative as the alert does not specifically mention snowmelt or overland water risk, though it is a reasonable inference given the heavy snow. The advisory does not fabricate any peril metrics or property features, maintaining overall factual accuracy.</t>
-        </is>
-      </c>
-      <c r="M38" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of heavy snowfall and the dwelling's characteristics. The first action addresses the primary loss driver of roof load stress due to heavy snow accumulation, which is pertinent given the metal roof's age and the potential for structural damage. The second action is crucial due to the uninsured gap for overland water, emphasizing the need for vigilance against snowmelt accumulation near the foundation. The third action ensures that downspouts are clear and functional, which is vital for directing snowmelt away from the foundation, further mitigating the risk of water intrusion. All actions are executable within the warning lead time and avoid hazardous outdoor work during the snowfall, adhering to life-safety requirements.</t>
-        </is>
-      </c>
-      <c r="O38" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P38" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the snow threat and the need to clear roof snow and monitor for snowmelt. It avoids insurance jargon and is well within the character limit. The push notification mirrors this clarity, providing a succinct title and body that reiterates the key actions. The micro-actions are straightforward, actionable, and free of technical language, guiding the homeowner on specific steps to mitigate risk. Overall, the communication is crystal clear, actionable, and devoid of confusing terminology.</t>
-        </is>
-      </c>
-      <c r="Q38" s="21" t="n">
-        <v>4.67</v>
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant to the active snowfall hazard and the dwelling's specific vulnerabilities. The first action addresses the risk of snowmelt infiltration into the basement, which is critical given the lack of a sump pump and the uninsured overland water gap. However, the dwelling has an unfinished basement, which slightly reduces the urgency compared to a finished basement scenario. The second action is relevant for preventing ice dams, which are a risk with heavy, wet snow, although the metal roof is less susceptible to ice dam formation compared to asphalt shingles. The third action is appropriate for protecting vehicles from snow accumulation and falling branches, which are significant risks during heavy snowfall. Overall, the actions are well-aligned with the peril and property, but minor tailoring could enhance their relevance.</t>
+        </is>
+      </c>
+      <c r="P38" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory reference actions. The action to clear snow from the foundation and egress windows aligns with the first mandatory action regarding preventing meltwater seepage. The action to check the roof and eaves for ice dam formation covers the second mandatory action about monitoring for ice damming and snow load strain. However, the agent did not address the third mandatory action, which involves ensuring that downspouts and drainage routes are clear to direct meltwater away from the foundation. The additional action regarding vehicle protection is logical and relevant given the alert's mention of potential tree limb breakage, so it is not penalized. Therefore, the score is 4 due to the omission of one mandatory action.</t>
+        </is>
+      </c>
+      <c r="R38" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and mostly clear, effectively communicating the threat of heavy snowfall and immediate actions to take. It avoids insurance jargon, except for the mention of 'overland water is uninsured,' which could be confusing to some homeowners. The message clearly instructs homeowners to clear snow from the foundation, monitor the roof for ice dams, and park vehicles under cover, which are actionable steps. The push notification mirrors the SMS in clarity and urgency. The micro-actions provide detailed instructions, but the SMS could be slightly improved by omitting the insurance reference or rephrasing it to be more immediately actionable.</t>
+        </is>
+      </c>
+      <c r="T38" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="39" ht="135" customHeight="1">
@@ -4113,62 +4637,77 @@
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
 Identified Vulnerabilities: Finished basement, Asphalt shingle roof (4 years old)
-Identified Gaps: Sewer backup damage is UNINSURED, Surface overland flood runoff is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H39" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items from the basement floor to higher ground.
-Rationale: Heavy rainfall (80 mm) and uninsured sewer backup/overland flood risk could lead to significant basement water damage.
-[P2] INDOOR_SHELTER: Close and lock all windows and doors, especially those on the windward side.
-Rationale: High wind gusts (90 km/h) and heavy rain can cause wind-driven rain intrusion and compromise dwelling security.
-[P3] LIFE_SAFETY: Prepare an emergency kit and identify the safest indoor shelter location for all family members.
-Rationale: Ensuring preparedness and a safe shelter plan is crucial for personal safety during severe weather with high winds.</t>
+Identified Gaps: Sewer Backup Endorsement: NO - CRITICAL GAP: Basement sewer backup damage is UNINSURED, Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy rain &amp; 90km/h winds expected. Move basement valuables to higher ground. Do NOT go on roof/ladders. Stay safe! #HOM1021"
-(Length: 132 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Elevate or move valuable items from the basement floor to protect against potential uninsured sewer backup or overland flooding.
+Rationale: Heavy rainfall (80 mm) and critical policy gaps for sewer backup and overland water increase the risk of water damage to basement contents.
+[P2] LIFE_SAFETY: Secure or store loose outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming projectiles in 90 km/h wind gusts.
+Rationale: High wind gusts (90 km/h) can cause unsecured outdoor items to become airborne, leading to property damage or injury.
+[P3] INDOOR_WATER_PROTECTION: Ensure downspouts are clear of debris and directed at least 6 feet away from the foundation to effectively channel heavy rainfall away from the home.
+Rationale: Proper downspout function is crucial to prevent water accumulation around the foundation, reducing the risk of basement leaks and potential uninsured overland water damage.</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90km/h winds. Move basement valuables &amp; secure outdoor items. Do NOT climb ladders. Stay safe! Info: +1-613-555-1021"
+(Length: 137 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rain (80mm) and 90km/h winds expected. Move basement valuables to higher ground. Close windows/doors. Do NOT go on roof or use ladders.</t>
-        </is>
-      </c>
-      <c r="K39" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The advisory correctly identifies that there is no hail detected, aligning with the absence of hail in the alert. The property details such as the finished basement and 4-year-old asphalt shingle roof are accurately reflected in the advisory. The coverage gaps regarding sewer backup and overland water are also correctly noted as uninsured, consistent with the policy details. All actions and recommendations are based on the factual data provided, with no hallucinations or fabrications present.</t>
-        </is>
-      </c>
-      <c r="M39" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and high winds, considering the dwelling's structural vulnerabilities and policy gaps. The first action directly addresses the risk of basement flooding due to the uninsured sewer backup and overland water gaps by moving valuables to higher ground, which is crucial given the finished basement. The second action mitigates the risk of wind-driven rain intrusion by securing windows and doors, which is appropriate given the high wind gusts. The third action ensures life safety by preparing an emergency kit and identifying a safe indoor shelter, which is essential during severe weather conditions. All actions are executable within the warning lead time and avoid dangerous outdoor activities, aligning perfectly with the loss drivers and property specifics.</t>
-        </is>
-      </c>
-      <c r="O39" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P39" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy rain and strong winds) and provides specific, actionable instructions (move valuables, avoid roof/ladders). It is free of insurance jargon and complies with the character limit. The push notification complements the SMS by providing additional details (rainfall amount) and further instructions (closing windows/doors), maintaining clarity and urgency. The micro-actions are straightforward, actionable, and devoid of technical language, ensuring homeowners know exactly what to do.</t>
-        </is>
-      </c>
-      <c r="Q39" s="21" t="n">
-        <v>5</v>
+Body: Heavy rain (80mm) and 90 km/h winds expected. Move basement valuables, secure outdoor items. Do NOT climb ladders. Critical policy gaps for water damage.</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The property details, such as the finished basement and 4-year-old asphalt shingle roof, are accurately reflected in the advisory. The critical coverage gaps for sewer backup and overland water endorsements are correctly identified as not endorsed in the policy. All actions and recommendations are consistent with the risks outlined in the weather alert and the property profile, with no fabricated or unverified claims.</t>
+        </is>
+      </c>
+      <c r="N39" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active peril and the dwelling's specific vulnerabilities. The first action directly addresses the risk of uninsured sewer backup and overland water damage by protecting valuable items in the finished basement, which is a critical vulnerability given the policy gaps. The second action is crucial for life safety, preventing windborne projectiles during high wind gusts, which is a primary loss driver in this scenario. The third action ensures that downspouts are functioning properly to mitigate water accumulation around the foundation, directly addressing the risk of basement leaks and overland water damage. All actions are executable within the warning lead time and avoid dangerous outdoor work during high winds, adhering to mandatory life-safety requirements.</t>
+        </is>
+      </c>
+      <c r="P39" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="20" t="inlineStr">
+        <is>
+          <t>The agent successfully covered the action of elevating or moving valuable items from the basement to protect against water damage, which aligns with the first mandatory action. However, the agent failed to address the monitoring of basement walls and the functionality of the sump pump and backwater valve, as well as the action of sealing windows and doors against wind-driven rain, both of which are critical given the alert conditions. Additionally, the action regarding downspouts is illogical for this scenario because the property is a detached home with a finished basement equipped with a sump pump and backwater valve, and the alert specifically mentions urban flash flooding and sewer backup, not overland flooding. The action to secure outdoor items is logical and relevant to the wind conditions but does not cover any mandatory actions.</t>
+        </is>
+      </c>
+      <c r="R39" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, effectively communicating the immediate threat (heavy rain and strong winds) and the first actions to take (move valuables, secure items). It avoids insurance jargon and complies with character limits. The push notification is slightly less clear due to the mention of 'critical policy gaps,' which introduces unnecessary complexity during an emergency. The micro-actions are clear but slightly wordy, especially the first one, which introduces insurance-related terms like 'uninsured sewer backup,' which could be simplified for clarity. Overall, the communication is effective but could be improved by removing any mention of policy details during an emergency.</t>
+        </is>
+      </c>
+      <c r="T39" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="40" ht="135" customHeight="1">
@@ -4214,62 +4753,78 @@
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Unfinished basement, No sump pump, No backwater valve
+Identified Vulnerabilities: unfinished basement, NO sump pump, NO backwater valve
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items off the floor in the unfinished basement to protect them from potential water damage.
-Rationale: With heavy rainfall (up to 80 mm) and no sump pump or backwater valve, the unfinished basement is at high risk of flooding.
-[P2] INDOOR_WATER_PROTECTION: Check for any leaks around windows and doors, and place towels or barriers to prevent water ingress.
-Rationale: Heavy rainfall and high winds can exploit vulnerabilities in window and door seals, leading to indoor water damage.
-[P3] LIFE_SAFETY: Prepare an emergency kit with essentials like flashlights, batteries, and a first-aid kit in case of power outages due to high winds.
-Rationale: Wind gusts of 90 km/h can cause power outages, making an emergency kit crucial for safety and comfort.</t>
-        </is>
-      </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy rain &amp; 90 km/h winds. Move basement valuables, check for leaks, and prepare emergency kit. Stay safe!"
-(Length: 115 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Ensure downspouts are properly extended at ground level to direct water at least 6 feet away from the foundation.
+Rationale: Heavy rainfall (80 mm) can lead to water pooling around the foundation, increasing the risk of basement flooding, especially with an unfinished basement and no sump pump/backwater valve.
+[P2] INDOOR_WATER_PROTECTION: Move any valuables or sensitive items off the floor in the unfinished basement to protect them from potential water damage.
+Rationale: With 80 mm of rain and no sump pump or backwater valve, there is a significant risk of basement flooding.
+[P3] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming projectiles in 90 km/h wind gusts.
+Rationale: High wind gusts of 90 km/h can cause unsecured outdoor items to become dangerous projectiles, leading to property damage or injury.</t>
         </is>
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain (80mm) &amp; 90km/h winds expected. Extend downspouts, secure outdoor items, &amp; move basement valuables off floor. Stay safe!"
+(Length: 139 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K40" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rainfall (80mm) and 90 km/h winds expected. Move basement valuables off floor, check for leaks, and prepare an emergency kit.</t>
-        </is>
-      </c>
-      <c r="K40" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The property details such as the unfinished basement, absence of a sump pump, and no backwater valve are accurately reflected in the advisory's exposure analysis. There is no mention of hail or tornado risk, consistent with the ground truth alert. All micro-actions are logically derived from the provided data, focusing on water protection and safety due to the specified weather conditions. No fabricated or unverified information is present.</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and the dwelling's characteristics. The first action addresses the risk of basement flooding by moving valuables off the floor, which is crucial given the lack of a sump pump or backwater valve. The second action targets potential water ingress through windows and doors, which is a realistic threat during heavy rain and high winds. The third action focuses on life safety by preparing for power outages, which are likely given the forecasted wind gusts. All actions are executable within the warning lead time and directly address the primary loss drivers of the active weather peril.</t>
-        </is>
-      </c>
-      <c r="O40" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy rain and strong winds) and provides actionable steps (move valuables, check for leaks, prepare emergency kit). It is well within the character limit and free of insurance jargon. The push notification and micro-actions are similarly clear and actionable, providing specific instructions without unnecessary complexity or technical language.</t>
-        </is>
-      </c>
-      <c r="Q40" s="21" t="n">
-        <v>5</v>
+Body: Heavy rainfall (80mm) and 90 km/h wind gusts expected. Ensure downspouts are extended, secure outdoor items, and move basement valuables off the floor. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rain and 90 km/h wind gusts. The property details such as 'unfinished basement', 'NO sump pump', and 'NO backwater valve' are accurately reflected in the advisory's exposure analysis. There is no mention of hail or tornado risk, consistent with the ground truth alert. All micro-actions and safety recommendations are based on the factual data provided, with no fabricated or extrapolated information.</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active weather peril and the dwelling's specific vulnerabilities. The first action addresses the risk of water pooling around the foundation due to heavy rainfall, which is critical given the lack of a sump pump or backwater valve in the unfinished basement. The second action further mitigates potential water damage by protecting valuables in the basement, acknowledging the high risk of flooding. The third action addresses life safety by preventing windborne projectiles, which is crucial given the forecasted 90 km/h wind gusts. All actions are executable within the warning lead time and directly target the primary loss drivers of the peril.</t>
+        </is>
+      </c>
+      <c r="P40" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="20" t="inlineStr">
+        <is>
+          <t>The agent successfully covered the action of moving valuables from the basement floor to protect against water damage, which aligns with the mandatory action of elevating belongings. However, the agent did not address monitoring the basement for water ingress or verifying sump pump and backwater valve functionality, which is critical given the basement's unfinished state and lack of these features. Additionally, the agent failed to mention sealing windows and doors against wind-driven rain, a key action given the forecasted wind gusts.
+The action regarding downspouts is illogical in this context because it does not directly address the immediate risk of torrential rain and flash flooding, especially since the property lacks a sump pump and backwater valve, making internal water management more critical. The action about securing outdoor items is logical but does not replace the need for sealing windows and doors.</t>
+        </is>
+      </c>
+      <c r="R40" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S40" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the threat (heavy rain and strong winds) and provide specific, actionable steps to mitigate potential damage. The language is free of insurance jargon and technical terms, making it accessible to all homeowners. The SMS is within the character limit, ensuring quick readability during an emergency. The micro-actions are detailed yet straightforward, providing clear instructions on what to do first, enhancing the overall clarity and effectiveness of the communication.</t>
+        </is>
+      </c>
+      <c r="T40" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="41" ht="135" customHeight="1">
@@ -4315,62 +4870,77 @@
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
-Rain: 80.0 mm | Snow: 0.0 cm
+Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Roof age (12 years old) susceptible to high winds, Crawlspace basement vulnerable to water ingress, No backwater valve increases sewer backup risk
+Identified Vulnerabilities: crawlspace, no backwater valve
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H41" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure all outdoor furniture, decorations, and any loose items that could become airborne.
-Rationale: High wind gusts of 90 km/h can turn unsecured objects into dangerous projectiles, causing property damage or injury.
-[P2] INDOOR_WATER_PROTECTION: Ensure downspouts are clear of debris and directed at least 6 feet away from the foundation to prevent water accumulation near the crawlspace.
-Rationale: Heavy rainfall (80 mm) can overwhelm drainage systems, leading to water pooling around the foundation and potential crawlspace flooding.
-[P3] INDOOR_WATER_PROTECTION: Minimize indoor water usage (e.g., limit showers, laundry, dishwashing) during the storm.
-Rationale: Without a backwater valve, heavy rainfall increases the risk of sewer system surcharge and potential backup into your crawlspace.</t>
-        </is>
-      </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: 90 km/h winds &amp; 80mm rain expected. Secure outdoor items immediately. Stay safe! #HOM1023"
-(Length: 97 / 160 chars)</t>
+          <t>[P1] VEHICLE_PROTECTION: Secure all outdoor furniture, decorations, and any loose items that could be picked up by strong winds.
+Rationale: Wind gusts of 90 km/h can cause unsecured items to become projectiles, leading to property damage or injury.
+[P2] INDOOR_WATER_PROTECTION: Ensure downspouts are extended away from the foundation at ground level to direct rainwater runoff effectively.
+Rationale: Heavy rainfall (80 mm) requires proper drainage to prevent water accumulation around the foundation and potential crawlspace flooding.
+[P3] INDOOR_WATER_PROTECTION: Monitor your crawlspace frequently for any signs of water intrusion or sewer backup, especially in low-lying areas.
+Rationale: Despite having a sump pump, the absence of a backwater valve combined with heavy rainfall increases the risk of sewer backup into the crawlspace.</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Rainfall warning for HOM-1023. Secure outdoor items &amp; ensure downspouts are extended. Winds 90km/h. Stay safe! Info: +1-613-555-1023"
+(Length: 140 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: 90 km/h winds and 80mm rain expected. Secure outdoor items, clear downspouts, and minimize water usage to protect your home.</t>
-        </is>
-      </c>
-      <c r="K41" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L41" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies wind gusts up to 90 km/h and rainfall between 60 to 80 mm, which matches the advisory's claims of 90 km/h wind gusts and 80 mm of rainfall. The property details such as the roof age (12 years), the presence of a crawlspace basement, and the absence of a backwater valve are accurately reflected in the advisory's exposure analysis. There are no fabricated or hallucinated claims regarding hail, snowfall, or tornado risk, as these are not mentioned in the ground truth. All micro-actions and their rationales are consistent with the provided data, ensuring the advisory is entirely faithful to the ground truth.</t>
-        </is>
-      </c>
-      <c r="M41" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and the dwelling's characteristics. The first action addresses the risk of windborne projectiles due to high wind gusts, which is a primary concern during such weather events. The second action focuses on preventing water accumulation near the crawlspace, which is crucial given the heavy rainfall and the dwelling's lack of a backwater valve. The third action is particularly relevant as it addresses the risk of sewer backup by minimizing indoor water usage, which is a prudent measure given the absence of a backwater valve. All actions are executable within the warning lead time and directly target the primary loss drivers of the active peril, considering the dwelling's structural vulnerabilities and policy coverage.</t>
-        </is>
-      </c>
-      <c r="O41" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P41" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (90 km/h winds &amp; 80mm rain) and the first action to take (secure outdoor items). It avoids any insurance jargon and fits well within the character limit. The push notification effectively expands on the SMS, providing additional actions (clear downspouts, minimize water usage) without overwhelming the user. The micro-actions are clear, actionable, and free of jargon, providing specific steps to mitigate potential damage. Overall, the communication is direct, actionable, and devoid of any confusing terminology, making it highly effective for emergency conditions.</t>
-        </is>
-      </c>
-      <c r="Q41" s="21" t="n">
-        <v>5</v>
+Body: Heavy rainfall (80mm) and 90km/h winds expected. Secure outdoor items, ensure downspouts are extended, and monitor crawlspace for water. Do NOT climb ladders.</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning event, wind gusts of 90 km/h, and expected rainfall of 80 mm are directly aligned with the weather alert. The property details such as the presence of a crawlspace, absence of a backwater valve, and presence of a sump pump are accurately reflected in the exposure analysis and micro-actions. No hail or tornado risk is mentioned, consistent with the alert. All contact information and policyholder details match the ground truth. There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and the dwelling's characteristics. The first action addresses the risk of windborne projectiles, which is a primary concern given the forecasted wind gusts of 90 km/h. The second action focuses on ensuring proper drainage away from the foundation, which is crucial to prevent water accumulation and potential crawlspace flooding, especially given the heavy rainfall forecast. The third action is particularly important due to the absence of a backwater valve, which increases the risk of sewer backup despite the presence of a sump pump. All actions are executable within the warning lead time and directly target the primary loss drivers of the active weather peril, considering the townhouse's structural vulnerabilities and policy coverage.</t>
+        </is>
+      </c>
+      <c r="P41" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions partially cover the mandatory actions. The action to monitor the crawlspace for water intrusion addresses the need to monitor for water ingress, but it does not explicitly verify the sump pump's functionality or mention the backwater valve, which is absent. The action to secure outdoor items is logical but does not cover any mandatory actions. The action to ensure downspouts are extended is illogical for a townhouse with a crawlspace, as it does not directly address the risk of water ingress or sewer backup in the crawlspace. The agent completely misses the mandatory action to close and seal exterior windows and doors, which is crucial given the wind-driven rain risk. Therefore, the score is 2 due to poor coverage and an illogical additional action.</t>
+        </is>
+      </c>
+      <c r="R41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S41" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without causing panic. It immediately informs the homeowner of the threat (rainfall and high winds) and provides specific actions to take (secure outdoor items, extend downspouts). The message is within the character limit and free of jargon. The push notification complements the SMS by providing additional context and safety advice (do not climb ladders), maintaining clarity and urgency. The micro-actions are straightforward, actionable, and devoid of technical language, ensuring homeowners understand what to do without confusion.</t>
+        </is>
+      </c>
+      <c r="T41" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="42" ht="135" customHeight="1">
@@ -4416,62 +4986,77 @@
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
+          <t>• Close, latch, and lock all balcony doors and windows tightly against 90 km/h wind-driven rain infiltration
+• Monitor interior window perimeters, balcony thresholds, and exterior walls for water seepage, keeping towels or barriers ready
+• Ensure balcony drainage at floor level is unobstructed to prevent torrential rainwater from pooling and overflowing into the living area</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
-Rain: 80.0 mm | Snow: None cm
+Rain: 80.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: highrise_condo (urban flash flooding risk), slab_on_grade (potential for surface water entry)
-Identified Gaps: Overland Water Endorsement (UNINSURED surface overland flood runoff)</t>
-        </is>
-      </c>
-      <c r="H42" s="20" t="inlineStr">
-        <is>
-          <t>[P1] VEHICLE_PROTECTION: Move vehicles to higher ground or a covered parking area away from potential flood zones.
-Rationale: Heavy rainfall (up to 80 mm) and urban flash flooding risk, combined with uninsured overland water coverage, could damage vehicles.
-[P2] INDOOR_SHELTER: Secure any loose items on balconies or near windows to prevent them from becoming projectiles in 90 km/h wind gusts.
-Rationale: Strong wind gusts can cause unsecured items to become dangerous and cause property damage.
-[P3] LIFE_SAFETY: Monitor local weather alerts and avoid unnecessary travel during the storm due to heavy rainfall and strong winds.
-Rationale: Heavy rainfall can reduce visibility and create hazardous driving conditions, while strong winds can cause debris.</t>
+Identified Vulnerabilities: highrise_condo (potential for balcony/window water intrusion), slab_on_grade basement (ground-level units at risk from surface water), 90 km/h wind gusts (risk of damage to unsecured outdoor items)
+Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Move vehicles to higher ground due to 80mm rain &amp; 90km/h winds. Secure balcony items. Avoid travel. Stay safe! #HOM1024"
-(Length: 127 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Clear balcony drains and ensure windows/doors are tightly sealed to prevent water intrusion from heavy rainfall.
+Rationale: Torrential downpours increase the risk of water entering your high-rise condo, especially with an uninsured overland water gap.
+[P2] LIFE_SAFETY: Secure or bring indoors any loose items on balconies or patios, such as furniture, plants, or decorations, to prevent them from becoming projectiles in 90 km/h wind gusts.
+Rationale: High wind gusts can turn unsecured outdoor items into hazards, causing property damage or injury.
+[P3] INDOOR_WATER_PROTECTION: Monitor for urban flash flooding, particularly if your unit is on a lower floor, and be prepared to protect valuables from potential water ingress.
+Rationale: Heavy rainfall can lead to localized urban flash flooding, posing a risk to ground-level units despite a slab-on-grade basement.</t>
         </is>
       </c>
       <c r="J42" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90km/h winds expected. Clear balcony drains &amp; secure outdoor items. Overland water is uninsured. Stay safe! #HOM1024"
+(Length: 137 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K42" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rain (80mm) &amp; 90km/h winds expected. Move vehicles to higher ground, secure balcony items, and avoid unnecessary travel. Your property has an uninsured overland water gap.</t>
-        </is>
-      </c>
-      <c r="K42" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm rainfall and 90 km/h wind gusts. The property is a highrise condo with a slab on grade, consistent with the advisory's mention of urban flash flooding risk and potential surface water entry. The advisory correctly identifies the lack of overland water endorsement as a coverage gap. No hail or tornado risk is mentioned, aligning with the ground truth. All contact details and policyholder information are accurate. No hallucinations or unverified claims are present.</t>
-        </is>
-      </c>
-      <c r="M42" s="21" t="n">
+Body: Heavy rain (80mm) &amp; 90km/h winds expected. Clear balcony drains &amp; secure outdoor items. Overland water is uninsured. Monitor for flooding.</t>
+        </is>
+      </c>
+      <c r="L42" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The property is a highrise condo with a slab-on-grade basement, consistent with the advisory's mention of potential water intrusion and ground-level unit risks. The advisory correctly identifies the lack of overland water endorsement as a coverage gap. No hail or tornado risk is mentioned, aligning with the ground truth. All claims are directly supported by the provided data, with no hallucinations or fabrications.</t>
+        </is>
+      </c>
+      <c r="N42" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and the dwelling's characteristics. The first action addresses the risk of water intrusion through balcony drains and windows, which is crucial given the uninsured overland water gap. The second action focuses on securing loose items on balconies, directly mitigating the risk of windborne projectiles due to 90 km/h gusts, which is a significant threat in high-rise settings. The third action advises monitoring for urban flash flooding, which is pertinent for lower-floor units in high-rise buildings, even with a slab-on-grade foundation. All actions are executable within the warning lead time and appropriately consider the dwelling's structural vulnerabilities and policy gaps.</t>
+        </is>
+      </c>
+      <c r="P42" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant to the active weather hazard of torrential rain and strong winds, and they are well-tailored to the dwelling's characteristics and policy gaps. The action to move vehicles to higher ground directly addresses the risk of urban flash flooding and the uninsured overland water gap, which is critical given the high rainfall and the condo's slab-on-grade foundation. Securing loose items on balconies is appropriate for the highrise condo setting, addressing the risk of windborne projectiles due to 90 km/h gusts. Monitoring weather alerts and avoiding travel is a prudent life-safety measure given the hazardous conditions. However, the actions could be slightly more tailored by considering the specific vulnerabilities of the highrise structure, such as potential water ingress through windows or doors, which is why the score is not a perfect 5.</t>
-        </is>
-      </c>
-      <c r="O42" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P42" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy rain and strong winds) and provides clear actions to take (move vehicles, secure items, avoid travel). It is well within the character limit and free of jargon. The push notification is similarly clear, though it includes a mention of an 'uninsured overland water gap,' which could be considered jargon, but it does not detract significantly from the overall clarity. The micro-actions are detailed yet straightforward, providing clear instructions without unnecessary complexity or jargon.</t>
-        </is>
-      </c>
-      <c r="Q42" s="21" t="n">
-        <v>4.67</v>
+      <c r="Q42" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to "Clear balcony drains and ensure windows/doors are tightly sealed" semantically matches the requirements to ensure balcony drainage is unobstructed and to close, latch, and lock all balcony doors and windows tightly. However, the agent did not explicitly address monitoring interior window perimeters, balcony thresholds, and exterior walls for water seepage, which is a missed mandatory action. The additional actions proposed by the agent are logical and relevant to the context of the alert, such as securing loose items on balconies due to high winds and monitoring for urban flash flooding, which are appropriate given the weather conditions described. Therefore, the score is 4 due to the omission of one mandatory action.</t>
+        </is>
+      </c>
+      <c r="R42" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S42" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (heavy rain and strong winds) and what actions to take first (clear drains, secure items). It avoids insurance jargon, only mentioning 'overland water is uninsured' in a straightforward manner. The character count is within limits, ensuring readability in an emergency. The push notification and micro-actions are similarly clear, providing specific actions without unnecessary complexity or jargon, maintaining a tone of urgency without inciting panic.</t>
+        </is>
+      </c>
+      <c r="T42" s="21" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="43" ht="135" customHeight="1">
@@ -4517,62 +5102,77 @@
       </c>
       <c r="G43" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 20-year-old asphalt shingle roof, finished basement, no backwater valve
-Identified Gaps: uninsured sewer backup</t>
-        </is>
-      </c>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>[P1] LIFE_SAFETY: Secure all outdoor items such as patio furniture, garbage bins, and garden tools to prevent them from becoming projectiles in high winds.
-Rationale: High wind gusts of 90 km/h can cause unsecured outdoor items to become dangerous projectiles, leading to property damage or injury.
-[P2] INDOOR_WATER_PROTECTION: Elevate or move valuable items from the basement floor to higher ground to protect them from potential water damage.
-Rationale: Heavy rainfall (80 mm) combined with a finished basement and lack of sewer backup endorsement significantly increases the risk of uninsured water damage from urban flash flooding or sewer backup.
-[P3] INDOOR_WATER_PROTECTION: Regularly monitor your basement for any signs of water intrusion or sewer backup and ensure your sump pump is operational.
-Rationale: Proactive monitoring is crucial to detect and mitigate water damage early, especially with a finished basement and the risk of heavy rainfall and potential sewer backup.</t>
+Identified Vulnerabilities: 20-year-old asphalt shingle roof vulnerable to high winds, Finished basement vulnerable to urban flash flooding and sewer backup, No backwater valve increases sewer backup risk
+Identified Gaps: Sewer Backup Endorsement: Basement sewer backup damage is UNINSURED</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: 90km/h winds &amp; 80mm rain for HOM-1025. Secure outdoor items immediately. Stay indoors. Monitor basement for flooding."
-(Length: 125 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Move valuables and electronics off the basement floor to higher ground.
+Rationale: Heavy rainfall and the lack of a backwater valve, combined with an uninsured sewer backup, put the finished basement at high risk of water damage.
+[P2] INDOOR_WATER_PROTECTION: Ensure your sump pump is clear and operating effectively.
+Rationale: With significant rainfall expected, a functional sump pump is crucial to manage water accumulation and prevent basement flooding.
+[P3] LIFE_SAFETY: Stay indoors and away from windows during the storm due to high wind gusts.
+Rationale: Wind gusts of 90 km/h pose a risk of flying debris and potential damage to the older asphalt shingle roof.</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90km/h winds expected. Move basement valuables, check sump pump, and stay indoors. Safety first! #HOM-1025"
+(Length: 127 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: 90 km/h winds and 80 mm rain expected. Secure outdoor items, move basement valuables, and monitor for water intrusion. Stay safe indoors.</t>
-        </is>
-      </c>
-      <c r="K43" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies wind gusts up to 90 km/h and rainfall between 60 to 80 mm, which matches the advisory's claims of 90 km/h wind gusts and 80 mm of rainfall. The advisory correctly notes the absence of hail and tornado risk, consistent with the alert. The property details, such as the 20-year-old asphalt shingle roof, finished basement, and lack of a backwater valve, are accurately reflected in the advisory. The mention of uninsured sewer backup aligns with the policy's lack of sewer backup endorsement. All actions and rationales are based on the factual data provided, with no hallucinations or fabrications present.</t>
-        </is>
-      </c>
-      <c r="M43" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active peril and the dwelling's specific vulnerabilities. The first action addresses the risk of windborne projectiles due to high wind gusts, which is a primary concern during the storm. The second action is highly relevant as it directly targets the risk of water damage in the finished basement, considering the uninsured gap for sewer backup. Elevating items is a practical measure given the lead time and the potential for flash flooding. The third action emphasizes proactive monitoring and sump pump functionality, which is critical given the heavy rainfall and the finished basement. All actions are executable within the warning lead time and specifically tailored to the dwelling's structural vulnerabilities and policy gaps.</t>
-        </is>
-      </c>
-      <c r="O43" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P43" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, urgent, and clear, immediately informing the homeowner of the threat (90km/h winds &amp; 80mm rain) and what actions to take first (secure outdoor items, stay indoors, monitor basement). It avoids any insurance jargon and fits within the character limit, making it highly effective for emergency communication. The push notification and micro-actions are also clear and actionable, providing specific steps without overwhelming the reader with technical terms or unnecessary details.</t>
-        </is>
-      </c>
-      <c r="Q43" s="21" t="n">
-        <v>5</v>
+Body: Heavy rain and 90 km/h winds expected. Move basement valuables, ensure sump pump is clear, and stay indoors away from windows. Your safety is paramount.</t>
+        </is>
+      </c>
+      <c r="L43" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M43" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm rainfall and 90 km/h wind gusts. The advisory correctly notes the absence of hail and tornado risk, consistent with the alert. The property details, such as the 20-year-old asphalt shingle roof, finished basement, and lack of a backwater valve, are accurately reflected in the advisory. The coverage gap regarding the lack of sewer backup endorsement is also correctly identified. All micro-actions are logically derived from the ground truth data, focusing on the vulnerabilities and coverage gaps identified. There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N43" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and property vulnerabilities. The first action directly addresses the risk of water damage to the finished basement due to the uninsured sewer backup gap, which is critical given the lack of a backwater valve. The second action ensures the sump pump is operational, which is vital for managing water accumulation during the torrential downpour. The third action addresses life safety by advising to stay indoors during high wind gusts, which is appropriate given the potential for windborne debris and the age of the asphalt shingle roof. All actions are executable within the warning lead time and directly target the primary loss drivers of the active weather peril.</t>
+        </is>
+      </c>
+      <c r="P43" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to move valuables and electronics off the basement floor addresses the need to protect against sewer backup and water seepage. The action to ensure the sump pump is operating effectively partially covers the need to monitor the sump pump, but it does not address monitoring the basement walls, window wells, and entryways for water ingress. The agent completely omits the action to close, latch, and seal exterior windows and doors, which is crucial for preventing water penetration and structural damage from wind-driven rain. Additionally, the action to stay indoors and away from windows is illogical in the context of property loss mitigation, as it does not address any specific property protection measures related to the alert.</t>
+        </is>
+      </c>
+      <c r="R43" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S43" s="20" t="inlineStr">
+        <is>
+          <t>The SMS and push notification are both clear, concise, and actionable. They immediately inform the homeowner of the threat (heavy rain and high winds) and provide specific actions to take (move valuables, check sump pump, stay indoors). The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit and effectively communicates urgency without causing panic. The micro-actions are also clear and provide step-by-step instructions that are easy to follow.</t>
+        </is>
+      </c>
+      <c r="T43" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="44" ht="135" customHeight="1">
@@ -4618,62 +5218,77 @@
       </c>
       <c r="G44" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
-Rain: 80.0 mm | Snow: None cm
+Rain: 80.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: 24-year-old metal roof, unfinished basement, NO sump pump, NO backwater valve
+Identified Vulnerabilities: semi_detached dwelling, unfinished basement, NO sump pump, NO backwater valve, metal roof (24 years old)
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H44" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items from the unfinished basement to higher ground to prevent water damage.
-Rationale: Heavy rainfall (80 mm) and potential sewer backup increase the risk of water damage to basement contents, despite coverage.
-[P2] LIFE_SAFETY: Secure all outdoor furniture, garbage bins, and any loose items on the property.
-Rationale: 90 km/h wind gusts can turn unsecured outdoor items into dangerous projectiles, posing a risk to property and life.
-[P3] INDOOR_SHELTER: Monitor local weather updates and be prepared for potential power outages.
-Rationale: High winds and heavy rain can lead to power disruptions, requiring preparedness for safety and comfort.</t>
-        </is>
-      </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Storm alert for HOM-1026. Move basement valuables, secure outdoor items. High winds (90 km/h) &amp; heavy rain (80mm) expected. Stay safe!"
-(Length: 142 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Move valuable items and electronics off the floor in the unfinished basement to protect them from potential water damage.
+Rationale: With 80 mm of rain and no sump pump or backwater valve, the unfinished basement is at high risk of flooding or sewer backup.
+[P2] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and garden tools.
+Rationale: 90 km/h wind gusts can turn unsecured objects into dangerous projectiles, causing property damage or injury.
+[P3] INDOOR_WATER_PROTECTION: Monitor for signs of water accumulation in the basement or around the foundation and be prepared to use towels or barriers if minor seepage occurs.
+Rationale: Given the heavy rainfall and lack of active water mitigation systems (sump pump, backwater valve), continuous monitoring is crucial to detect and respond to water ingress promptly.</t>
         </is>
       </c>
       <c r="J44" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90km/h winds expected. Move basement items off floor, secure outdoor objects, and monitor for water. Stay safe!"
+(Length: 132 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K44" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: High winds (90 km/h) and heavy rain (80mm) expected. Move basement valuables and secure outdoor items immediately. Stay safe!</t>
-        </is>
-      </c>
-      <c r="K44" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The property details such as the 24-year-old metal roof, unfinished basement, and absence of a sump pump and backwater valve are accurately reflected in the advisory. There are no fabricated or hallucinated claims regarding hail, snowfall, or tornado risk, as these are not mentioned in the ground truth. The micro actions and safety status are consistent with the risks outlined in the alert and property vulnerabilities. Overall, the advisory is a faithful representation of the ground truth data.</t>
-        </is>
-      </c>
-      <c r="M44" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N44" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and dwelling characteristics. The first action directly addresses the risk of water damage in the unfinished basement due to heavy rainfall and potential sewer backup, despite the coverage, by moving valuables to higher ground. The second action mitigates the risk of windborne projectiles by securing outdoor items, which is crucial given the 90 km/h wind gusts. The third action ensures preparedness for power outages, which are a common consequence of severe weather conditions like the one described. All actions are executable within the warning lead time and avoid dangerous outdoor activities during high winds, aligning with mandatory life-safety requirements.</t>
-        </is>
-      </c>
-      <c r="O44" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P44" s="20" t="inlineStr">
-        <is>
-          <t>The SMS and push notification are both concise, clear, and urgent without inciting panic. They immediately inform the homeowner of the storm threat and provide specific actions to take: moving basement valuables and securing outdoor items. The language is straightforward and free of insurance jargon, making it easy to understand in an emergency. The SMS is within the character limit, ensuring quick readability. The micro-actions are direct and actionable, further enhancing clarity and preparedness.</t>
-        </is>
-      </c>
-      <c r="Q44" s="21" t="n">
-        <v>5</v>
+Body: Heavy rainfall (80mm) and 90 km/h winds expected. Move basement items off floor, secure outdoor objects, and monitor for water ingress. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L44" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rain and 90 km/h wind gusts. The property details such as 'semi_detached dwelling', 'unfinished basement', 'NO sump pump', 'NO backwater valve', and 'metal roof (24 years old)' are all accurately reflected in the advisory. There is no mention of hail or tornado risk, consistent with the ground truth. The micro actions and rationale are appropriate given the property's vulnerabilities and the weather alert, without any fabricated or unverified claims. Therefore, the advisory is fully faithful to the ground truth.</t>
+        </is>
+      </c>
+      <c r="N44" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling vulnerabilities. The first action directly addresses the risk of water damage in the unfinished basement, which lacks a sump pump and backwater valve, by moving valuables off the floor. This is crucial given the high rainfall and potential for flooding. The second action addresses the risk of windborne projectiles due to 90 km/h gusts by securing outdoor items, which is a primary loss driver in such conditions. The third action involves monitoring for water ingress, which is essential given the absence of active water mitigation systems. All actions are executable within the warning lead time and directly target the primary loss drivers of the rainfall and wind event, while considering the dwelling's structural vulnerabilities and policy coverage.</t>
+        </is>
+      </c>
+      <c r="P44" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to move valuable items and electronics off the basement floor addresses the need to protect against water damage, satisfying the first mandatory action. The action to monitor for water accumulation in the basement partially covers the second mandatory action, but it does not address verifying the sump pump and backwater valve, which are not present in this case, so this part is irrelevant. However, the agent completely omits the action to close and seal exterior windows and doors, which is crucial given the wind-driven rain. Additionally, the action to secure outdoor items is illogical in this context as it does not relate to the mandatory actions focused on water ingress and does not mitigate the specific risks outlined in the alert.</t>
+        </is>
+      </c>
+      <c r="R44" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S44" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and within the character limit, effectively communicating the urgency of the situation without causing panic. It specifies the threat (heavy rain and strong winds) and provides immediate, actionable steps (move items, secure objects, monitor water). The language is straightforward and free of insurance jargon, making it easy for a homeowner to understand and act upon quickly. The push notification and micro-actions are similarly clear and actionable, providing detailed instructions without unnecessary complexity or technical terms.</t>
+        </is>
+      </c>
+      <c r="T44" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="45" ht="135" customHeight="1">
@@ -4719,62 +5334,83 @@
       </c>
       <c r="G45" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
-Rain: 80.0 mm | Snow: None cm
+Rain: 80.0 mm | Snow: 0.0 cm
 Tornado Risk: NO
-Identified Vulnerabilities: Crawlspace, Townhouse (potential for shared drainage issues)
-Identified Gaps: Overland Water Endorsement (uninsured surface overland flood runoff)</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Move any valuable items or electronics from the crawlspace to higher ground to protect them from potential water damage.
-Rationale: Heavy rainfall (80 mm) and a crawlspace foundation, combined with uninsured overland water, significantly increase the risk of water intrusion and damage to contents.
-[P2] INDOOR_WATER_PROTECTION: Ensure all basement windows and any ground-level openings are securely closed and sealed to prevent water entry.
-Rationale: With 80 mm of rain, water can easily enter through unsealed openings, leading to damage, especially with a crawlspace.
-[P3] LIFE_SAFETY: If safe to do so from the ground, quickly secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and decorations.
-Rationale: Wind gusts up to 90 km/h can turn unsecured items into dangerous projectiles, causing property damage or injury. Prioritize personal safety and avoid prolonged exposure to high winds.</t>
+Identified Vulnerabilities: crawlspace basement
+Identified Gaps: Overland Water Endorsement (UNINSURED)</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy rain &amp; 90km/h winds for HOM-1027. Move valuables from crawlspace &amp; secure ground openings. Overland flood not covered. Stay safe! Info: +1-613-555-1027"
-(Length: 165 / 160 chars)</t>
+          <t>[P1] VEHICLE_PROTECTION: Move vehicles from street parking or low-lying areas to higher ground or a garage to prevent flood damage.
+Rationale: Torrential rainfall and urban flash flooding risk, coupled with uninsured overland water coverage, poses a significant threat to vehicles.
+[P2] INDOOR_WATER_PROTECTION: Monitor your crawlspace for any signs of water intrusion or dampness, even with your sump pump and backwater valve.
+Rationale: Extreme rainfall (up to 80 mm) can overwhelm drainage systems, potentially leading to water entry into the crawlspace despite existing protections.
+[P3] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and decorations.
+Rationale: Wind gusts up to 90 km/h can turn unsecured objects into dangerous projectiles, causing property damage or injury.</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Move vehicles to higher ground due to flash flood risk. Secure outdoor items. Do NOT climb ladders. Stay safe! #HOM1027"
+(Length: 127 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rainfall (80mm) and 90 km/h winds expected. Move crawlspace valuables and secure ground openings. Overland flood is not covered. Contact Sebastian Simard at +1-613-555-1027 for more.</t>
-        </is>
-      </c>
-      <c r="K45" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rainfall and 90 km/h wind gusts. The property is a townhouse with a crawlspace, and the advisory correctly identifies these vulnerabilities. The advisory also accurately notes the lack of overland water endorsement, which is a coverage gap. All contact information and policyholder details are consistent with the ground truth. There are no fabricated or hallucinated claims in the advisory.</t>
-        </is>
-      </c>
-      <c r="M45" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N45" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and dwelling characteristics. The first action directly addresses the risk of water damage to contents in the crawlspace, which is particularly important given the uninsured overland water gap. The second action focuses on preventing water entry through potential vulnerabilities in the structure, which is crucial given the heavy rainfall and the presence of a crawlspace. The third action addresses life safety by mitigating the risk of windborne projectiles, which is appropriate given the forecasted wind gusts. All actions are executable within the warning lead time and prioritize safety, making them exemplary in relevance and tailoring.</t>
-        </is>
-      </c>
-      <c r="O45" s="22" t="n">
+Body: Torrential rain and 90 km/h winds expected. Move vehicles, secure outdoor items, and monitor crawlspace. Do NOT climb ladders.</t>
+        </is>
+      </c>
+      <c r="L45" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M45" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning event, wind gusts of 90 km/h, and the 80 mm rainfall are directly mentioned in the weather alert. The property details such as the crawlspace basement, presence of a sump pump, and lack of overland water endorsement are accurately reflected in the advisory. No hail or snowfall is mentioned, consistent with the alert. The micro-actions are appropriate and based on the provided data, with no fabricated or unverified claims. All contact information and policyholder details match the ground truth.</t>
+        </is>
+      </c>
+      <c r="N45" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant and well-tailored to the specific peril of torrential rainfall and wind gusts, considering the dwelling's structural features and policy gaps. 
+1. The action to move vehicles to higher ground directly addresses the risk of overland water damage, which is uninsured, and is crucial given the urban flash flooding threat. This action is executable within the warning lead time and targets a significant loss driver.
+2. Monitoring the crawlspace for water intrusion is pertinent due to the potential for drainage systems to be overwhelmed by the heavy rainfall. This action is tailored to the dwelling's crawlspace feature and acknowledges the presence of a sump pump and backwater valve, ensuring comprehensive risk management.
+3. Securing loose outdoor items is a critical life-safety measure given the high wind speeds, preventing potential projectile damage. This action is appropriate and necessary for the wind conditions described.
+Overall, the actions are well-aligned with the specific weather conditions and the property's vulnerabilities, ensuring effective loss mitigation.</t>
+        </is>
+      </c>
+      <c r="P45" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P45" s="20" t="inlineStr">
-        <is>
-          <t>The SMS exceeds the 160-character limit, which can hinder quick readability in an emergency. It effectively communicates the threat (heavy rain and winds) and the immediate actions (move valuables, secure openings), but the mention of 'Overland flood not covered' introduces insurance jargon that could confuse homeowners during a crisis. The push notification is clear but slightly wordy, and the contact information might be unnecessary in an urgent alert. The micro-actions are clear and actionable, but the SMS and push notification could benefit from more concise phrasing to enhance clarity and urgency.</t>
-        </is>
-      </c>
-      <c r="Q45" s="21" t="n">
-        <v>4.33</v>
+      <c r="Q45" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions partially cover the mandatory actions. The action to monitor the crawlspace for water intrusion aligns with the requirement to monitor the basement and verify sump pump and backwater valve functionality. However, the agent fails to address the need to elevate or move valuables from the crawlspace and does not mention sealing exterior windows and doors. The additional action to move vehicles is illogical in the context of property protection for a townhouse, as it does not relate to the dwelling's structural or interior protection. The action to secure loose outdoor items is logical given the wind conditions but does not cover any mandatory actions.</t>
+        </is>
+      </c>
+      <c r="R45" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S45" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and actionable, providing immediate instructions on what to do (move vehicles, secure items) and what not to do (climb ladders) in a flash flood scenario. It avoids any insurance jargon and maintains a calm yet urgent tone. The character count is well within the limit, ensuring quick readability.
+The push notification effectively communicates the urgency of the situation with a clear title and body. It specifies the weather conditions and provides actionable steps without overwhelming the reader. The instructions are straightforward and free of technical language.
+The micro-actions are detailed yet clear, providing specific steps to mitigate damage. They avoid jargon and are easy to follow, ensuring homeowners can quickly understand and act upon them.</t>
+        </is>
+      </c>
+      <c r="T45" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="46" ht="135" customHeight="1">
@@ -4820,62 +5456,77 @@
       </c>
       <c r="G46" s="20" t="inlineStr">
         <is>
+          <t>• Close, latch, and lock all balcony doors and windows tightly against 90 km/h wind-driven rain infiltration
+• Monitor interior window perimeters, balcony thresholds, and exterior walls for water seepage, keeping towels or barriers ready
+• Ensure balcony drainage at floor level is unobstructed to prevent torrential rainwater from pooling and overflowing into the living area</t>
+        </is>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: Highrise condo with 7-year-old tar and gravel roof susceptible to high winds and heavy rain, Slab-on-grade basement, but urban flash flooding can still affect ground-level units or common areas
+Identified Vulnerabilities: Highrise condo susceptible to wind damage on balconies and water ingress through windows/balcony doors during heavy rain.
 Identified Gaps: None</t>
         </is>
       </c>
-      <c r="H46" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_SHELTER: Secure any loose items on balconies or patios to prevent them from becoming projectiles in high winds.
-Rationale: High wind gusts of 90 km/h can turn unsecured items into dangerous projectiles, posing a risk to property and safety.
-[P2] INDOOR_WATER_PROTECTION: Monitor for signs of urban flash flooding, especially if your unit is on a lower floor or if common areas are susceptible.
-Rationale: Torrential downpours of 80 mm can lead to localized urban flash flooding, potentially affecting ground-level units or building common areas.
-[P3] LIFE_SAFETY: Review your building's emergency procedures for severe weather, as high-rise living has specific protocols.
-Rationale: Familiarity with building-specific emergency plans is crucial for safety and effective response during severe weather events like heavy rainfall and strong winds.</t>
-        </is>
-      </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Secure balcony items due to 90 km/h winds. Monitor for urban flooding. Review building emergency plan. Stay safe!"
-(Length: 121 / 160 chars)</t>
+          <t>[P1] INDOOR_WATER_PROTECTION: Ensure all windows and balcony doors are tightly closed and locked to prevent water intrusion from heavy rainfall.
+Rationale: Heavy rainfall (80 mm) and high winds (90 km/h) can force water into the dwelling through unsecured openings, leading to interior damage.
+[P2] LIFE_SAFETY: Secure all loose items on balconies and patios (e.g., furniture, planters, decorations) to prevent them from becoming dangerous projectiles in high winds.
+Rationale: Wind gusts of 90 km/h can easily dislodge unsecured items, posing a significant safety risk to people and property below.
+[P3] INDOOR_SHELTER: Stay informed about the storm's progression through local weather alerts and be prepared for potential power interruptions.
+Rationale: Monitoring official weather updates ensures timely response to changing conditions, and preparing for outages helps maintain safety and comfort.</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Storm alert for HOM-1028. Secure balcony items &amp; close all windows/doors. High winds (90km/h) &amp; heavy rain (80mm) expected. Stay safe!"
+(Length: 142 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K46" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: 90 km/h winds &amp; 80mm rain expected. Secure balcony items, monitor for urban flooding, and review building emergency plan.</t>
-        </is>
-      </c>
-      <c r="K46" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies wind gusts of 90 km/h and rainfall of 60 to 80 mm, which matches the advisory's claims of 90 km/h wind gusts and 80 mm of rainfall. The property details such as the dwelling type (highrise condo), roof type (tar and gravel), and roof age (7 years) are accurately reflected in the advisory. The advisory correctly notes the absence of a sump pump and the slab-on-grade basement type, aligning with the ground truth. No hail or tornado risk is mentioned, consistent with the alert. All micro-actions and safety recommendations are appropriate and based on the factual data provided. There is no evidence of hallucination or unverified speculation in the advisory.</t>
-        </is>
-      </c>
-      <c r="M46" s="21" t="n">
+Body: High winds (90km/h) and heavy rain (80mm) expected for HOM-1028. Secure balcony items and ensure all windows/doors are tightly closed. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L46" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M46" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies wind gusts up to 90 km/h and rainfall between 60 to 80 mm, which matches the advisory's claims of 90 km/h wind gusts and 80 mm of rainfall. The advisory correctly identifies the dwelling as a highrise condo, consistent with the property data. There is no mention of hail or tornado risk, aligning with the alert's focus on rainfall and wind. The advisory's micro-actions and safety recommendations are appropriate for the described conditions and do not introduce any unverified features or metrics. All contact information and policyholder details are accurately reflected from the ground truth.</t>
+        </is>
+      </c>
+      <c r="N46" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="N46" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant to the active weather hazard of torrential rain and high winds, particularly for a high-rise condo. The first action addresses the risk of windborne projectiles, which is pertinent given the 90 km/h wind gusts, although it could be more tailored by specifying the condo's balcony setup. The second action is relevant for monitoring urban flash flooding, especially for lower-floor units, aligning well with the risk of localized flooding. However, it could be more tailored by considering the specific floor level of the unit. The third action on reviewing emergency procedures is important for life safety in a high-rise during severe weather, though it is somewhat generic. Overall, the actions are well-aligned with the peril and dwelling type, but minor tailoring could enhance their specificity.</t>
-        </is>
-      </c>
-      <c r="O46" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P46" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (90 km/h winds) and provides actionable steps (secure balcony items, monitor flooding, review emergency plan). It is well within the character limit and free of jargon. The push notification complements the SMS by providing additional context (rain expected) and maintains clarity and urgency. The micro-actions are detailed yet straightforward, avoiding technical language and focusing on practical steps, enhancing the overall clarity and effectiveness of the communication.</t>
-        </is>
-      </c>
-      <c r="Q46" s="21" t="n">
-        <v>4.67</v>
+      <c r="O46" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are highly relevant to the active peril of torrential rainfall and high winds, and they are well-tailored to the dwelling's characteristics as a highrise condo. The first action addresses the risk of water intrusion through windows and doors, which is a primary concern during heavy rainfall, especially with the wind gusts that can drive rain into the building. The second action is crucial for life safety, as unsecured items on balconies can become projectiles in high winds, posing a risk to people and property below. The third action, while important for general preparedness, is less directly tied to the specific structural vulnerabilities or policy gaps of the dwelling, which is why the score is not a perfect 5. However, it is still a prudent measure given the potential for power outages during severe weather. Overall, the actions are well-aligned with the peril and the dwelling's specific context, but could be slightly improved by addressing any potential water ingress through other building vulnerabilities, such as drainage systems.</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="20" t="inlineStr">
+        <is>
+          <t>The agent successfully covered the mandatory action of securing windows and balcony doors against wind-driven rain infiltration. However, it completely omitted the actions related to monitoring for water seepage and ensuring balcony drainage is unobstructed. These are critical for preventing water damage in the described torrential rain conditions. The additional actions proposed by the agent, such as securing loose items on balconies and staying informed about the storm, are logical and relevant to the situation, but they do not compensate for the missing mandatory actions. Therefore, the score reflects the omission of two key mandatory actions.</t>
+        </is>
+      </c>
+      <c r="R46" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S46" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and within the character limit, effectively communicating the urgency of the storm threat and immediate actions to take. It avoids any insurance jargon and uses straightforward language. The push notification complements the SMS by reiterating the key actions and maintaining a clear, urgent tone. The micro-actions provide detailed, actionable steps without overwhelming the reader, ensuring clarity and focus on safety. Overall, the communication is well-structured, direct, and free of technical language, making it highly effective for emergency conditions.</t>
+        </is>
+      </c>
+      <c r="T46" s="21" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="47" ht="135" customHeight="1">
@@ -4921,15 +5572,22 @@
       </c>
       <c r="G47" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
 Identified Vulnerabilities: Finished basement, No backwater valve, Asphalt shingle roof (11 years old) vulnerable to high winds
-Identified Gaps: Sewer backup damage is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
+Identified Gaps: Sewer Backup Endorsement: Basement sewer backup damage is UNINSURED</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>[P1] INDOOR_WATER_PROTECTION: Move valuables and electronics from the basement floor to higher ground.
 Rationale: Protects against potential urban flash flooding and uninsured sewer backup due to torrential downpours.
@@ -4939,44 +5597,52 @@
 Rationale: High wind gusts (90 km/h) and heavy rainfall pose a risk of flying debris and structural damage.</t>
         </is>
       </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>"Urgent: Heavy rain &amp; 90km/h winds. Move basement valuables to higher ground. Stay indoors. Info: david.leblanc29@example.ca"
-(Length: 123 / 160 chars)</t>
-        </is>
-      </c>
       <c r="J47" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90km/h winds expected. Move basement valuables to higher ground. Stay indoors. Info: david.leblanc29@example.ca"
+(Length: 132 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rain and 90 km/h winds expected. Move basement valuables to higher ground. Ensure windows/doors are sealed. Stay indoors.</t>
-        </is>
-      </c>
-      <c r="K47" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm rainfall and 90 km/h wind gusts. The advisory correctly notes the absence of hail and tornado risk, consistent with the alert. The property details, such as the finished basement, absence of a backwater valve, and the 11-year-old asphalt shingle roof, are accurately reflected in the exposure analysis. The advisory's micro-actions are appropriate and based on the vulnerabilities and coverage gaps identified, such as the uninsured sewer backup risk. All contact information and policyholder details are correctly stated. There is no evidence of hallucination or unverified speculation.</t>
-        </is>
-      </c>
-      <c r="M47" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N47" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are exemplary in relevance and tailoring to the active weather hazard and the dwelling's specific vulnerabilities. The first action directly addresses the risk of basement flooding due to the uninsured sewer backup gap by moving valuables and electronics to higher ground, which is crucial given the finished basement. The second action ensures that potential water intrusion points are secured, which is vital for preventing water damage during torrential downpours. The third action prioritizes life safety by advising occupants to stay indoors and away from windows, which is appropriate given the high wind gusts. All actions are executable within the warning lead time and directly target the primary loss drivers of the peril.</t>
-        </is>
-      </c>
-      <c r="O47" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P47" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy rain and strong winds) and provides a clear first action (move valuables to higher ground). The message is free of insurance jargon and complies with the character limit. The push notification and micro-actions are similarly clear and actionable, providing specific steps to mitigate risk without using technical language.</t>
-        </is>
-      </c>
-      <c r="Q47" s="21" t="n">
-        <v>5</v>
+Body: Heavy rain and 90 km/h winds expected. Move basement valuables to higher ground and ensure windows are sealed. Stay indoors.</t>
+        </is>
+      </c>
+      <c r="L47" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies '60 to 80 mm of rain in under 3 hours with wind gusts to 90 km/h,' which matches the advisory's claims of 80 mm rainfall and 90 km/h wind gusts. The advisory correctly notes the absence of hail and tornado risk, consistent with the alert. The property details, such as the 'finished basement,' 'no backwater valve,' and 'asphalt shingle roof (11 years old),' are accurately reflected in the advisory's exposure analysis. The advisory's micro-actions are appropriate and based on the alert's mention of 'localized urban flash flooding and sewer backup risk.' There is no evidence of hallucination or unverified speculation in the advisory.</t>
+        </is>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the active peril and the dwelling's specific vulnerabilities. The first action directly addresses the risk of basement flooding and the uninsured sewer backup gap by moving valuables and electronics to higher ground, which is crucial given the finished basement and lack of sewer backup coverage. The second action ensures that potential water entry points are secured, which is vital for preventing water intrusion during torrential downpours. The third action prioritizes life safety by advising occupants to stay indoors and away from windows, which is appropriate given the high wind gusts and potential for flying debris. All actions are executable within the warning lead time and directly target the primary loss drivers of the rainfall event.</t>
+        </is>
+      </c>
+      <c r="P47" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="20" t="inlineStr">
+        <is>
+          <t>The agent's actions cover two of the three mandatory actions. The action to move valuables and electronics from the basement floor to higher ground addresses the first mandatory action. The action to ensure all basement windows and ground-level doors are securely closed and sealed partially covers the third mandatory action, though it does not explicitly mention all exterior windows and doors. The second mandatory action, which involves monitoring for water ingress and verifying sump pump functionality, is completely omitted. Additionally, the agent's suggestion to stay indoors and away from windows is categorized as a life-safety action, which is outside the scope of property loss mitigation and thus considered illogical in this context.</t>
+        </is>
+      </c>
+      <c r="R47" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, clear, and urgent without inciting panic. It immediately informs the homeowner of the threat (heavy rain and strong winds) and provides a clear first action (move valuables to higher ground). The message is within the character limit and free of insurance jargon. The push notification and micro-actions are also clear and actionable, providing specific steps to mitigate risk without using technical language.</t>
+        </is>
+      </c>
+      <c r="T47" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="48" ht="135" customHeight="1">
@@ -5022,71 +5688,86 @@
       </c>
       <c r="G48" s="20" t="inlineStr">
         <is>
+          <t>• Elevate or move valuable belongings, electronics, and furnishings from the basement or crawlspace floor to higher ground to protect against sewer backup and water seepage
+• Monitor interior basement walls, window wells, and entryways for water ingress, and verify that the sump pump and backwater valve are actively functioning
+• Close, tightly latch, and seal all exterior windows and doors to prevent water penetration and structural damage from 90 km/h wind-driven rain</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
           <t>Identified Event: rainfall warning in effect
 Wind Gust: 90 km/h | Hail: None (None cm)
 Rain: 80.0 mm | Snow: None cm
 Tornado Risk: NO
-Identified Vulnerabilities: unfinished basement, no sump pump, metal roof (15 years old) susceptible to 90 km/h wind gusts
-Identified Gaps: Overland Water Endorsement: NO - CRITICAL GAP: Surface overland flood runoff is UNINSURED</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>[P1] INDOOR_WATER_PROTECTION: Close and lock all basement windows and ground-level doors/openings to prevent water ingress.
-Rationale: Heavy rainfall (up to 80 mm) and lack of a sump pump increase the risk of basement flooding.
-[P2] VEHICLE_PROTECTION: Move vehicles from street parking or low-lying areas to a garage or higher ground.
-Rationale: Risk of urban flash flooding due to torrential downpours, and overland water damage is uninsured.
-[P3] LIFE_SAFETY: Secure or bring indoors any loose outdoor items (patio furniture, garbage bins, decorations).
-Rationale: Wind gusts up to 90 km/h can turn unsecured items into dangerous projectiles.</t>
+Identified Vulnerabilities: No sump pump, Unfinished basement (susceptible to water ingress), Semi-detached dwelling (potential shared wall vulnerabilities)
+Identified Gaps: Overland Water Endorsement: NO - Surface overland flood runoff is UNINSURED</t>
         </is>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>"Urgent: Heavy rain &amp; 90km/h winds. Close basement windows, move cars to high ground, secure outdoor items. Stay safe! #HOM-1030"
-(Length: 127 / 160 chars)</t>
+          <t>[P1] LIFE_SAFETY: Secure or bring indoors any loose outdoor items such as patio furniture, garbage bins, and decorations to prevent them from becoming projectiles in 90 km/h wind gusts.
+Rationale: High wind gusts pose a significant risk of property damage and injury from flying debris.
+[P2] INDOOR_WATER_PROTECTION: Move any valuable items, electronics, and important documents from your basement floor to higher ground or upper levels.
+Rationale: With up to 80 mm of rain and no overland water coverage, there is a risk of urban flash flooding and sewer backup impacting your unfinished basement.
+[P3] INDOOR_WATER_PROTECTION: Ensure all basement windows and doors are securely closed and properly sealed to prevent water ingress from heavy rainfall and potential surface runoff.
+Rationale: Heavy rainfall increases the risk of water entering through unsealed openings, especially with an unfinished basement and no sump pump.</t>
         </is>
       </c>
       <c r="J48" s="20" t="inlineStr">
         <is>
+          <t>"Urgent: Heavy rain &amp; 90 km/h winds expected. Secure outdoor items &amp; move basement valuables to higher ground. Close basement windows. Stay safe! -PNC"
+(Length: 149 / 160 chars)</t>
+        </is>
+      </c>
+      <c r="K48" s="20" t="inlineStr">
+        <is>
           <t>Title: Urgent: Storm Mitigation Required
-Body: Heavy rain (80mm) &amp; 90km/h winds expected. Close basement windows, move vehicles to higher ground, and secure all outdoor items. Overland water is uninsured.</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L48" s="20" t="inlineStr">
-        <is>
-          <t>The advisory is fully grounded in the provided ground truth data. The rainfall warning specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm rainfall and 90 km/h wind gusts. The property details such as 'unfinished basement', 'no sump pump', and 'metal roof (15 years old)' are accurately reflected from the ground truth. The advisory correctly identifies the lack of overland water endorsement as a coverage gap, which is consistent with the ground truth data. No unverified claims or hallucinations are present.</t>
-        </is>
-      </c>
-      <c r="M48" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N48" s="20" t="inlineStr">
-        <is>
-          <t>The proposed actions are highly relevant and well-tailored to the specific peril and dwelling characteristics. The first action addresses the risk of water ingress through basement windows and doors, which is critical given the lack of a sump pump and the overland water coverage gap. The second action mitigates the risk of vehicle damage from urban flash flooding, which is particularly important due to the uninsured overland water risk. The third action addresses life safety by preventing windborne projectiles, which is crucial given the forecasted wind gusts. All actions are executable within the warning lead time and avoid dangerous outdoor work during high winds.</t>
-        </is>
-      </c>
-      <c r="O48" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P48" s="20" t="inlineStr">
-        <is>
-          <t>The SMS is concise, clear, and actionable, providing immediate instructions on what to do in response to the threat of heavy rain and high winds. It avoids any insurance jargon and stays well within the character limit, making it easy to read quickly in an emergency. The push notification is similarly clear, with a slightly more detailed description of the weather conditions, but still maintains clarity and urgency without causing panic. The micro-actions are straightforward and provide specific steps to mitigate potential damage, free of technical language or insurance terms.</t>
-        </is>
-      </c>
-      <c r="Q48" s="21" t="n">
-        <v>5</v>
+Body: Heavy rain (80mm) &amp; 90 km/h winds expected. Secure outdoor items, move basement valuables to higher ground, and close basement windows. Overland water is uninsured. Stay safe!</t>
+        </is>
+      </c>
+      <c r="L48" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M48" s="20" t="inlineStr">
+        <is>
+          <t>The advisory is fully grounded in the provided ground truth data. The weather alert specifies 60 to 80 mm of rain and wind gusts up to 90 km/h, which matches the advisory's claims of 80 mm of rain and 90 km/h wind gusts. The advisory correctly notes the absence of hail and tornado risk, consistent with the alert. The property details, such as the absence of a sump pump, the unfinished basement, and the semi-detached dwelling type, are accurately reflected in the advisory. The coverage gap regarding the lack of overland water endorsement is also correctly identified. All actions and recommendations are based on the factual data provided, with no hallucinations or fabrications present.</t>
+        </is>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>The proposed actions are exemplary in relevance and tailoring to the specific peril and dwelling characteristics. The first action addresses the risk of windborne projectiles, which is a primary concern given the forecasted 90 km/h wind gusts. This is crucial for life safety and property protection. The second action is highly relevant as it mitigates the risk of water damage to valuable items in the basement, considering the dwelling's lack of overland water coverage and the unfinished state of the basement. The third action focuses on preventing water ingress through basement openings, which is critical given the heavy rainfall and the absence of a sump pump. All actions are executable within the warning lead time and directly target the primary loss drivers of the active weather peril, while also considering the dwelling's structural vulnerabilities and policy gaps.</t>
+        </is>
+      </c>
+      <c r="P48" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="20" t="inlineStr">
+        <is>
+          <t>The agent's proposed actions cover two of the three mandatory actions. The action to move valuable items from the basement to higher ground addresses the need to protect against sewer backup and water seepage. The action to ensure all basement windows and doors are securely closed and sealed aligns with the requirement to prevent water penetration from wind-driven rain. However, the agent did not address monitoring the basement for water ingress or verifying the functionality of the backwater valve, which is a critical aspect of the mandatory actions. The additional action to secure outdoor items is logical and relevant given the high wind gusts, but it does not compensate for the missing mandatory action related to monitoring and verifying basement protections. Therefore, the score is 4, as the coverage is substantially complete but misses one secondary aspect.</t>
+        </is>
+      </c>
+      <c r="R48" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S48" s="20" t="inlineStr">
+        <is>
+          <t>The SMS is concise, urgent, and clear, effectively communicating the threat (heavy rain and strong winds) and immediate actions (securing items, moving valuables, closing windows). It avoids insurance jargon and fits within the character limit. The push notification is slightly more detailed, mentioning 'overland water is uninsured,' which introduces a minor element of insurance-related information that could be confusing in an emergency. The micro-actions are clear but slightly wordy, which could be streamlined for quicker comprehension during a stressful situation. Overall, the communications are effective but could be improved by simplifying the micro-actions and removing the insurance reference in the push notification.</t>
+        </is>
+      </c>
+      <c r="T48" s="21" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="K5:P5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="L5:S5"/>
+    <mergeCell ref="H5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5098,7 +5779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5155,7 +5836,7 @@
       </c>
     </row>
     <row r="4" ht="95" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Faithfulness &amp; Anti-Hallucination</t>
         </is>
@@ -5192,7 +5873,7 @@
       </c>
     </row>
     <row r="5" ht="95" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Action Relevance &amp; Tailoring</t>
         </is>
@@ -5229,37 +5910,74 @@
       </c>
     </row>
     <row r="6" ht="95" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Action Correctness &amp; Semantic Coverage</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Measures whether the expert-defined mandatory mitigation actions from the golden reference dataset are semantically present in the agent's proposed micro-actions, and verifies that any additional actions proposed by the model are logical and appropriate for the property and peril.</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Complete &amp; Sound: 100% of reference mandatory actions are semantically captured. Any additional actions suggested by the agent are logical, practical, and appropriate for the dwelling and peril.</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Substantially Complete &amp; Sound: All mandatory actions are semantically captured, but an additional action is somewhat redundant or marginally relevant; OR all mandatory actions are covered except one minor secondary aspect that is only partially addressed, while all actions remain logical.</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Moderate Coverage or Questionable Actions: One mandatory action is completely omitted, OR all mandatory actions are covered but the model includes an illogical, ungrounded, or irrelevant additional action (e.g., advising gutter cleaning for an upper-floor condo).</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Poor Coverage / Multiple Illogical Actions: Multiple mandatory actions are missing, AND/OR the model proposes multiple illogical, contradictory, or ungrounded additional actions.</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>No Coverage or Completely Illogical: None of the reference mandatory actions are semantically identifiable, OR the proposed actions are completely illogical and unrelated to the hazard or dwelling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Communication Clarity &amp; Actionability</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Measures how clear, concise, actionable, and appropriately urgent the customer-facing communications (SMS and Push Notifications) and micro-action instructions are, ensuring they are free of insurance jargon and immediately understandable to a homeowner under stress.</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Crystal Clear &amp; Actionable: Punchy, unambiguous, urgent without causing panic, completely free of insurance jargon, and immediately tells the homeowner WHAT the threat is and WHAT to do first. SMS strictly complies with length limits and maximizes impact.</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Clear &amp; Effective: Easy to understand with minor stylistic stiffness or slightly wordy phrasing.</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>Adequate: Understandable, but somewhat wordy, passive, or slightly dense for a quick glance during an emergency.</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>Poor Clarity: Vague instructions, confusing sequencing, heavy jargon (e.g., 'endorsement riders'), or awkward phrasing.</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>Incomprehensible / Dangerous: Confusing, contradictory, illegible, or dangerously unclear instructions.</t>
         </is>
